--- a/app_horarios/datos/excel/export-15-04.xlsx
+++ b/app_horarios/datos/excel/export-15-04.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F0A45E-9DC8-43E0-8805-C456A9AFB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="11" activeTab="18" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="asignaturas" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,20 @@
     <sheet name="tfg" sheetId="18" r:id="rId18"/>
     <sheet name="usuarios" sheetId="19" r:id="rId19"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -751,7 +764,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -809,7 +822,7 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/app_horarios/datos/excel/export-15-04.xlsx
+++ b/app_horarios/datos/excel/export-15-04.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\Ingeniería informática\4º Trabajo de Fin de Grado\Trabajo-Fin-de-Grado-2025-2026\app_horarios\datos\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2F0A45E-9DC8-43E0-8805-C456A9AFB544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C384CC-F9C5-46C6-954E-24A282A43DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" firstSheet="11" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="asignaturas" sheetId="1" r:id="rId1"/>
@@ -766,7 +766,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -779,6 +779,14 @@
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -816,13 +824,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1251,10 +1260,10 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:H681"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>127</v>
       </c>
@@ -1269,6 +1278,9527 @@
       </c>
       <c r="E1" s="1" t="s">
         <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>6392</v>
+      </c>
+      <c r="E2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>101</v>
+      </c>
+      <c r="C3">
+        <v>6392</v>
+      </c>
+      <c r="E3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>102</v>
+      </c>
+      <c r="C4">
+        <v>6392</v>
+      </c>
+      <c r="E4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>6393</v>
+      </c>
+      <c r="E5">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>101</v>
+      </c>
+      <c r="C6">
+        <v>6393</v>
+      </c>
+      <c r="E6">
+        <v>25</v>
+      </c>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>102</v>
+      </c>
+      <c r="C7">
+        <v>6393</v>
+      </c>
+      <c r="E7">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>6394</v>
+      </c>
+      <c r="E8">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>101</v>
+      </c>
+      <c r="C9">
+        <v>6394</v>
+      </c>
+      <c r="E9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>102</v>
+      </c>
+      <c r="C10">
+        <v>6394</v>
+      </c>
+      <c r="E10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>6395</v>
+      </c>
+      <c r="E11">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>101</v>
+      </c>
+      <c r="C12">
+        <v>6395</v>
+      </c>
+      <c r="E12">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>102</v>
+      </c>
+      <c r="C13">
+        <v>6395</v>
+      </c>
+      <c r="E13">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>6396</v>
+      </c>
+      <c r="E14">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>101</v>
+      </c>
+      <c r="C15">
+        <v>6396</v>
+      </c>
+      <c r="E15">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>102</v>
+      </c>
+      <c r="C16">
+        <v>6396</v>
+      </c>
+      <c r="E16">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>6397</v>
+      </c>
+      <c r="E17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>101</v>
+      </c>
+      <c r="C18">
+        <v>6397</v>
+      </c>
+      <c r="E18">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>102</v>
+      </c>
+      <c r="C19">
+        <v>6397</v>
+      </c>
+      <c r="E19">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>6398</v>
+      </c>
+      <c r="E20">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>101</v>
+      </c>
+      <c r="C21">
+        <v>6398</v>
+      </c>
+      <c r="E21">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>102</v>
+      </c>
+      <c r="C22">
+        <v>6398</v>
+      </c>
+      <c r="E22">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>6399</v>
+      </c>
+      <c r="E23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>101</v>
+      </c>
+      <c r="C24">
+        <v>6399</v>
+      </c>
+      <c r="E24">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25">
+        <v>102</v>
+      </c>
+      <c r="C25">
+        <v>6399</v>
+      </c>
+      <c r="E25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>1</v>
+      </c>
+      <c r="C26">
+        <v>6400</v>
+      </c>
+      <c r="E26">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>101</v>
+      </c>
+      <c r="C27">
+        <v>6400</v>
+      </c>
+      <c r="E27">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>102</v>
+      </c>
+      <c r="C28">
+        <v>6400</v>
+      </c>
+      <c r="E28">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29">
+        <v>6401</v>
+      </c>
+      <c r="E29">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>101</v>
+      </c>
+      <c r="C30">
+        <v>6401</v>
+      </c>
+      <c r="E30">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31">
+        <v>102</v>
+      </c>
+      <c r="C31">
+        <v>6401</v>
+      </c>
+      <c r="E31">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32">
+        <v>1</v>
+      </c>
+      <c r="C32">
+        <v>6402</v>
+      </c>
+      <c r="E32">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33">
+        <v>101</v>
+      </c>
+      <c r="C33">
+        <v>6402</v>
+      </c>
+      <c r="E33">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34">
+        <v>102</v>
+      </c>
+      <c r="C34">
+        <v>6402</v>
+      </c>
+      <c r="E34">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35">
+        <v>1</v>
+      </c>
+      <c r="C35">
+        <v>6403</v>
+      </c>
+      <c r="E35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36">
+        <v>101</v>
+      </c>
+      <c r="C36">
+        <v>6403</v>
+      </c>
+      <c r="E36">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37">
+        <v>102</v>
+      </c>
+      <c r="C37">
+        <v>6403</v>
+      </c>
+      <c r="E37">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>6404</v>
+      </c>
+      <c r="E38">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39">
+        <v>101</v>
+      </c>
+      <c r="C39">
+        <v>6404</v>
+      </c>
+      <c r="E39">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40">
+        <v>102</v>
+      </c>
+      <c r="C40">
+        <v>6404</v>
+      </c>
+      <c r="E40">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
+      </c>
+      <c r="C41">
+        <v>6405</v>
+      </c>
+      <c r="E41">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42">
+        <v>101</v>
+      </c>
+      <c r="C42">
+        <v>6405</v>
+      </c>
+      <c r="E42">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43">
+        <v>102</v>
+      </c>
+      <c r="C43">
+        <v>6405</v>
+      </c>
+      <c r="E43">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44">
+        <v>1</v>
+      </c>
+      <c r="C44">
+        <v>6406</v>
+      </c>
+      <c r="E44">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45">
+        <v>101</v>
+      </c>
+      <c r="C45">
+        <v>6406</v>
+      </c>
+      <c r="E45">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46">
+        <v>102</v>
+      </c>
+      <c r="C46">
+        <v>6406</v>
+      </c>
+      <c r="E46">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47">
+        <v>1</v>
+      </c>
+      <c r="C47">
+        <v>6407</v>
+      </c>
+      <c r="E47">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48">
+        <v>101</v>
+      </c>
+      <c r="C48">
+        <v>6407</v>
+      </c>
+      <c r="E48">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49">
+        <v>102</v>
+      </c>
+      <c r="C49">
+        <v>6407</v>
+      </c>
+      <c r="E49">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50">
+        <v>1</v>
+      </c>
+      <c r="C50">
+        <v>6408</v>
+      </c>
+      <c r="E50">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51">
+        <v>101</v>
+      </c>
+      <c r="C51">
+        <v>6408</v>
+      </c>
+      <c r="E51">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52">
+        <v>102</v>
+      </c>
+      <c r="C52">
+        <v>6408</v>
+      </c>
+      <c r="E52">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53">
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <v>6409</v>
+      </c>
+      <c r="E53">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54">
+        <v>101</v>
+      </c>
+      <c r="C54">
+        <v>6409</v>
+      </c>
+      <c r="E54">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55">
+        <v>102</v>
+      </c>
+      <c r="C55">
+        <v>6409</v>
+      </c>
+      <c r="E55">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56">
+        <v>1</v>
+      </c>
+      <c r="C56">
+        <v>6410</v>
+      </c>
+      <c r="E56">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57">
+        <v>101</v>
+      </c>
+      <c r="C57">
+        <v>6410</v>
+      </c>
+      <c r="E57">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58">
+        <v>102</v>
+      </c>
+      <c r="C58">
+        <v>6410</v>
+      </c>
+      <c r="E58">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>58</v>
+      </c>
+      <c r="B59">
+        <v>1</v>
+      </c>
+      <c r="C59">
+        <v>6411</v>
+      </c>
+      <c r="E59">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>59</v>
+      </c>
+      <c r="B60">
+        <v>101</v>
+      </c>
+      <c r="C60">
+        <v>6411</v>
+      </c>
+      <c r="E60">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61">
+        <v>102</v>
+      </c>
+      <c r="C61">
+        <v>6411</v>
+      </c>
+      <c r="E61">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>61</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62">
+        <v>6412</v>
+      </c>
+      <c r="E62">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>62</v>
+      </c>
+      <c r="B63">
+        <v>101</v>
+      </c>
+      <c r="C63">
+        <v>6412</v>
+      </c>
+      <c r="E63">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>63</v>
+      </c>
+      <c r="B64">
+        <v>102</v>
+      </c>
+      <c r="C64">
+        <v>6412</v>
+      </c>
+      <c r="E64">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>64</v>
+      </c>
+      <c r="B65">
+        <v>1</v>
+      </c>
+      <c r="C65">
+        <v>6413</v>
+      </c>
+      <c r="E65">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>65</v>
+      </c>
+      <c r="B66">
+        <v>101</v>
+      </c>
+      <c r="C66">
+        <v>6413</v>
+      </c>
+      <c r="E66">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>66</v>
+      </c>
+      <c r="B67">
+        <v>102</v>
+      </c>
+      <c r="C67">
+        <v>6413</v>
+      </c>
+      <c r="E67">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68">
+        <v>1</v>
+      </c>
+      <c r="C68">
+        <v>6414</v>
+      </c>
+      <c r="E68">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69">
+        <v>101</v>
+      </c>
+      <c r="C69">
+        <v>6414</v>
+      </c>
+      <c r="E69">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70">
+        <v>102</v>
+      </c>
+      <c r="C70">
+        <v>6414</v>
+      </c>
+      <c r="E70">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
+      </c>
+      <c r="C71">
+        <v>6415</v>
+      </c>
+      <c r="E71">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72">
+        <v>101</v>
+      </c>
+      <c r="C72">
+        <v>6415</v>
+      </c>
+      <c r="E72">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73">
+        <v>102</v>
+      </c>
+      <c r="C73">
+        <v>6415</v>
+      </c>
+      <c r="E73">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+      <c r="C74">
+        <v>6416</v>
+      </c>
+      <c r="E74">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75">
+        <v>101</v>
+      </c>
+      <c r="C75">
+        <v>6416</v>
+      </c>
+      <c r="E75">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76">
+        <v>102</v>
+      </c>
+      <c r="C76">
+        <v>6416</v>
+      </c>
+      <c r="E76">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77">
+        <v>1</v>
+      </c>
+      <c r="C77">
+        <v>6417</v>
+      </c>
+      <c r="E77">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78">
+        <v>101</v>
+      </c>
+      <c r="C78">
+        <v>6417</v>
+      </c>
+      <c r="E78">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79">
+        <v>1</v>
+      </c>
+      <c r="C79">
+        <v>6418</v>
+      </c>
+      <c r="E79">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80">
+        <v>101</v>
+      </c>
+      <c r="C80">
+        <v>6418</v>
+      </c>
+      <c r="E80">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81">
+        <v>1</v>
+      </c>
+      <c r="C81">
+        <v>6419</v>
+      </c>
+      <c r="E81">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82">
+        <v>101</v>
+      </c>
+      <c r="C82">
+        <v>6419</v>
+      </c>
+      <c r="E82">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83">
+        <v>1</v>
+      </c>
+      <c r="C83">
+        <v>6420</v>
+      </c>
+      <c r="E83">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84">
+        <v>101</v>
+      </c>
+      <c r="C84">
+        <v>6420</v>
+      </c>
+      <c r="E84">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85">
+        <v>1</v>
+      </c>
+      <c r="C85">
+        <v>6421</v>
+      </c>
+      <c r="E85">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86">
+        <v>101</v>
+      </c>
+      <c r="C86">
+        <v>6421</v>
+      </c>
+      <c r="E86">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="C87">
+        <v>6422</v>
+      </c>
+      <c r="E87">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88">
+        <v>101</v>
+      </c>
+      <c r="C88">
+        <v>6422</v>
+      </c>
+      <c r="E88">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89">
+        <v>1</v>
+      </c>
+      <c r="C89">
+        <v>6423</v>
+      </c>
+      <c r="E89">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90">
+        <v>101</v>
+      </c>
+      <c r="C90">
+        <v>6423</v>
+      </c>
+      <c r="E90">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91">
+        <v>1</v>
+      </c>
+      <c r="C91">
+        <v>6424</v>
+      </c>
+      <c r="E91">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92">
+        <v>101</v>
+      </c>
+      <c r="C92">
+        <v>6424</v>
+      </c>
+      <c r="E92">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93">
+        <v>1</v>
+      </c>
+      <c r="C93">
+        <v>6425</v>
+      </c>
+      <c r="E93">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94">
+        <v>101</v>
+      </c>
+      <c r="C94">
+        <v>6425</v>
+      </c>
+      <c r="E94">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95">
+        <v>6426</v>
+      </c>
+      <c r="E95">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96">
+        <v>101</v>
+      </c>
+      <c r="C96">
+        <v>6426</v>
+      </c>
+      <c r="E96">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="C97">
+        <v>6427</v>
+      </c>
+      <c r="E97">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98">
+        <v>101</v>
+      </c>
+      <c r="C98">
+        <v>6427</v>
+      </c>
+      <c r="E98">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99">
+        <v>1</v>
+      </c>
+      <c r="C99">
+        <v>6428</v>
+      </c>
+      <c r="E99">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100">
+        <v>101</v>
+      </c>
+      <c r="C100">
+        <v>6428</v>
+      </c>
+      <c r="E100">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101">
+        <v>1</v>
+      </c>
+      <c r="C101">
+        <v>6429</v>
+      </c>
+      <c r="E101">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102">
+        <v>101</v>
+      </c>
+      <c r="C102">
+        <v>6429</v>
+      </c>
+      <c r="E102">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103">
+        <v>1</v>
+      </c>
+      <c r="C103">
+        <v>6430</v>
+      </c>
+      <c r="E103">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104">
+        <v>101</v>
+      </c>
+      <c r="C104">
+        <v>6430</v>
+      </c>
+      <c r="E104">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105">
+        <v>1</v>
+      </c>
+      <c r="C105">
+        <v>6302</v>
+      </c>
+      <c r="E105">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106">
+        <v>101</v>
+      </c>
+      <c r="C106">
+        <v>6302</v>
+      </c>
+      <c r="E106">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107">
+        <v>102</v>
+      </c>
+      <c r="C107">
+        <v>6302</v>
+      </c>
+      <c r="E107">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108">
+        <v>103</v>
+      </c>
+      <c r="C108">
+        <v>6302</v>
+      </c>
+      <c r="E108">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109">
+        <v>104</v>
+      </c>
+      <c r="C109">
+        <v>6302</v>
+      </c>
+      <c r="E109">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110">
+        <v>105</v>
+      </c>
+      <c r="C110">
+        <v>6302</v>
+      </c>
+      <c r="E110">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111">
+        <v>1</v>
+      </c>
+      <c r="C111">
+        <v>6303</v>
+      </c>
+      <c r="E111">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112">
+        <v>101</v>
+      </c>
+      <c r="C112">
+        <v>6303</v>
+      </c>
+      <c r="E112">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113">
+        <v>102</v>
+      </c>
+      <c r="C113">
+        <v>6303</v>
+      </c>
+      <c r="E113">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114">
+        <v>103</v>
+      </c>
+      <c r="C114">
+        <v>6303</v>
+      </c>
+      <c r="E114">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115">
+        <v>104</v>
+      </c>
+      <c r="C115">
+        <v>6303</v>
+      </c>
+      <c r="E115">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116">
+        <v>105</v>
+      </c>
+      <c r="C116">
+        <v>6303</v>
+      </c>
+      <c r="E116">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117">
+        <v>6304</v>
+      </c>
+      <c r="E117">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118">
+        <v>101</v>
+      </c>
+      <c r="C118">
+        <v>6304</v>
+      </c>
+      <c r="E118">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119">
+        <v>102</v>
+      </c>
+      <c r="C119">
+        <v>6304</v>
+      </c>
+      <c r="E119">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120">
+        <v>103</v>
+      </c>
+      <c r="C120">
+        <v>6304</v>
+      </c>
+      <c r="E120">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121">
+        <v>104</v>
+      </c>
+      <c r="C121">
+        <v>6304</v>
+      </c>
+      <c r="E121">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122">
+        <v>105</v>
+      </c>
+      <c r="C122">
+        <v>6304</v>
+      </c>
+      <c r="E122">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123">
+        <v>1</v>
+      </c>
+      <c r="C123">
+        <v>6305</v>
+      </c>
+      <c r="E123">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124">
+        <v>101</v>
+      </c>
+      <c r="C124">
+        <v>6305</v>
+      </c>
+      <c r="E124">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125">
+        <v>102</v>
+      </c>
+      <c r="C125">
+        <v>6305</v>
+      </c>
+      <c r="E125">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126">
+        <v>103</v>
+      </c>
+      <c r="C126">
+        <v>6305</v>
+      </c>
+      <c r="E126">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127">
+        <v>104</v>
+      </c>
+      <c r="C127">
+        <v>6305</v>
+      </c>
+      <c r="E127">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128">
+        <v>1</v>
+      </c>
+      <c r="C128">
+        <v>6306</v>
+      </c>
+      <c r="E128">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129">
+        <v>101</v>
+      </c>
+      <c r="C129">
+        <v>6306</v>
+      </c>
+      <c r="E129">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130">
+        <v>102</v>
+      </c>
+      <c r="C130">
+        <v>6306</v>
+      </c>
+      <c r="E130">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131">
+        <v>103</v>
+      </c>
+      <c r="C131">
+        <v>6306</v>
+      </c>
+      <c r="E131">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132">
+        <v>104</v>
+      </c>
+      <c r="C132">
+        <v>6306</v>
+      </c>
+      <c r="E132">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133">
+        <v>1</v>
+      </c>
+      <c r="C133">
+        <v>6307</v>
+      </c>
+      <c r="E133">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134">
+        <v>101</v>
+      </c>
+      <c r="C134">
+        <v>6307</v>
+      </c>
+      <c r="E134">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135">
+        <v>102</v>
+      </c>
+      <c r="C135">
+        <v>6307</v>
+      </c>
+      <c r="E135">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136">
+        <v>103</v>
+      </c>
+      <c r="C136">
+        <v>6307</v>
+      </c>
+      <c r="E136">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137">
+        <v>104</v>
+      </c>
+      <c r="C137">
+        <v>6307</v>
+      </c>
+      <c r="E137">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138">
+        <v>1</v>
+      </c>
+      <c r="C138">
+        <v>6308</v>
+      </c>
+      <c r="E138">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139">
+        <v>101</v>
+      </c>
+      <c r="C139">
+        <v>6308</v>
+      </c>
+      <c r="E139">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140">
+        <v>102</v>
+      </c>
+      <c r="C140">
+        <v>6308</v>
+      </c>
+      <c r="E140">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141">
+        <v>103</v>
+      </c>
+      <c r="C141">
+        <v>6308</v>
+      </c>
+      <c r="E141">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142">
+        <v>104</v>
+      </c>
+      <c r="C142">
+        <v>6308</v>
+      </c>
+      <c r="E142">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143">
+        <v>1</v>
+      </c>
+      <c r="C143">
+        <v>6309</v>
+      </c>
+      <c r="E143">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>101</v>
+      </c>
+      <c r="C144">
+        <v>6309</v>
+      </c>
+      <c r="E144">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145">
+        <v>102</v>
+      </c>
+      <c r="C145">
+        <v>6309</v>
+      </c>
+      <c r="E145">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146">
+        <v>103</v>
+      </c>
+      <c r="C146">
+        <v>6309</v>
+      </c>
+      <c r="E146">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147">
+        <v>104</v>
+      </c>
+      <c r="C147">
+        <v>6309</v>
+      </c>
+      <c r="E147">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148">
+        <v>1</v>
+      </c>
+      <c r="C148">
+        <v>6310</v>
+      </c>
+      <c r="E148">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149">
+        <v>101</v>
+      </c>
+      <c r="C149">
+        <v>6310</v>
+      </c>
+      <c r="E149">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150">
+        <v>102</v>
+      </c>
+      <c r="C150">
+        <v>6310</v>
+      </c>
+      <c r="E150">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>150</v>
+      </c>
+      <c r="B151">
+        <v>103</v>
+      </c>
+      <c r="C151">
+        <v>6310</v>
+      </c>
+      <c r="E151">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>151</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+      <c r="C152">
+        <v>6311</v>
+      </c>
+      <c r="E152">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>152</v>
+      </c>
+      <c r="B153">
+        <v>101</v>
+      </c>
+      <c r="C153">
+        <v>6311</v>
+      </c>
+      <c r="E153">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>153</v>
+      </c>
+      <c r="B154">
+        <v>102</v>
+      </c>
+      <c r="C154">
+        <v>6311</v>
+      </c>
+      <c r="E154">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>154</v>
+      </c>
+      <c r="B155">
+        <v>103</v>
+      </c>
+      <c r="C155">
+        <v>6311</v>
+      </c>
+      <c r="E155">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>155</v>
+      </c>
+      <c r="B156">
+        <v>1</v>
+      </c>
+      <c r="C156">
+        <v>6312</v>
+      </c>
+      <c r="E156">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>156</v>
+      </c>
+      <c r="B157">
+        <v>101</v>
+      </c>
+      <c r="C157">
+        <v>6312</v>
+      </c>
+      <c r="E157">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>157</v>
+      </c>
+      <c r="B158">
+        <v>102</v>
+      </c>
+      <c r="C158">
+        <v>6312</v>
+      </c>
+      <c r="E158">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>158</v>
+      </c>
+      <c r="B159">
+        <v>103</v>
+      </c>
+      <c r="C159">
+        <v>6312</v>
+      </c>
+      <c r="E159">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>159</v>
+      </c>
+      <c r="B160">
+        <v>1</v>
+      </c>
+      <c r="C160">
+        <v>6313</v>
+      </c>
+      <c r="E160">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>160</v>
+      </c>
+      <c r="B161">
+        <v>101</v>
+      </c>
+      <c r="C161">
+        <v>6313</v>
+      </c>
+      <c r="E161">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>161</v>
+      </c>
+      <c r="B162">
+        <v>102</v>
+      </c>
+      <c r="C162">
+        <v>6313</v>
+      </c>
+      <c r="E162">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>162</v>
+      </c>
+      <c r="B163">
+        <v>103</v>
+      </c>
+      <c r="C163">
+        <v>6313</v>
+      </c>
+      <c r="E163">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>163</v>
+      </c>
+      <c r="B164">
+        <v>1</v>
+      </c>
+      <c r="C164">
+        <v>6314</v>
+      </c>
+      <c r="E164">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>164</v>
+      </c>
+      <c r="B165">
+        <v>101</v>
+      </c>
+      <c r="C165">
+        <v>6314</v>
+      </c>
+      <c r="E165">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>165</v>
+      </c>
+      <c r="B166">
+        <v>102</v>
+      </c>
+      <c r="C166">
+        <v>6314</v>
+      </c>
+      <c r="E166">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>166</v>
+      </c>
+      <c r="B167">
+        <v>103</v>
+      </c>
+      <c r="C167">
+        <v>6314</v>
+      </c>
+      <c r="E167">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>167</v>
+      </c>
+      <c r="B168">
+        <v>1</v>
+      </c>
+      <c r="C168">
+        <v>6315</v>
+      </c>
+      <c r="E168">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>168</v>
+      </c>
+      <c r="B169">
+        <v>101</v>
+      </c>
+      <c r="C169">
+        <v>6315</v>
+      </c>
+      <c r="E169">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>169</v>
+      </c>
+      <c r="B170">
+        <v>102</v>
+      </c>
+      <c r="C170">
+        <v>6315</v>
+      </c>
+      <c r="E170">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>170</v>
+      </c>
+      <c r="B171">
+        <v>103</v>
+      </c>
+      <c r="C171">
+        <v>6315</v>
+      </c>
+      <c r="E171">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>171</v>
+      </c>
+      <c r="B172">
+        <v>1</v>
+      </c>
+      <c r="C172">
+        <v>6316</v>
+      </c>
+      <c r="E172">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>172</v>
+      </c>
+      <c r="B173">
+        <v>101</v>
+      </c>
+      <c r="C173">
+        <v>6316</v>
+      </c>
+      <c r="E173">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>173</v>
+      </c>
+      <c r="B174">
+        <v>102</v>
+      </c>
+      <c r="C174">
+        <v>6316</v>
+      </c>
+      <c r="E174">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>174</v>
+      </c>
+      <c r="B175">
+        <v>103</v>
+      </c>
+      <c r="C175">
+        <v>6316</v>
+      </c>
+      <c r="E175">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>175</v>
+      </c>
+      <c r="B176">
+        <v>1</v>
+      </c>
+      <c r="C176">
+        <v>6317</v>
+      </c>
+      <c r="E176">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>176</v>
+      </c>
+      <c r="B177">
+        <v>101</v>
+      </c>
+      <c r="C177">
+        <v>6317</v>
+      </c>
+      <c r="E177">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>177</v>
+      </c>
+      <c r="B178">
+        <v>102</v>
+      </c>
+      <c r="C178">
+        <v>6317</v>
+      </c>
+      <c r="E178">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>178</v>
+      </c>
+      <c r="B179">
+        <v>103</v>
+      </c>
+      <c r="C179">
+        <v>6317</v>
+      </c>
+      <c r="E179">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>179</v>
+      </c>
+      <c r="B180">
+        <v>1</v>
+      </c>
+      <c r="C180">
+        <v>6318</v>
+      </c>
+      <c r="E180">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>180</v>
+      </c>
+      <c r="B181">
+        <v>101</v>
+      </c>
+      <c r="C181">
+        <v>6318</v>
+      </c>
+      <c r="E181">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>181</v>
+      </c>
+      <c r="B182">
+        <v>102</v>
+      </c>
+      <c r="C182">
+        <v>6318</v>
+      </c>
+      <c r="E182">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>182</v>
+      </c>
+      <c r="B183">
+        <v>103</v>
+      </c>
+      <c r="C183">
+        <v>6318</v>
+      </c>
+      <c r="E183">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>183</v>
+      </c>
+      <c r="B184">
+        <v>1</v>
+      </c>
+      <c r="C184">
+        <v>6319</v>
+      </c>
+      <c r="E184">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>184</v>
+      </c>
+      <c r="B185">
+        <v>101</v>
+      </c>
+      <c r="C185">
+        <v>6319</v>
+      </c>
+      <c r="E185">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>102</v>
+      </c>
+      <c r="C186">
+        <v>6319</v>
+      </c>
+      <c r="E186">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>103</v>
+      </c>
+      <c r="C187">
+        <v>6319</v>
+      </c>
+      <c r="E187">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>1</v>
+      </c>
+      <c r="C188">
+        <v>6320</v>
+      </c>
+      <c r="E188">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>101</v>
+      </c>
+      <c r="C189">
+        <v>6320</v>
+      </c>
+      <c r="E189">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>102</v>
+      </c>
+      <c r="C190">
+        <v>6320</v>
+      </c>
+      <c r="E190">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>103</v>
+      </c>
+      <c r="C191">
+        <v>6320</v>
+      </c>
+      <c r="E191">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>1</v>
+      </c>
+      <c r="C192">
+        <v>6321</v>
+      </c>
+      <c r="E192">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>101</v>
+      </c>
+      <c r="C193">
+        <v>6321</v>
+      </c>
+      <c r="E193">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>102</v>
+      </c>
+      <c r="C194">
+        <v>6321</v>
+      </c>
+      <c r="E194">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>103</v>
+      </c>
+      <c r="C195">
+        <v>6321</v>
+      </c>
+      <c r="E195">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>1</v>
+      </c>
+      <c r="C196">
+        <v>6322</v>
+      </c>
+      <c r="E196">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>101</v>
+      </c>
+      <c r="C197">
+        <v>6322</v>
+      </c>
+      <c r="E197">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>102</v>
+      </c>
+      <c r="C198">
+        <v>6322</v>
+      </c>
+      <c r="E198">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>1</v>
+      </c>
+      <c r="C199">
+        <v>6323</v>
+      </c>
+      <c r="E199">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>101</v>
+      </c>
+      <c r="C200">
+        <v>6323</v>
+      </c>
+      <c r="E200">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>102</v>
+      </c>
+      <c r="C201">
+        <v>6323</v>
+      </c>
+      <c r="E201">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>1</v>
+      </c>
+      <c r="C202">
+        <v>6324</v>
+      </c>
+      <c r="E202">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>101</v>
+      </c>
+      <c r="C203">
+        <v>6324</v>
+      </c>
+      <c r="E203">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>102</v>
+      </c>
+      <c r="C204">
+        <v>6324</v>
+      </c>
+      <c r="E204">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>1</v>
+      </c>
+      <c r="C205">
+        <v>6325</v>
+      </c>
+      <c r="E205">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>101</v>
+      </c>
+      <c r="C206">
+        <v>6325</v>
+      </c>
+      <c r="E206">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>102</v>
+      </c>
+      <c r="C207">
+        <v>6325</v>
+      </c>
+      <c r="E207">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>1</v>
+      </c>
+      <c r="C208">
+        <v>6326</v>
+      </c>
+      <c r="E208">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>101</v>
+      </c>
+      <c r="C209">
+        <v>6326</v>
+      </c>
+      <c r="E209">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>102</v>
+      </c>
+      <c r="C210">
+        <v>6326</v>
+      </c>
+      <c r="E210">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>1</v>
+      </c>
+      <c r="C211">
+        <v>6327</v>
+      </c>
+      <c r="E211">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>101</v>
+      </c>
+      <c r="C212">
+        <v>6327</v>
+      </c>
+      <c r="E212">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>102</v>
+      </c>
+      <c r="C213">
+        <v>6327</v>
+      </c>
+      <c r="E213">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>1</v>
+      </c>
+      <c r="C214">
+        <v>6328</v>
+      </c>
+      <c r="E214">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>101</v>
+      </c>
+      <c r="C215">
+        <v>6328</v>
+      </c>
+      <c r="E215">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>102</v>
+      </c>
+      <c r="C216">
+        <v>6328</v>
+      </c>
+      <c r="E216">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>1</v>
+      </c>
+      <c r="C217">
+        <v>6329</v>
+      </c>
+      <c r="E217">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>101</v>
+      </c>
+      <c r="C218">
+        <v>6329</v>
+      </c>
+      <c r="E218">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>102</v>
+      </c>
+      <c r="C219">
+        <v>6329</v>
+      </c>
+      <c r="E219">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>1</v>
+      </c>
+      <c r="C220">
+        <v>6330</v>
+      </c>
+      <c r="E220">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>101</v>
+      </c>
+      <c r="C221">
+        <v>6330</v>
+      </c>
+      <c r="E221">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>102</v>
+      </c>
+      <c r="C222">
+        <v>6330</v>
+      </c>
+      <c r="E222">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>1</v>
+      </c>
+      <c r="C223">
+        <v>6331</v>
+      </c>
+      <c r="E223">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>101</v>
+      </c>
+      <c r="C224">
+        <v>6331</v>
+      </c>
+      <c r="E224">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>102</v>
+      </c>
+      <c r="C225">
+        <v>6331</v>
+      </c>
+      <c r="E225">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>1</v>
+      </c>
+      <c r="C226">
+        <v>6332</v>
+      </c>
+      <c r="E226">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>101</v>
+      </c>
+      <c r="C227">
+        <v>6332</v>
+      </c>
+      <c r="E227">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>1</v>
+      </c>
+      <c r="C228">
+        <v>6333</v>
+      </c>
+      <c r="E228">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>101</v>
+      </c>
+      <c r="C229">
+        <v>6333</v>
+      </c>
+      <c r="E229">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>1</v>
+      </c>
+      <c r="C230">
+        <v>6334</v>
+      </c>
+      <c r="E230">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>101</v>
+      </c>
+      <c r="C231">
+        <v>6334</v>
+      </c>
+      <c r="E231">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>1</v>
+      </c>
+      <c r="C232">
+        <v>6335</v>
+      </c>
+      <c r="E232">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>101</v>
+      </c>
+      <c r="C233">
+        <v>6335</v>
+      </c>
+      <c r="E233">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>1</v>
+      </c>
+      <c r="C234">
+        <v>6336</v>
+      </c>
+      <c r="E234">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>101</v>
+      </c>
+      <c r="C235">
+        <v>6336</v>
+      </c>
+      <c r="E235">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>1</v>
+      </c>
+      <c r="C236">
+        <v>8507</v>
+      </c>
+      <c r="E236">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>101</v>
+      </c>
+      <c r="C237">
+        <v>8507</v>
+      </c>
+      <c r="E237">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>1</v>
+      </c>
+      <c r="C238">
+        <v>6338</v>
+      </c>
+      <c r="E238">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>101</v>
+      </c>
+      <c r="C239">
+        <v>6338</v>
+      </c>
+      <c r="E239">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>1</v>
+      </c>
+      <c r="C240">
+        <v>6339</v>
+      </c>
+      <c r="E240">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>101</v>
+      </c>
+      <c r="C241">
+        <v>6339</v>
+      </c>
+      <c r="E241">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A242">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>1</v>
+      </c>
+      <c r="C242">
+        <v>6340</v>
+      </c>
+      <c r="E242">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>101</v>
+      </c>
+      <c r="C243">
+        <v>6340</v>
+      </c>
+      <c r="E243">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>1</v>
+      </c>
+      <c r="C244">
+        <v>6341</v>
+      </c>
+      <c r="E244">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A245">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>101</v>
+      </c>
+      <c r="C245">
+        <v>6341</v>
+      </c>
+      <c r="E245">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A246">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>1</v>
+      </c>
+      <c r="C246">
+        <v>9115</v>
+      </c>
+      <c r="E246">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A247">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>101</v>
+      </c>
+      <c r="C247">
+        <v>9115</v>
+      </c>
+      <c r="E247">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A248">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>102</v>
+      </c>
+      <c r="C248">
+        <v>9115</v>
+      </c>
+      <c r="E248">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A249">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>103</v>
+      </c>
+      <c r="C249">
+        <v>6115</v>
+      </c>
+      <c r="E249">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A250">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>1</v>
+      </c>
+      <c r="C250">
+        <v>9116</v>
+      </c>
+      <c r="E250">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A251">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>101</v>
+      </c>
+      <c r="C251">
+        <v>9116</v>
+      </c>
+      <c r="E251">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A252">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>102</v>
+      </c>
+      <c r="C252">
+        <v>9116</v>
+      </c>
+      <c r="E252">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A253">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>1</v>
+      </c>
+      <c r="C253">
+        <v>9117</v>
+      </c>
+      <c r="E253">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>101</v>
+      </c>
+      <c r="C254">
+        <v>9117</v>
+      </c>
+      <c r="E254">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A255">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>102</v>
+      </c>
+      <c r="C255">
+        <v>9117</v>
+      </c>
+      <c r="E255">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A256">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>103</v>
+      </c>
+      <c r="C256">
+        <v>9117</v>
+      </c>
+      <c r="E256">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A257">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>80</v>
+      </c>
+      <c r="C257">
+        <v>9117</v>
+      </c>
+      <c r="E257">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A258">
+        <v>257</v>
+      </c>
+      <c r="B258">
+        <v>801</v>
+      </c>
+      <c r="C258">
+        <v>9117</v>
+      </c>
+      <c r="E258">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A259">
+        <v>258</v>
+      </c>
+      <c r="B259">
+        <v>1</v>
+      </c>
+      <c r="C259">
+        <v>9118</v>
+      </c>
+      <c r="E259">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A260">
+        <v>259</v>
+      </c>
+      <c r="B260">
+        <v>101</v>
+      </c>
+      <c r="C260">
+        <v>9118</v>
+      </c>
+      <c r="E260">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A261">
+        <v>260</v>
+      </c>
+      <c r="B261">
+        <v>102</v>
+      </c>
+      <c r="C261">
+        <v>9118</v>
+      </c>
+      <c r="E261">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A262">
+        <v>261</v>
+      </c>
+      <c r="B262">
+        <v>1</v>
+      </c>
+      <c r="C262">
+        <v>9119</v>
+      </c>
+      <c r="E262">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A263">
+        <v>262</v>
+      </c>
+      <c r="B263">
+        <v>101</v>
+      </c>
+      <c r="C263">
+        <v>9119</v>
+      </c>
+      <c r="E263">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A264">
+        <v>263</v>
+      </c>
+      <c r="B264">
+        <v>102</v>
+      </c>
+      <c r="C264">
+        <v>9119</v>
+      </c>
+      <c r="E264">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A265">
+        <v>264</v>
+      </c>
+      <c r="B265">
+        <v>1</v>
+      </c>
+      <c r="C265">
+        <v>9120</v>
+      </c>
+      <c r="E265">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A266">
+        <v>265</v>
+      </c>
+      <c r="B266">
+        <v>101</v>
+      </c>
+      <c r="C266">
+        <v>9120</v>
+      </c>
+      <c r="E266">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A267">
+        <v>266</v>
+      </c>
+      <c r="B267">
+        <v>102</v>
+      </c>
+      <c r="C267">
+        <v>9120</v>
+      </c>
+      <c r="E267">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A268">
+        <v>267</v>
+      </c>
+      <c r="B268">
+        <v>103</v>
+      </c>
+      <c r="C268">
+        <v>9120</v>
+      </c>
+      <c r="E268">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A269">
+        <v>268</v>
+      </c>
+      <c r="B269">
+        <v>1</v>
+      </c>
+      <c r="C269">
+        <v>9121</v>
+      </c>
+      <c r="E269">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A270">
+        <v>269</v>
+      </c>
+      <c r="B270">
+        <v>101</v>
+      </c>
+      <c r="C270">
+        <v>9121</v>
+      </c>
+      <c r="E270">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A271">
+        <v>270</v>
+      </c>
+      <c r="B271">
+        <v>102</v>
+      </c>
+      <c r="C271">
+        <v>9121</v>
+      </c>
+      <c r="E271">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A272">
+        <v>271</v>
+      </c>
+      <c r="B272">
+        <v>103</v>
+      </c>
+      <c r="C272">
+        <v>9121</v>
+      </c>
+      <c r="E272">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A273">
+        <v>272</v>
+      </c>
+      <c r="B273">
+        <v>1</v>
+      </c>
+      <c r="C273">
+        <v>9122</v>
+      </c>
+      <c r="E273">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A274">
+        <v>273</v>
+      </c>
+      <c r="B274">
+        <v>101</v>
+      </c>
+      <c r="C274">
+        <v>9122</v>
+      </c>
+      <c r="E274">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A275">
+        <v>274</v>
+      </c>
+      <c r="B275">
+        <v>102</v>
+      </c>
+      <c r="C275">
+        <v>9122</v>
+      </c>
+      <c r="E275">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A276">
+        <v>275</v>
+      </c>
+      <c r="B276">
+        <v>103</v>
+      </c>
+      <c r="C276">
+        <v>9122</v>
+      </c>
+      <c r="E276">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A277">
+        <v>276</v>
+      </c>
+      <c r="B277">
+        <v>1</v>
+      </c>
+      <c r="C277">
+        <v>9123</v>
+      </c>
+      <c r="E277">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A278">
+        <v>277</v>
+      </c>
+      <c r="B278">
+        <v>101</v>
+      </c>
+      <c r="C278">
+        <v>9123</v>
+      </c>
+      <c r="E278">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A279">
+        <v>278</v>
+      </c>
+      <c r="B279">
+        <v>102</v>
+      </c>
+      <c r="C279">
+        <v>9123</v>
+      </c>
+      <c r="E279">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A280">
+        <v>279</v>
+      </c>
+      <c r="B280">
+        <v>103</v>
+      </c>
+      <c r="C280">
+        <v>9123</v>
+      </c>
+      <c r="E280">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A281">
+        <v>280</v>
+      </c>
+      <c r="B281">
+        <v>1</v>
+      </c>
+      <c r="C281">
+        <v>9124</v>
+      </c>
+      <c r="E281">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A282">
+        <v>281</v>
+      </c>
+      <c r="B282">
+        <v>101</v>
+      </c>
+      <c r="C282">
+        <v>9124</v>
+      </c>
+      <c r="E282">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A283">
+        <v>282</v>
+      </c>
+      <c r="B283">
+        <v>102</v>
+      </c>
+      <c r="C283">
+        <v>9124</v>
+      </c>
+      <c r="E283">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A284">
+        <v>283</v>
+      </c>
+      <c r="B284">
+        <v>80</v>
+      </c>
+      <c r="C284">
+        <v>9124</v>
+      </c>
+      <c r="E284">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A285">
+        <v>284</v>
+      </c>
+      <c r="B285">
+        <v>801</v>
+      </c>
+      <c r="C285">
+        <v>9124</v>
+      </c>
+      <c r="E285">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A286">
+        <v>285</v>
+      </c>
+      <c r="B286">
+        <v>1</v>
+      </c>
+      <c r="C286">
+        <v>9125</v>
+      </c>
+      <c r="E286">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A287">
+        <v>286</v>
+      </c>
+      <c r="B287">
+        <v>101</v>
+      </c>
+      <c r="C287">
+        <v>9125</v>
+      </c>
+      <c r="E287">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A288">
+        <v>287</v>
+      </c>
+      <c r="B288">
+        <v>80</v>
+      </c>
+      <c r="C288">
+        <v>9125</v>
+      </c>
+      <c r="E288">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A289">
+        <v>288</v>
+      </c>
+      <c r="B289">
+        <v>801</v>
+      </c>
+      <c r="C289">
+        <v>9125</v>
+      </c>
+      <c r="E289">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A290">
+        <v>289</v>
+      </c>
+      <c r="B290">
+        <v>1</v>
+      </c>
+      <c r="C290">
+        <v>9126</v>
+      </c>
+      <c r="E290">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A291">
+        <v>290</v>
+      </c>
+      <c r="B291">
+        <v>101</v>
+      </c>
+      <c r="C291">
+        <v>9126</v>
+      </c>
+      <c r="E291">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A292">
+        <v>291</v>
+      </c>
+      <c r="B292">
+        <v>102</v>
+      </c>
+      <c r="C292">
+        <v>9126</v>
+      </c>
+      <c r="E292">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A293">
+        <v>292</v>
+      </c>
+      <c r="B293">
+        <v>1</v>
+      </c>
+      <c r="C293">
+        <v>9127</v>
+      </c>
+      <c r="E293">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A294">
+        <v>293</v>
+      </c>
+      <c r="B294">
+        <v>101</v>
+      </c>
+      <c r="C294">
+        <v>9127</v>
+      </c>
+      <c r="E294">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A295">
+        <v>294</v>
+      </c>
+      <c r="B295">
+        <v>80</v>
+      </c>
+      <c r="C295">
+        <v>9127</v>
+      </c>
+      <c r="E295">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A296">
+        <v>295</v>
+      </c>
+      <c r="B296">
+        <v>801</v>
+      </c>
+      <c r="C296">
+        <v>9127</v>
+      </c>
+      <c r="E296">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A297">
+        <v>296</v>
+      </c>
+      <c r="B297">
+        <v>1</v>
+      </c>
+      <c r="C297">
+        <v>9128</v>
+      </c>
+      <c r="E297">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A298">
+        <v>297</v>
+      </c>
+      <c r="B298">
+        <v>101</v>
+      </c>
+      <c r="C298">
+        <v>9128</v>
+      </c>
+      <c r="E298">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A299">
+        <v>298</v>
+      </c>
+      <c r="B299">
+        <v>102</v>
+      </c>
+      <c r="C299">
+        <v>9128</v>
+      </c>
+      <c r="E299">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A300">
+        <v>299</v>
+      </c>
+      <c r="B300">
+        <v>80</v>
+      </c>
+      <c r="C300">
+        <v>9128</v>
+      </c>
+      <c r="E300">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A301">
+        <v>300</v>
+      </c>
+      <c r="B301">
+        <v>801</v>
+      </c>
+      <c r="C301">
+        <v>9128</v>
+      </c>
+      <c r="E301">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A302">
+        <v>301</v>
+      </c>
+      <c r="B302">
+        <v>1</v>
+      </c>
+      <c r="C302">
+        <v>9129</v>
+      </c>
+      <c r="E302">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A303">
+        <v>302</v>
+      </c>
+      <c r="B303">
+        <v>101</v>
+      </c>
+      <c r="C303">
+        <v>9129</v>
+      </c>
+      <c r="E303">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A304">
+        <v>303</v>
+      </c>
+      <c r="B304">
+        <v>102</v>
+      </c>
+      <c r="C304">
+        <v>9129</v>
+      </c>
+      <c r="E304">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A305">
+        <v>304</v>
+      </c>
+      <c r="B305">
+        <v>80</v>
+      </c>
+      <c r="C305">
+        <v>9129</v>
+      </c>
+      <c r="E305">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A306">
+        <v>305</v>
+      </c>
+      <c r="B306">
+        <v>801</v>
+      </c>
+      <c r="C306">
+        <v>9129</v>
+      </c>
+      <c r="E306">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A307">
+        <v>306</v>
+      </c>
+      <c r="B307">
+        <v>1</v>
+      </c>
+      <c r="C307">
+        <v>9130</v>
+      </c>
+      <c r="E307">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A308">
+        <v>307</v>
+      </c>
+      <c r="B308">
+        <v>101</v>
+      </c>
+      <c r="C308">
+        <v>9130</v>
+      </c>
+      <c r="E308">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A309">
+        <v>308</v>
+      </c>
+      <c r="B309">
+        <v>102</v>
+      </c>
+      <c r="C309">
+        <v>9130</v>
+      </c>
+      <c r="E309">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A310">
+        <v>309</v>
+      </c>
+      <c r="B310">
+        <v>1</v>
+      </c>
+      <c r="C310">
+        <v>9131</v>
+      </c>
+      <c r="E310">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A311">
+        <v>310</v>
+      </c>
+      <c r="B311">
+        <v>101</v>
+      </c>
+      <c r="C311">
+        <v>9131</v>
+      </c>
+      <c r="E311">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A312">
+        <v>311</v>
+      </c>
+      <c r="B312">
+        <v>102</v>
+      </c>
+      <c r="C312">
+        <v>9131</v>
+      </c>
+      <c r="E312">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A313">
+        <v>312</v>
+      </c>
+      <c r="B313">
+        <v>1</v>
+      </c>
+      <c r="C313">
+        <v>9132</v>
+      </c>
+      <c r="E313">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A314">
+        <v>313</v>
+      </c>
+      <c r="B314">
+        <v>102</v>
+      </c>
+      <c r="C314">
+        <v>9132</v>
+      </c>
+      <c r="E314">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A315">
+        <v>314</v>
+      </c>
+      <c r="B315">
+        <v>102</v>
+      </c>
+      <c r="C315">
+        <v>9132</v>
+      </c>
+      <c r="E315">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A316">
+        <v>315</v>
+      </c>
+      <c r="B316">
+        <v>80</v>
+      </c>
+      <c r="C316">
+        <v>9132</v>
+      </c>
+      <c r="E316">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A317">
+        <v>316</v>
+      </c>
+      <c r="B317">
+        <v>801</v>
+      </c>
+      <c r="C317">
+        <v>9132</v>
+      </c>
+      <c r="E317">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A318">
+        <v>317</v>
+      </c>
+      <c r="B318">
+        <v>1</v>
+      </c>
+      <c r="C318">
+        <v>9133</v>
+      </c>
+      <c r="E318">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A319">
+        <v>318</v>
+      </c>
+      <c r="B319">
+        <v>101</v>
+      </c>
+      <c r="C319">
+        <v>9133</v>
+      </c>
+      <c r="E319">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A320">
+        <v>319</v>
+      </c>
+      <c r="B320">
+        <v>102</v>
+      </c>
+      <c r="C320">
+        <v>9133</v>
+      </c>
+      <c r="E320">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A321">
+        <v>320</v>
+      </c>
+      <c r="B321">
+        <v>1</v>
+      </c>
+      <c r="C321">
+        <v>9134</v>
+      </c>
+      <c r="E321">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A322">
+        <v>321</v>
+      </c>
+      <c r="B322">
+        <v>101</v>
+      </c>
+      <c r="C322">
+        <v>9134</v>
+      </c>
+      <c r="E322">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A323">
+        <v>322</v>
+      </c>
+      <c r="B323">
+        <v>102</v>
+      </c>
+      <c r="C323">
+        <v>9134</v>
+      </c>
+      <c r="E323">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A324">
+        <v>323</v>
+      </c>
+      <c r="B324">
+        <v>1</v>
+      </c>
+      <c r="C324">
+        <v>9135</v>
+      </c>
+      <c r="E324">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A325">
+        <v>324</v>
+      </c>
+      <c r="B325">
+        <v>101</v>
+      </c>
+      <c r="C325">
+        <v>9135</v>
+      </c>
+      <c r="E325">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A326">
+        <v>325</v>
+      </c>
+      <c r="B326">
+        <v>102</v>
+      </c>
+      <c r="C326">
+        <v>9135</v>
+      </c>
+      <c r="E326">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A327">
+        <v>326</v>
+      </c>
+      <c r="B327">
+        <v>80</v>
+      </c>
+      <c r="C327">
+        <v>9135</v>
+      </c>
+      <c r="E327">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A328">
+        <v>327</v>
+      </c>
+      <c r="B328">
+        <v>801</v>
+      </c>
+      <c r="C328">
+        <v>9135</v>
+      </c>
+      <c r="E328">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A329">
+        <v>328</v>
+      </c>
+      <c r="B329">
+        <v>1</v>
+      </c>
+      <c r="C329">
+        <v>9136</v>
+      </c>
+      <c r="E329">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A330">
+        <v>329</v>
+      </c>
+      <c r="B330">
+        <v>101</v>
+      </c>
+      <c r="C330">
+        <v>9136</v>
+      </c>
+      <c r="E330">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A331">
+        <v>330</v>
+      </c>
+      <c r="B331">
+        <v>102</v>
+      </c>
+      <c r="C331">
+        <v>9136</v>
+      </c>
+      <c r="E331">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A332">
+        <v>331</v>
+      </c>
+      <c r="B332">
+        <v>80</v>
+      </c>
+      <c r="C332">
+        <v>9136</v>
+      </c>
+      <c r="E332">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A333">
+        <v>332</v>
+      </c>
+      <c r="B333">
+        <v>801</v>
+      </c>
+      <c r="C333">
+        <v>9136</v>
+      </c>
+      <c r="E333">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A334">
+        <v>333</v>
+      </c>
+      <c r="B334">
+        <v>1</v>
+      </c>
+      <c r="C334">
+        <v>9137</v>
+      </c>
+      <c r="E334">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A335">
+        <v>334</v>
+      </c>
+      <c r="B335">
+        <v>101</v>
+      </c>
+      <c r="C335">
+        <v>9137</v>
+      </c>
+      <c r="E335">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A336">
+        <v>335</v>
+      </c>
+      <c r="B336">
+        <v>102</v>
+      </c>
+      <c r="C336">
+        <v>9137</v>
+      </c>
+      <c r="E336">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A337">
+        <v>336</v>
+      </c>
+      <c r="B337">
+        <v>1</v>
+      </c>
+      <c r="C337">
+        <v>9138</v>
+      </c>
+      <c r="E337">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A338">
+        <v>337</v>
+      </c>
+      <c r="B338">
+        <v>101</v>
+      </c>
+      <c r="C338">
+        <v>9138</v>
+      </c>
+      <c r="E338">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A339">
+        <v>338</v>
+      </c>
+      <c r="B339">
+        <v>102</v>
+      </c>
+      <c r="C339">
+        <v>9138</v>
+      </c>
+      <c r="E339">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A340">
+        <v>339</v>
+      </c>
+      <c r="B340">
+        <v>1</v>
+      </c>
+      <c r="C340">
+        <v>9139</v>
+      </c>
+      <c r="E340">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A341">
+        <v>340</v>
+      </c>
+      <c r="B341">
+        <v>101</v>
+      </c>
+      <c r="C341">
+        <v>9139</v>
+      </c>
+      <c r="E341">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A342">
+        <v>341</v>
+      </c>
+      <c r="B342">
+        <v>102</v>
+      </c>
+      <c r="C342">
+        <v>9139</v>
+      </c>
+      <c r="E342">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A343">
+        <v>342</v>
+      </c>
+      <c r="B343">
+        <v>1</v>
+      </c>
+      <c r="C343">
+        <v>9140</v>
+      </c>
+      <c r="E343">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A344">
+        <v>343</v>
+      </c>
+      <c r="B344">
+        <v>101</v>
+      </c>
+      <c r="C344">
+        <v>9140</v>
+      </c>
+      <c r="E344">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A345">
+        <v>344</v>
+      </c>
+      <c r="B345">
+        <v>102</v>
+      </c>
+      <c r="C345">
+        <v>9140</v>
+      </c>
+      <c r="E345">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A346">
+        <v>345</v>
+      </c>
+      <c r="B346">
+        <v>1</v>
+      </c>
+      <c r="C346">
+        <v>9141</v>
+      </c>
+      <c r="E346">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A347">
+        <v>346</v>
+      </c>
+      <c r="B347">
+        <v>101</v>
+      </c>
+      <c r="C347">
+        <v>9141</v>
+      </c>
+      <c r="E347">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A348">
+        <v>347</v>
+      </c>
+      <c r="B348">
+        <v>102</v>
+      </c>
+      <c r="C348">
+        <v>9141</v>
+      </c>
+      <c r="E348">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A349">
+        <v>348</v>
+      </c>
+      <c r="B349">
+        <v>80</v>
+      </c>
+      <c r="C349">
+        <v>9141</v>
+      </c>
+      <c r="E349">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A350">
+        <v>349</v>
+      </c>
+      <c r="B350">
+        <v>801</v>
+      </c>
+      <c r="C350">
+        <v>9141</v>
+      </c>
+      <c r="E350">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A351">
+        <v>350</v>
+      </c>
+      <c r="B351">
+        <v>1</v>
+      </c>
+      <c r="C351">
+        <v>9142</v>
+      </c>
+      <c r="E351">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A352">
+        <v>351</v>
+      </c>
+      <c r="B352">
+        <v>101</v>
+      </c>
+      <c r="C352">
+        <v>9142</v>
+      </c>
+      <c r="E352">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A353">
+        <v>352</v>
+      </c>
+      <c r="B353">
+        <v>102</v>
+      </c>
+      <c r="C353">
+        <v>9142</v>
+      </c>
+      <c r="E353">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A354">
+        <v>353</v>
+      </c>
+      <c r="B354">
+        <v>80</v>
+      </c>
+      <c r="C354">
+        <v>9142</v>
+      </c>
+      <c r="E354">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A355">
+        <v>354</v>
+      </c>
+      <c r="B355">
+        <v>801</v>
+      </c>
+      <c r="C355">
+        <v>9142</v>
+      </c>
+      <c r="E355">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A356">
+        <v>355</v>
+      </c>
+      <c r="B356">
+        <v>1</v>
+      </c>
+      <c r="C356">
+        <v>9143</v>
+      </c>
+      <c r="E356">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A357">
+        <v>356</v>
+      </c>
+      <c r="B357">
+        <v>101</v>
+      </c>
+      <c r="C357">
+        <v>9143</v>
+      </c>
+      <c r="E357">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A358">
+        <v>357</v>
+      </c>
+      <c r="B358">
+        <v>102</v>
+      </c>
+      <c r="C358">
+        <v>9143</v>
+      </c>
+      <c r="E358">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A359">
+        <v>358</v>
+      </c>
+      <c r="B359">
+        <v>80</v>
+      </c>
+      <c r="C359">
+        <v>9143</v>
+      </c>
+      <c r="E359">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A360">
+        <v>359</v>
+      </c>
+      <c r="B360">
+        <v>801</v>
+      </c>
+      <c r="C360">
+        <v>9143</v>
+      </c>
+      <c r="E360">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A361">
+        <v>360</v>
+      </c>
+      <c r="B361">
+        <v>1</v>
+      </c>
+      <c r="C361">
+        <v>9144</v>
+      </c>
+      <c r="E361">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A362">
+        <v>361</v>
+      </c>
+      <c r="B362">
+        <v>101</v>
+      </c>
+      <c r="C362">
+        <v>9144</v>
+      </c>
+      <c r="E362">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A363">
+        <v>362</v>
+      </c>
+      <c r="B363">
+        <v>102</v>
+      </c>
+      <c r="C363">
+        <v>9144</v>
+      </c>
+      <c r="E363">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A364">
+        <v>363</v>
+      </c>
+      <c r="B364">
+        <v>1</v>
+      </c>
+      <c r="C364">
+        <v>9145</v>
+      </c>
+      <c r="E364">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A365">
+        <v>364</v>
+      </c>
+      <c r="B365">
+        <v>101</v>
+      </c>
+      <c r="C365">
+        <v>9145</v>
+      </c>
+      <c r="E365">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A366">
+        <v>365</v>
+      </c>
+      <c r="B366">
+        <v>1</v>
+      </c>
+      <c r="C366">
+        <v>9146</v>
+      </c>
+      <c r="E366">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A367">
+        <v>366</v>
+      </c>
+      <c r="B367">
+        <v>101</v>
+      </c>
+      <c r="C367">
+        <v>9146</v>
+      </c>
+      <c r="E367">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A368">
+        <v>367</v>
+      </c>
+      <c r="B368">
+        <v>1</v>
+      </c>
+      <c r="C368">
+        <v>9147</v>
+      </c>
+      <c r="E368">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A369">
+        <v>368</v>
+      </c>
+      <c r="B369">
+        <v>101</v>
+      </c>
+      <c r="C369">
+        <v>9147</v>
+      </c>
+      <c r="E369">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A370">
+        <v>369</v>
+      </c>
+      <c r="B370">
+        <v>1</v>
+      </c>
+      <c r="C370">
+        <v>9148</v>
+      </c>
+      <c r="E370">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A371">
+        <v>370</v>
+      </c>
+      <c r="B371">
+        <v>101</v>
+      </c>
+      <c r="C371">
+        <v>9148</v>
+      </c>
+      <c r="E371">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A372">
+        <v>371</v>
+      </c>
+      <c r="B372">
+        <v>80</v>
+      </c>
+      <c r="C372">
+        <v>9148</v>
+      </c>
+      <c r="E372">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A373">
+        <v>372</v>
+      </c>
+      <c r="B373">
+        <v>801</v>
+      </c>
+      <c r="C373">
+        <v>9148</v>
+      </c>
+      <c r="E373">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A374">
+        <v>373</v>
+      </c>
+      <c r="B374">
+        <v>1</v>
+      </c>
+      <c r="C374">
+        <v>9149</v>
+      </c>
+      <c r="E374">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A375">
+        <v>374</v>
+      </c>
+      <c r="B375">
+        <v>101</v>
+      </c>
+      <c r="C375">
+        <v>9149</v>
+      </c>
+      <c r="E375">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A376">
+        <v>375</v>
+      </c>
+      <c r="B376">
+        <v>1</v>
+      </c>
+      <c r="C376">
+        <v>9151</v>
+      </c>
+      <c r="E376">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A377">
+        <v>376</v>
+      </c>
+      <c r="B377">
+        <v>101</v>
+      </c>
+      <c r="C377">
+        <v>9151</v>
+      </c>
+      <c r="E377">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A378">
+        <v>377</v>
+      </c>
+      <c r="B378">
+        <v>80</v>
+      </c>
+      <c r="C378">
+        <v>9151</v>
+      </c>
+      <c r="E378">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A379">
+        <v>378</v>
+      </c>
+      <c r="B379">
+        <v>801</v>
+      </c>
+      <c r="C379">
+        <v>9151</v>
+      </c>
+      <c r="E379">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A380">
+        <v>379</v>
+      </c>
+      <c r="B380">
+        <v>1</v>
+      </c>
+      <c r="C380">
+        <v>9152</v>
+      </c>
+      <c r="E380">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A381">
+        <v>380</v>
+      </c>
+      <c r="B381">
+        <v>101</v>
+      </c>
+      <c r="C381">
+        <v>9152</v>
+      </c>
+      <c r="E381">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A382">
+        <v>381</v>
+      </c>
+      <c r="B382">
+        <v>80</v>
+      </c>
+      <c r="C382">
+        <v>9153</v>
+      </c>
+      <c r="E382">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A383">
+        <v>382</v>
+      </c>
+      <c r="B383">
+        <v>801</v>
+      </c>
+      <c r="C383">
+        <v>9153</v>
+      </c>
+      <c r="E383">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A384">
+        <v>383</v>
+      </c>
+      <c r="B384">
+        <v>1</v>
+      </c>
+      <c r="C384">
+        <v>7711</v>
+      </c>
+      <c r="E384">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A385">
+        <v>384</v>
+      </c>
+      <c r="B385">
+        <v>101</v>
+      </c>
+      <c r="C385">
+        <v>7711</v>
+      </c>
+      <c r="E385">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A386">
+        <v>385</v>
+      </c>
+      <c r="B386">
+        <v>1</v>
+      </c>
+      <c r="C386">
+        <v>7712</v>
+      </c>
+      <c r="E386">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A387">
+        <v>386</v>
+      </c>
+      <c r="B387">
+        <v>101</v>
+      </c>
+      <c r="C387">
+        <v>7712</v>
+      </c>
+      <c r="E387">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A388">
+        <v>387</v>
+      </c>
+      <c r="B388">
+        <v>1</v>
+      </c>
+      <c r="C388">
+        <v>7713</v>
+      </c>
+      <c r="E388">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A389">
+        <v>388</v>
+      </c>
+      <c r="B389">
+        <v>101</v>
+      </c>
+      <c r="C389">
+        <v>7713</v>
+      </c>
+      <c r="E389">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A390">
+        <v>389</v>
+      </c>
+      <c r="B390">
+        <v>1</v>
+      </c>
+      <c r="C390">
+        <v>7714</v>
+      </c>
+      <c r="E390">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A391">
+        <v>390</v>
+      </c>
+      <c r="B391">
+        <v>101</v>
+      </c>
+      <c r="C391">
+        <v>7714</v>
+      </c>
+      <c r="E391">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A392">
+        <v>391</v>
+      </c>
+      <c r="B392">
+        <v>1</v>
+      </c>
+      <c r="C392">
+        <v>7715</v>
+      </c>
+      <c r="E392">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A393">
+        <v>392</v>
+      </c>
+      <c r="B393">
+        <v>101</v>
+      </c>
+      <c r="C393">
+        <v>7715</v>
+      </c>
+      <c r="E393">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A394">
+        <v>393</v>
+      </c>
+      <c r="B394">
+        <v>1</v>
+      </c>
+      <c r="C394">
+        <v>7716</v>
+      </c>
+      <c r="E394">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A395">
+        <v>394</v>
+      </c>
+      <c r="B395">
+        <v>101</v>
+      </c>
+      <c r="C395">
+        <v>7716</v>
+      </c>
+      <c r="E395">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A396">
+        <v>395</v>
+      </c>
+      <c r="B396">
+        <v>1</v>
+      </c>
+      <c r="C396">
+        <v>7717</v>
+      </c>
+      <c r="E396">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A397">
+        <v>396</v>
+      </c>
+      <c r="B397">
+        <v>101</v>
+      </c>
+      <c r="C397">
+        <v>7717</v>
+      </c>
+      <c r="E397">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A398">
+        <v>397</v>
+      </c>
+      <c r="B398">
+        <v>1</v>
+      </c>
+      <c r="C398">
+        <v>7718</v>
+      </c>
+      <c r="E398">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A399">
+        <v>398</v>
+      </c>
+      <c r="B399">
+        <v>101</v>
+      </c>
+      <c r="C399">
+        <v>7718</v>
+      </c>
+      <c r="E399">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A400">
+        <v>399</v>
+      </c>
+      <c r="B400">
+        <v>1</v>
+      </c>
+      <c r="C400">
+        <v>7719</v>
+      </c>
+      <c r="E400">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A401">
+        <v>400</v>
+      </c>
+      <c r="B401">
+        <v>101</v>
+      </c>
+      <c r="C401">
+        <v>7719</v>
+      </c>
+      <c r="E401">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A402">
+        <v>401</v>
+      </c>
+      <c r="B402">
+        <v>1</v>
+      </c>
+      <c r="C402">
+        <v>7720</v>
+      </c>
+      <c r="E402">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A403">
+        <v>402</v>
+      </c>
+      <c r="B403">
+        <v>101</v>
+      </c>
+      <c r="C403">
+        <v>7720</v>
+      </c>
+      <c r="E403">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A404">
+        <v>403</v>
+      </c>
+      <c r="B404">
+        <v>1</v>
+      </c>
+      <c r="C404">
+        <v>7721</v>
+      </c>
+      <c r="E404">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A405">
+        <v>404</v>
+      </c>
+      <c r="B405">
+        <v>101</v>
+      </c>
+      <c r="C405">
+        <v>7721</v>
+      </c>
+      <c r="E405">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A406">
+        <v>405</v>
+      </c>
+      <c r="B406">
+        <v>1</v>
+      </c>
+      <c r="C406">
+        <v>7722</v>
+      </c>
+      <c r="E406">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A407">
+        <v>406</v>
+      </c>
+      <c r="B407">
+        <v>101</v>
+      </c>
+      <c r="C407">
+        <v>7722</v>
+      </c>
+      <c r="E407">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A408">
+        <v>407</v>
+      </c>
+      <c r="B408">
+        <v>1</v>
+      </c>
+      <c r="C408">
+        <v>7723</v>
+      </c>
+      <c r="E408">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A409">
+        <v>408</v>
+      </c>
+      <c r="B409">
+        <v>101</v>
+      </c>
+      <c r="C409">
+        <v>7723</v>
+      </c>
+      <c r="E409">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A410">
+        <v>409</v>
+      </c>
+      <c r="B410">
+        <v>1</v>
+      </c>
+      <c r="C410">
+        <v>7724</v>
+      </c>
+      <c r="E410">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A411">
+        <v>410</v>
+      </c>
+      <c r="B411">
+        <v>101</v>
+      </c>
+      <c r="C411">
+        <v>7724</v>
+      </c>
+      <c r="E411">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A412">
+        <v>411</v>
+      </c>
+      <c r="B412">
+        <v>1</v>
+      </c>
+      <c r="C412">
+        <v>7725</v>
+      </c>
+      <c r="E412">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A413">
+        <v>412</v>
+      </c>
+      <c r="B413">
+        <v>101</v>
+      </c>
+      <c r="C413">
+        <v>7725</v>
+      </c>
+      <c r="E413">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A414">
+        <v>413</v>
+      </c>
+      <c r="B414">
+        <v>1</v>
+      </c>
+      <c r="C414">
+        <v>7726</v>
+      </c>
+      <c r="E414">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A415">
+        <v>414</v>
+      </c>
+      <c r="B415">
+        <v>101</v>
+      </c>
+      <c r="C415">
+        <v>7726</v>
+      </c>
+      <c r="E415">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A416">
+        <v>415</v>
+      </c>
+      <c r="B416">
+        <v>1</v>
+      </c>
+      <c r="C416">
+        <v>7727</v>
+      </c>
+      <c r="E416">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A417">
+        <v>416</v>
+      </c>
+      <c r="B417">
+        <v>101</v>
+      </c>
+      <c r="C417">
+        <v>7727</v>
+      </c>
+      <c r="E417">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A418">
+        <v>417</v>
+      </c>
+      <c r="B418">
+        <v>1</v>
+      </c>
+      <c r="C418">
+        <v>7728</v>
+      </c>
+      <c r="E418">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A419">
+        <v>418</v>
+      </c>
+      <c r="B419">
+        <v>101</v>
+      </c>
+      <c r="C419">
+        <v>7728</v>
+      </c>
+      <c r="E419">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A420">
+        <v>419</v>
+      </c>
+      <c r="B420">
+        <v>1</v>
+      </c>
+      <c r="C420">
+        <v>7729</v>
+      </c>
+      <c r="E420">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A421">
+        <v>420</v>
+      </c>
+      <c r="B421">
+        <v>101</v>
+      </c>
+      <c r="C421">
+        <v>7729</v>
+      </c>
+      <c r="E421">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A422">
+        <v>421</v>
+      </c>
+      <c r="B422">
+        <v>1</v>
+      </c>
+      <c r="C422">
+        <v>7730</v>
+      </c>
+      <c r="E422">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A423">
+        <v>422</v>
+      </c>
+      <c r="B423">
+        <v>101</v>
+      </c>
+      <c r="C423">
+        <v>7730</v>
+      </c>
+      <c r="E423">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A424">
+        <v>423</v>
+      </c>
+      <c r="B424">
+        <v>1</v>
+      </c>
+      <c r="C424">
+        <v>7731</v>
+      </c>
+      <c r="E424">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A425">
+        <v>424</v>
+      </c>
+      <c r="B425">
+        <v>101</v>
+      </c>
+      <c r="C425">
+        <v>7731</v>
+      </c>
+      <c r="E425">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A426">
+        <v>425</v>
+      </c>
+      <c r="B426">
+        <v>1</v>
+      </c>
+      <c r="C426">
+        <v>7732</v>
+      </c>
+      <c r="E426">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A427">
+        <v>426</v>
+      </c>
+      <c r="B427">
+        <v>101</v>
+      </c>
+      <c r="C427">
+        <v>7732</v>
+      </c>
+      <c r="E427">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A428">
+        <v>427</v>
+      </c>
+      <c r="B428">
+        <v>1</v>
+      </c>
+      <c r="C428">
+        <v>7733</v>
+      </c>
+      <c r="E428">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A429">
+        <v>428</v>
+      </c>
+      <c r="B429">
+        <v>101</v>
+      </c>
+      <c r="C429">
+        <v>7733</v>
+      </c>
+      <c r="E429">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A430">
+        <v>429</v>
+      </c>
+      <c r="B430">
+        <v>1</v>
+      </c>
+      <c r="C430">
+        <v>7740</v>
+      </c>
+      <c r="E430">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A431">
+        <v>430</v>
+      </c>
+      <c r="B431">
+        <v>101</v>
+      </c>
+      <c r="C431">
+        <v>7740</v>
+      </c>
+      <c r="E431">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A432">
+        <v>431</v>
+      </c>
+      <c r="B432">
+        <v>1</v>
+      </c>
+      <c r="C432">
+        <v>7735</v>
+      </c>
+      <c r="E432">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A433">
+        <v>432</v>
+      </c>
+      <c r="B433">
+        <v>101</v>
+      </c>
+      <c r="C433">
+        <v>7735</v>
+      </c>
+      <c r="E433">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A434">
+        <v>433</v>
+      </c>
+      <c r="B434">
+        <v>1</v>
+      </c>
+      <c r="C434">
+        <v>7736</v>
+      </c>
+      <c r="E434">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A435">
+        <v>434</v>
+      </c>
+      <c r="B435">
+        <v>101</v>
+      </c>
+      <c r="C435">
+        <v>7736</v>
+      </c>
+      <c r="E435">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A436">
+        <v>435</v>
+      </c>
+      <c r="B436">
+        <v>1</v>
+      </c>
+      <c r="C436">
+        <v>7737</v>
+      </c>
+      <c r="E436">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A437">
+        <v>436</v>
+      </c>
+      <c r="B437">
+        <v>101</v>
+      </c>
+      <c r="C437">
+        <v>7737</v>
+      </c>
+      <c r="E437">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A438">
+        <v>437</v>
+      </c>
+      <c r="B438">
+        <v>1</v>
+      </c>
+      <c r="C438">
+        <v>7738</v>
+      </c>
+      <c r="E438">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A439">
+        <v>438</v>
+      </c>
+      <c r="B439">
+        <v>101</v>
+      </c>
+      <c r="C439">
+        <v>7738</v>
+      </c>
+      <c r="E439">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A440">
+        <v>439</v>
+      </c>
+      <c r="B440">
+        <v>1</v>
+      </c>
+      <c r="C440">
+        <v>7739</v>
+      </c>
+      <c r="E440">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A441">
+        <v>440</v>
+      </c>
+      <c r="B441">
+        <v>101</v>
+      </c>
+      <c r="C441">
+        <v>7739</v>
+      </c>
+      <c r="E441">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A442">
+        <v>441</v>
+      </c>
+      <c r="B442">
+        <v>1</v>
+      </c>
+      <c r="C442">
+        <v>7734</v>
+      </c>
+      <c r="E442">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A443">
+        <v>442</v>
+      </c>
+      <c r="B443">
+        <v>101</v>
+      </c>
+      <c r="C443">
+        <v>7734</v>
+      </c>
+      <c r="E443">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A444">
+        <v>443</v>
+      </c>
+      <c r="B444">
+        <v>1</v>
+      </c>
+      <c r="C444">
+        <v>7741</v>
+      </c>
+      <c r="E444">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A445">
+        <v>444</v>
+      </c>
+      <c r="B445">
+        <v>101</v>
+      </c>
+      <c r="C445">
+        <v>7741</v>
+      </c>
+      <c r="E445">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A446">
+        <v>445</v>
+      </c>
+      <c r="B446">
+        <v>1</v>
+      </c>
+      <c r="C446">
+        <v>7742</v>
+      </c>
+      <c r="E446">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A447">
+        <v>446</v>
+      </c>
+      <c r="B447">
+        <v>101</v>
+      </c>
+      <c r="C447">
+        <v>7742</v>
+      </c>
+      <c r="E447">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A448">
+        <v>447</v>
+      </c>
+      <c r="B448">
+        <v>1</v>
+      </c>
+      <c r="C448">
+        <v>7743</v>
+      </c>
+      <c r="E448">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A449">
+        <v>448</v>
+      </c>
+      <c r="B449">
+        <v>101</v>
+      </c>
+      <c r="C449">
+        <v>7743</v>
+      </c>
+      <c r="E449">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A450">
+        <v>449</v>
+      </c>
+      <c r="B450">
+        <v>1</v>
+      </c>
+      <c r="C450">
+        <v>7749</v>
+      </c>
+      <c r="E450">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A451">
+        <v>450</v>
+      </c>
+      <c r="B451">
+        <v>101</v>
+      </c>
+      <c r="C451">
+        <v>7749</v>
+      </c>
+      <c r="E451">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A452">
+        <v>451</v>
+      </c>
+      <c r="B452">
+        <v>1</v>
+      </c>
+      <c r="C452">
+        <v>7745</v>
+      </c>
+      <c r="E452">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A453">
+        <v>452</v>
+      </c>
+      <c r="B453">
+        <v>101</v>
+      </c>
+      <c r="C453">
+        <v>7745</v>
+      </c>
+      <c r="E453">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A454">
+        <v>453</v>
+      </c>
+      <c r="B454">
+        <v>1</v>
+      </c>
+      <c r="C454">
+        <v>7746</v>
+      </c>
+      <c r="E454">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A455">
+        <v>454</v>
+      </c>
+      <c r="B455">
+        <v>101</v>
+      </c>
+      <c r="C455">
+        <v>7746</v>
+      </c>
+      <c r="E455">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A456">
+        <v>455</v>
+      </c>
+      <c r="B456">
+        <v>1</v>
+      </c>
+      <c r="C456">
+        <v>7747</v>
+      </c>
+      <c r="E456">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A457">
+        <v>456</v>
+      </c>
+      <c r="B457">
+        <v>101</v>
+      </c>
+      <c r="C457">
+        <v>7747</v>
+      </c>
+      <c r="E457">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A458">
+        <v>457</v>
+      </c>
+      <c r="B458">
+        <v>1</v>
+      </c>
+      <c r="C458">
+        <v>7748</v>
+      </c>
+      <c r="E458">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A459">
+        <v>458</v>
+      </c>
+      <c r="B459">
+        <v>101</v>
+      </c>
+      <c r="C459">
+        <v>7748</v>
+      </c>
+      <c r="E459">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A460">
+        <v>459</v>
+      </c>
+      <c r="B460">
+        <v>1</v>
+      </c>
+      <c r="C460">
+        <v>7744</v>
+      </c>
+      <c r="E460">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A461">
+        <v>460</v>
+      </c>
+      <c r="B461">
+        <v>101</v>
+      </c>
+      <c r="C461">
+        <v>7744</v>
+      </c>
+      <c r="E461">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A462">
+        <v>461</v>
+      </c>
+      <c r="B462">
+        <v>1</v>
+      </c>
+      <c r="C462">
+        <v>7750</v>
+      </c>
+      <c r="E462">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A463">
+        <v>462</v>
+      </c>
+      <c r="B463">
+        <v>101</v>
+      </c>
+      <c r="C463">
+        <v>7750</v>
+      </c>
+      <c r="E463">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A464">
+        <v>463</v>
+      </c>
+      <c r="B464">
+        <v>1</v>
+      </c>
+      <c r="C464">
+        <v>7751</v>
+      </c>
+      <c r="E464">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A465">
+        <v>464</v>
+      </c>
+      <c r="B465">
+        <v>101</v>
+      </c>
+      <c r="C465">
+        <v>7751</v>
+      </c>
+      <c r="E465">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A466">
+        <v>465</v>
+      </c>
+      <c r="B466">
+        <v>1</v>
+      </c>
+      <c r="C466">
+        <v>7752</v>
+      </c>
+      <c r="E466">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A467">
+        <v>466</v>
+      </c>
+      <c r="B467">
+        <v>101</v>
+      </c>
+      <c r="C467">
+        <v>7752</v>
+      </c>
+      <c r="E467">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A468">
+        <v>467</v>
+      </c>
+      <c r="B468">
+        <v>1</v>
+      </c>
+      <c r="C468">
+        <v>7753</v>
+      </c>
+      <c r="E468">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A469">
+        <v>468</v>
+      </c>
+      <c r="B469">
+        <v>101</v>
+      </c>
+      <c r="C469">
+        <v>7753</v>
+      </c>
+      <c r="E469">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A470">
+        <v>469</v>
+      </c>
+      <c r="B470">
+        <v>1</v>
+      </c>
+      <c r="C470">
+        <v>7763</v>
+      </c>
+      <c r="E470">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A471">
+        <v>470</v>
+      </c>
+      <c r="B471">
+        <v>101</v>
+      </c>
+      <c r="C471">
+        <v>7763</v>
+      </c>
+      <c r="E471">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A472">
+        <v>471</v>
+      </c>
+      <c r="B472">
+        <v>1</v>
+      </c>
+      <c r="C472">
+        <v>7754</v>
+      </c>
+      <c r="E472">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A473">
+        <v>472</v>
+      </c>
+      <c r="B473">
+        <v>101</v>
+      </c>
+      <c r="C473">
+        <v>7754</v>
+      </c>
+      <c r="E473">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A474">
+        <v>473</v>
+      </c>
+      <c r="B474">
+        <v>1</v>
+      </c>
+      <c r="C474">
+        <v>7755</v>
+      </c>
+      <c r="E474">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A475">
+        <v>474</v>
+      </c>
+      <c r="B475">
+        <v>101</v>
+      </c>
+      <c r="C475">
+        <v>7755</v>
+      </c>
+      <c r="E475">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A476">
+        <v>475</v>
+      </c>
+      <c r="B476">
+        <v>1</v>
+      </c>
+      <c r="C476">
+        <v>7756</v>
+      </c>
+      <c r="E476">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A477">
+        <v>476</v>
+      </c>
+      <c r="B477">
+        <v>101</v>
+      </c>
+      <c r="C477">
+        <v>7756</v>
+      </c>
+      <c r="E477">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A478">
+        <v>477</v>
+      </c>
+      <c r="B478">
+        <v>1</v>
+      </c>
+      <c r="C478">
+        <v>7757</v>
+      </c>
+      <c r="E478">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A479">
+        <v>478</v>
+      </c>
+      <c r="B479">
+        <v>101</v>
+      </c>
+      <c r="C479">
+        <v>7757</v>
+      </c>
+      <c r="E479">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A480">
+        <v>479</v>
+      </c>
+      <c r="B480">
+        <v>1</v>
+      </c>
+      <c r="C480">
+        <v>7758</v>
+      </c>
+      <c r="E480">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A481">
+        <v>480</v>
+      </c>
+      <c r="B481">
+        <v>101</v>
+      </c>
+      <c r="C481">
+        <v>7758</v>
+      </c>
+      <c r="E481">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A482">
+        <v>481</v>
+      </c>
+      <c r="B482">
+        <v>1</v>
+      </c>
+      <c r="C482">
+        <v>7760</v>
+      </c>
+      <c r="E482">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A483">
+        <v>482</v>
+      </c>
+      <c r="B483">
+        <v>101</v>
+      </c>
+      <c r="C483">
+        <v>7760</v>
+      </c>
+      <c r="E483">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A484">
+        <v>483</v>
+      </c>
+      <c r="B484">
+        <v>1</v>
+      </c>
+      <c r="C484">
+        <v>8797</v>
+      </c>
+      <c r="E484">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A485">
+        <v>484</v>
+      </c>
+      <c r="B485">
+        <v>2</v>
+      </c>
+      <c r="C485">
+        <v>8797</v>
+      </c>
+      <c r="E485">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A486">
+        <v>485</v>
+      </c>
+      <c r="B486">
+        <v>101</v>
+      </c>
+      <c r="C486">
+        <v>8797</v>
+      </c>
+      <c r="E486">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A487">
+        <v>486</v>
+      </c>
+      <c r="B487">
+        <v>102</v>
+      </c>
+      <c r="C487">
+        <v>8797</v>
+      </c>
+      <c r="E487">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A488">
+        <v>487</v>
+      </c>
+      <c r="B488">
+        <v>103</v>
+      </c>
+      <c r="C488">
+        <v>8797</v>
+      </c>
+      <c r="E488">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A489">
+        <v>488</v>
+      </c>
+      <c r="B489">
+        <v>201</v>
+      </c>
+      <c r="C489">
+        <v>8797</v>
+      </c>
+      <c r="E489">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A490">
+        <v>489</v>
+      </c>
+      <c r="B490">
+        <v>202</v>
+      </c>
+      <c r="C490">
+        <v>8797</v>
+      </c>
+      <c r="E490">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A491">
+        <v>490</v>
+      </c>
+      <c r="B491">
+        <v>1</v>
+      </c>
+      <c r="C491">
+        <v>8798</v>
+      </c>
+      <c r="E491">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A492">
+        <v>491</v>
+      </c>
+      <c r="B492">
+        <v>2</v>
+      </c>
+      <c r="C492">
+        <v>8798</v>
+      </c>
+      <c r="E492">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A493">
+        <v>492</v>
+      </c>
+      <c r="B493">
+        <v>101</v>
+      </c>
+      <c r="C493">
+        <v>8798</v>
+      </c>
+      <c r="E493">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A494">
+        <v>493</v>
+      </c>
+      <c r="B494">
+        <v>102</v>
+      </c>
+      <c r="C494">
+        <v>8798</v>
+      </c>
+      <c r="E494">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A495">
+        <v>494</v>
+      </c>
+      <c r="B495">
+        <v>103</v>
+      </c>
+      <c r="C495">
+        <v>8798</v>
+      </c>
+      <c r="E495">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A496">
+        <v>495</v>
+      </c>
+      <c r="B496">
+        <v>201</v>
+      </c>
+      <c r="C496">
+        <v>8798</v>
+      </c>
+      <c r="E496">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A497">
+        <v>496</v>
+      </c>
+      <c r="B497">
+        <v>202</v>
+      </c>
+      <c r="C497">
+        <v>8798</v>
+      </c>
+      <c r="E497">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A498">
+        <v>497</v>
+      </c>
+      <c r="B498">
+        <v>1</v>
+      </c>
+      <c r="C498">
+        <v>8799</v>
+      </c>
+      <c r="E498">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A499">
+        <v>498</v>
+      </c>
+      <c r="B499">
+        <v>2</v>
+      </c>
+      <c r="C499">
+        <v>8799</v>
+      </c>
+      <c r="E499">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A500">
+        <v>499</v>
+      </c>
+      <c r="B500">
+        <v>101</v>
+      </c>
+      <c r="C500">
+        <v>8799</v>
+      </c>
+      <c r="E500">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A501">
+        <v>500</v>
+      </c>
+      <c r="B501">
+        <v>102</v>
+      </c>
+      <c r="C501">
+        <v>8799</v>
+      </c>
+      <c r="E501">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A502">
+        <v>501</v>
+      </c>
+      <c r="B502">
+        <v>103</v>
+      </c>
+      <c r="C502">
+        <v>8799</v>
+      </c>
+      <c r="E502">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A503">
+        <v>502</v>
+      </c>
+      <c r="B503">
+        <v>201</v>
+      </c>
+      <c r="C503">
+        <v>8799</v>
+      </c>
+      <c r="E503">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A504">
+        <v>503</v>
+      </c>
+      <c r="B504">
+        <v>202</v>
+      </c>
+      <c r="C504">
+        <v>8799</v>
+      </c>
+      <c r="E504">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A505">
+        <v>504</v>
+      </c>
+      <c r="B505">
+        <v>1</v>
+      </c>
+      <c r="C505">
+        <v>8800</v>
+      </c>
+      <c r="E505">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A506">
+        <v>505</v>
+      </c>
+      <c r="B506">
+        <v>2</v>
+      </c>
+      <c r="C506">
+        <v>8800</v>
+      </c>
+      <c r="E506">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A507">
+        <v>506</v>
+      </c>
+      <c r="B507">
+        <v>101</v>
+      </c>
+      <c r="C507">
+        <v>8800</v>
+      </c>
+      <c r="E507">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A508">
+        <v>507</v>
+      </c>
+      <c r="B508">
+        <v>102</v>
+      </c>
+      <c r="C508">
+        <v>8800</v>
+      </c>
+      <c r="E508">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A509">
+        <v>508</v>
+      </c>
+      <c r="B509">
+        <v>103</v>
+      </c>
+      <c r="C509">
+        <v>8800</v>
+      </c>
+      <c r="E509">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A510">
+        <v>509</v>
+      </c>
+      <c r="B510">
+        <v>201</v>
+      </c>
+      <c r="C510">
+        <v>8800</v>
+      </c>
+      <c r="E510">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A511">
+        <v>510</v>
+      </c>
+      <c r="B511">
+        <v>202</v>
+      </c>
+      <c r="C511">
+        <v>8800</v>
+      </c>
+      <c r="E511">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A512">
+        <v>511</v>
+      </c>
+      <c r="B512">
+        <v>1</v>
+      </c>
+      <c r="C512">
+        <v>8796</v>
+      </c>
+      <c r="E512">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A513">
+        <v>512</v>
+      </c>
+      <c r="B513">
+        <v>2</v>
+      </c>
+      <c r="C513">
+        <v>8796</v>
+      </c>
+      <c r="E513">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A514">
+        <v>513</v>
+      </c>
+      <c r="B514">
+        <v>101</v>
+      </c>
+      <c r="C514">
+        <v>8796</v>
+      </c>
+      <c r="E514">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A515">
+        <v>514</v>
+      </c>
+      <c r="B515">
+        <v>102</v>
+      </c>
+      <c r="C515">
+        <v>8796</v>
+      </c>
+      <c r="E515">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A516">
+        <v>515</v>
+      </c>
+      <c r="B516">
+        <v>103</v>
+      </c>
+      <c r="C516">
+        <v>8796</v>
+      </c>
+      <c r="E516">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A517">
+        <v>516</v>
+      </c>
+      <c r="B517">
+        <v>201</v>
+      </c>
+      <c r="C517">
+        <v>8796</v>
+      </c>
+      <c r="E517">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A518">
+        <v>517</v>
+      </c>
+      <c r="B518">
+        <v>202</v>
+      </c>
+      <c r="C518">
+        <v>8796</v>
+      </c>
+      <c r="E518">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A519">
+        <v>518</v>
+      </c>
+      <c r="B519">
+        <v>1</v>
+      </c>
+      <c r="C519">
+        <v>8801</v>
+      </c>
+      <c r="E519">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A520">
+        <v>519</v>
+      </c>
+      <c r="B520">
+        <v>2</v>
+      </c>
+      <c r="C520">
+        <v>8801</v>
+      </c>
+      <c r="E520">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A521">
+        <v>520</v>
+      </c>
+      <c r="B521">
+        <v>101</v>
+      </c>
+      <c r="C521">
+        <v>8801</v>
+      </c>
+      <c r="E521">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A522">
+        <v>521</v>
+      </c>
+      <c r="B522">
+        <v>102</v>
+      </c>
+      <c r="C522">
+        <v>8801</v>
+      </c>
+      <c r="E522">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A523">
+        <v>522</v>
+      </c>
+      <c r="B523">
+        <v>201</v>
+      </c>
+      <c r="C523">
+        <v>8801</v>
+      </c>
+      <c r="E523">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A524">
+        <v>523</v>
+      </c>
+      <c r="B524">
+        <v>202</v>
+      </c>
+      <c r="C524">
+        <v>8801</v>
+      </c>
+      <c r="E524">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A525">
+        <v>524</v>
+      </c>
+      <c r="B525">
+        <v>1</v>
+      </c>
+      <c r="C525">
+        <v>8802</v>
+      </c>
+      <c r="E525">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A526">
+        <v>525</v>
+      </c>
+      <c r="B526">
+        <v>2</v>
+      </c>
+      <c r="C526">
+        <v>8802</v>
+      </c>
+      <c r="E526">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A527">
+        <v>526</v>
+      </c>
+      <c r="B527">
+        <v>101</v>
+      </c>
+      <c r="C527">
+        <v>8802</v>
+      </c>
+      <c r="E527">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A528">
+        <v>527</v>
+      </c>
+      <c r="B528">
+        <v>102</v>
+      </c>
+      <c r="C528">
+        <v>8802</v>
+      </c>
+      <c r="E528">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A529">
+        <v>528</v>
+      </c>
+      <c r="B529">
+        <v>103</v>
+      </c>
+      <c r="C529">
+        <v>8802</v>
+      </c>
+      <c r="E529">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A530">
+        <v>529</v>
+      </c>
+      <c r="B530">
+        <v>201</v>
+      </c>
+      <c r="C530">
+        <v>8802</v>
+      </c>
+      <c r="E530">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A531">
+        <v>530</v>
+      </c>
+      <c r="B531">
+        <v>202</v>
+      </c>
+      <c r="C531">
+        <v>8802</v>
+      </c>
+      <c r="E531">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A532">
+        <v>531</v>
+      </c>
+      <c r="B532">
+        <v>1</v>
+      </c>
+      <c r="C532">
+        <v>8803</v>
+      </c>
+      <c r="E532">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A533">
+        <v>532</v>
+      </c>
+      <c r="B533">
+        <v>2</v>
+      </c>
+      <c r="C533">
+        <v>8803</v>
+      </c>
+      <c r="E533">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A534">
+        <v>533</v>
+      </c>
+      <c r="B534">
+        <v>101</v>
+      </c>
+      <c r="C534">
+        <v>8803</v>
+      </c>
+      <c r="E534">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A535">
+        <v>534</v>
+      </c>
+      <c r="B535">
+        <v>102</v>
+      </c>
+      <c r="C535">
+        <v>8803</v>
+      </c>
+      <c r="E535">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A536">
+        <v>535</v>
+      </c>
+      <c r="B536">
+        <v>103</v>
+      </c>
+      <c r="C536">
+        <v>8803</v>
+      </c>
+      <c r="E536">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A537">
+        <v>536</v>
+      </c>
+      <c r="B537">
+        <v>201</v>
+      </c>
+      <c r="C537">
+        <v>8803</v>
+      </c>
+      <c r="E537">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A538">
+        <v>537</v>
+      </c>
+      <c r="B538">
+        <v>202</v>
+      </c>
+      <c r="C538">
+        <v>8803</v>
+      </c>
+      <c r="E538">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A539">
+        <v>538</v>
+      </c>
+      <c r="B539">
+        <v>203</v>
+      </c>
+      <c r="C539">
+        <v>8803</v>
+      </c>
+      <c r="E539">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A540">
+        <v>539</v>
+      </c>
+      <c r="B540">
+        <v>1</v>
+      </c>
+      <c r="C540">
+        <v>8804</v>
+      </c>
+      <c r="E540">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A541">
+        <v>540</v>
+      </c>
+      <c r="B541">
+        <v>2</v>
+      </c>
+      <c r="C541">
+        <v>8804</v>
+      </c>
+      <c r="E541">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A542">
+        <v>541</v>
+      </c>
+      <c r="B542">
+        <v>101</v>
+      </c>
+      <c r="C542">
+        <v>8804</v>
+      </c>
+      <c r="E542">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A543">
+        <v>542</v>
+      </c>
+      <c r="B543">
+        <v>102</v>
+      </c>
+      <c r="C543">
+        <v>8804</v>
+      </c>
+      <c r="E543">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A544">
+        <v>543</v>
+      </c>
+      <c r="B544">
+        <v>201</v>
+      </c>
+      <c r="C544">
+        <v>8804</v>
+      </c>
+      <c r="E544">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A545">
+        <v>544</v>
+      </c>
+      <c r="B545">
+        <v>202</v>
+      </c>
+      <c r="C545">
+        <v>8804</v>
+      </c>
+      <c r="E545">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A546">
+        <v>545</v>
+      </c>
+      <c r="B546">
+        <v>1</v>
+      </c>
+      <c r="C546">
+        <v>8805</v>
+      </c>
+      <c r="E546">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A547">
+        <v>546</v>
+      </c>
+      <c r="B547">
+        <v>2</v>
+      </c>
+      <c r="C547">
+        <v>8805</v>
+      </c>
+      <c r="E547">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A548">
+        <v>547</v>
+      </c>
+      <c r="B548">
+        <v>101</v>
+      </c>
+      <c r="C548">
+        <v>8805</v>
+      </c>
+      <c r="E548">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A549">
+        <v>548</v>
+      </c>
+      <c r="B549">
+        <v>102</v>
+      </c>
+      <c r="C549">
+        <v>8805</v>
+      </c>
+      <c r="E549">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A550">
+        <v>549</v>
+      </c>
+      <c r="B550">
+        <v>103</v>
+      </c>
+      <c r="C550">
+        <v>8805</v>
+      </c>
+      <c r="E550">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A551">
+        <v>550</v>
+      </c>
+      <c r="B551">
+        <v>201</v>
+      </c>
+      <c r="C551">
+        <v>8805</v>
+      </c>
+      <c r="E551">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A552">
+        <v>551</v>
+      </c>
+      <c r="B552">
+        <v>202</v>
+      </c>
+      <c r="C552">
+        <v>8805</v>
+      </c>
+      <c r="E552">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A553">
+        <v>552</v>
+      </c>
+      <c r="B553">
+        <v>1</v>
+      </c>
+      <c r="C553">
+        <v>8806</v>
+      </c>
+      <c r="E553">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A554">
+        <v>553</v>
+      </c>
+      <c r="B554">
+        <v>2</v>
+      </c>
+      <c r="C554">
+        <v>8806</v>
+      </c>
+      <c r="E554">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A555">
+        <v>554</v>
+      </c>
+      <c r="B555">
+        <v>101</v>
+      </c>
+      <c r="C555">
+        <v>8806</v>
+      </c>
+      <c r="E555">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A556">
+        <v>555</v>
+      </c>
+      <c r="B556">
+        <v>102</v>
+      </c>
+      <c r="C556">
+        <v>8806</v>
+      </c>
+      <c r="E556">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A557">
+        <v>556</v>
+      </c>
+      <c r="B557">
+        <v>103</v>
+      </c>
+      <c r="C557">
+        <v>8806</v>
+      </c>
+      <c r="E557">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A558">
+        <v>557</v>
+      </c>
+      <c r="B558">
+        <v>201</v>
+      </c>
+      <c r="C558">
+        <v>8806</v>
+      </c>
+      <c r="E558">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A559">
+        <v>558</v>
+      </c>
+      <c r="B559">
+        <v>202</v>
+      </c>
+      <c r="C559">
+        <v>8806</v>
+      </c>
+      <c r="E559">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A560">
+        <v>559</v>
+      </c>
+      <c r="B560">
+        <v>1</v>
+      </c>
+      <c r="C560">
+        <v>8807</v>
+      </c>
+      <c r="E560">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A561">
+        <v>560</v>
+      </c>
+      <c r="B561">
+        <v>2</v>
+      </c>
+      <c r="C561">
+        <v>8807</v>
+      </c>
+      <c r="E561">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A562">
+        <v>561</v>
+      </c>
+      <c r="B562">
+        <v>101</v>
+      </c>
+      <c r="C562">
+        <v>8807</v>
+      </c>
+      <c r="E562">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A563">
+        <v>562</v>
+      </c>
+      <c r="B563">
+        <v>102</v>
+      </c>
+      <c r="C563">
+        <v>8807</v>
+      </c>
+      <c r="E563">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A564">
+        <v>563</v>
+      </c>
+      <c r="B564">
+        <v>103</v>
+      </c>
+      <c r="C564">
+        <v>8807</v>
+      </c>
+      <c r="E564">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A565">
+        <v>564</v>
+      </c>
+      <c r="B565">
+        <v>201</v>
+      </c>
+      <c r="C565">
+        <v>8807</v>
+      </c>
+      <c r="E565">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A566">
+        <v>565</v>
+      </c>
+      <c r="B566">
+        <v>202</v>
+      </c>
+      <c r="C566">
+        <v>8807</v>
+      </c>
+      <c r="E566">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A567">
+        <v>566</v>
+      </c>
+      <c r="B567">
+        <v>1</v>
+      </c>
+      <c r="C567">
+        <v>8808</v>
+      </c>
+      <c r="E567">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A568">
+        <v>567</v>
+      </c>
+      <c r="B568">
+        <v>2</v>
+      </c>
+      <c r="C568">
+        <v>8808</v>
+      </c>
+      <c r="E568">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A569">
+        <v>568</v>
+      </c>
+      <c r="B569">
+        <v>101</v>
+      </c>
+      <c r="C569">
+        <v>8808</v>
+      </c>
+      <c r="E569">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A570">
+        <v>569</v>
+      </c>
+      <c r="B570">
+        <v>102</v>
+      </c>
+      <c r="C570">
+        <v>8808</v>
+      </c>
+      <c r="E570">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A571">
+        <v>570</v>
+      </c>
+      <c r="B571">
+        <v>201</v>
+      </c>
+      <c r="C571">
+        <v>8808</v>
+      </c>
+      <c r="E571">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A572">
+        <v>571</v>
+      </c>
+      <c r="B572">
+        <v>202</v>
+      </c>
+      <c r="C572">
+        <v>8808</v>
+      </c>
+      <c r="E572">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A573">
+        <v>572</v>
+      </c>
+      <c r="B573">
+        <v>1</v>
+      </c>
+      <c r="C573">
+        <v>8809</v>
+      </c>
+      <c r="E573">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A574">
+        <v>573</v>
+      </c>
+      <c r="B574">
+        <v>2</v>
+      </c>
+      <c r="C574">
+        <v>8809</v>
+      </c>
+      <c r="E574">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A575">
+        <v>574</v>
+      </c>
+      <c r="B575">
+        <v>101</v>
+      </c>
+      <c r="C575">
+        <v>8809</v>
+      </c>
+      <c r="E575">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A576">
+        <v>575</v>
+      </c>
+      <c r="B576">
+        <v>102</v>
+      </c>
+      <c r="C576">
+        <v>8809</v>
+      </c>
+      <c r="E576">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A577">
+        <v>576</v>
+      </c>
+      <c r="B577">
+        <v>103</v>
+      </c>
+      <c r="C577">
+        <v>8809</v>
+      </c>
+      <c r="E577">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A578">
+        <v>577</v>
+      </c>
+      <c r="B578">
+        <v>201</v>
+      </c>
+      <c r="C578">
+        <v>8809</v>
+      </c>
+      <c r="E578">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A579">
+        <v>578</v>
+      </c>
+      <c r="B579">
+        <v>202</v>
+      </c>
+      <c r="C579">
+        <v>8809</v>
+      </c>
+      <c r="E579">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A580">
+        <v>579</v>
+      </c>
+      <c r="B580">
+        <v>1</v>
+      </c>
+      <c r="C580">
+        <v>8810</v>
+      </c>
+      <c r="E580">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A581">
+        <v>580</v>
+      </c>
+      <c r="B581">
+        <v>2</v>
+      </c>
+      <c r="C581">
+        <v>8810</v>
+      </c>
+      <c r="E581">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A582">
+        <v>581</v>
+      </c>
+      <c r="B582">
+        <v>101</v>
+      </c>
+      <c r="C582">
+        <v>8810</v>
+      </c>
+      <c r="E582">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A583">
+        <v>582</v>
+      </c>
+      <c r="B583">
+        <v>102</v>
+      </c>
+      <c r="C583">
+        <v>8810</v>
+      </c>
+      <c r="E583">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A584">
+        <v>583</v>
+      </c>
+      <c r="B584">
+        <v>103</v>
+      </c>
+      <c r="C584">
+        <v>8810</v>
+      </c>
+      <c r="E584">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A585">
+        <v>584</v>
+      </c>
+      <c r="B585">
+        <v>201</v>
+      </c>
+      <c r="C585">
+        <v>8810</v>
+      </c>
+      <c r="E585">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A586">
+        <v>585</v>
+      </c>
+      <c r="B586">
+        <v>202</v>
+      </c>
+      <c r="C586">
+        <v>8810</v>
+      </c>
+      <c r="E586">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A587">
+        <v>586</v>
+      </c>
+      <c r="B587">
+        <v>1</v>
+      </c>
+      <c r="C587">
+        <v>8811</v>
+      </c>
+      <c r="E587">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A588">
+        <v>587</v>
+      </c>
+      <c r="B588">
+        <v>2</v>
+      </c>
+      <c r="C588">
+        <v>8811</v>
+      </c>
+      <c r="E588">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A589">
+        <v>588</v>
+      </c>
+      <c r="B589">
+        <v>101</v>
+      </c>
+      <c r="C589">
+        <v>8811</v>
+      </c>
+      <c r="E589">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A590">
+        <v>589</v>
+      </c>
+      <c r="B590">
+        <v>102</v>
+      </c>
+      <c r="C590">
+        <v>8811</v>
+      </c>
+      <c r="E590">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A591">
+        <v>590</v>
+      </c>
+      <c r="B591">
+        <v>201</v>
+      </c>
+      <c r="C591">
+        <v>8811</v>
+      </c>
+      <c r="E591">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A592">
+        <v>591</v>
+      </c>
+      <c r="B592">
+        <v>202</v>
+      </c>
+      <c r="C592">
+        <v>8811</v>
+      </c>
+      <c r="E592">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="593" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A593">
+        <v>592</v>
+      </c>
+      <c r="B593">
+        <v>1</v>
+      </c>
+      <c r="C593">
+        <v>8812</v>
+      </c>
+      <c r="E593">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="594" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A594">
+        <v>593</v>
+      </c>
+      <c r="B594">
+        <v>2</v>
+      </c>
+      <c r="C594">
+        <v>8812</v>
+      </c>
+      <c r="E594">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="595" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A595">
+        <v>594</v>
+      </c>
+      <c r="B595">
+        <v>101</v>
+      </c>
+      <c r="C595">
+        <v>8812</v>
+      </c>
+      <c r="E595">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="596" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A596">
+        <v>595</v>
+      </c>
+      <c r="B596">
+        <v>102</v>
+      </c>
+      <c r="C596">
+        <v>8812</v>
+      </c>
+      <c r="E596">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="597" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A597">
+        <v>596</v>
+      </c>
+      <c r="B597">
+        <v>201</v>
+      </c>
+      <c r="C597">
+        <v>8812</v>
+      </c>
+      <c r="E597">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="598" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A598">
+        <v>597</v>
+      </c>
+      <c r="B598">
+        <v>202</v>
+      </c>
+      <c r="C598">
+        <v>8812</v>
+      </c>
+      <c r="E598">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="599" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A599">
+        <v>598</v>
+      </c>
+      <c r="B599">
+        <v>1</v>
+      </c>
+      <c r="C599">
+        <v>8813</v>
+      </c>
+      <c r="E599">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="600" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A600">
+        <v>599</v>
+      </c>
+      <c r="B600">
+        <v>2</v>
+      </c>
+      <c r="C600">
+        <v>8813</v>
+      </c>
+      <c r="E600">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="601" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A601">
+        <v>600</v>
+      </c>
+      <c r="B601">
+        <v>101</v>
+      </c>
+      <c r="C601">
+        <v>8813</v>
+      </c>
+      <c r="E601">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="602" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A602">
+        <v>601</v>
+      </c>
+      <c r="B602">
+        <v>102</v>
+      </c>
+      <c r="C602">
+        <v>8813</v>
+      </c>
+      <c r="E602">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="603" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A603">
+        <v>602</v>
+      </c>
+      <c r="B603">
+        <v>201</v>
+      </c>
+      <c r="C603">
+        <v>8813</v>
+      </c>
+      <c r="E603">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="604" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A604">
+        <v>603</v>
+      </c>
+      <c r="B604">
+        <v>202</v>
+      </c>
+      <c r="C604">
+        <v>8813</v>
+      </c>
+      <c r="E604">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="605" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A605">
+        <v>604</v>
+      </c>
+      <c r="B605">
+        <v>1</v>
+      </c>
+      <c r="C605">
+        <v>8814</v>
+      </c>
+      <c r="E605">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="606" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A606">
+        <v>605</v>
+      </c>
+      <c r="B606">
+        <v>2</v>
+      </c>
+      <c r="C606">
+        <v>8814</v>
+      </c>
+      <c r="E606">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="607" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A607">
+        <v>606</v>
+      </c>
+      <c r="B607">
+        <v>101</v>
+      </c>
+      <c r="C607">
+        <v>8814</v>
+      </c>
+      <c r="E607">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="608" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A608">
+        <v>607</v>
+      </c>
+      <c r="B608">
+        <v>102</v>
+      </c>
+      <c r="C608">
+        <v>8814</v>
+      </c>
+      <c r="E608">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A609">
+        <v>608</v>
+      </c>
+      <c r="B609">
+        <v>201</v>
+      </c>
+      <c r="C609">
+        <v>8814</v>
+      </c>
+      <c r="E609">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="610" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A610">
+        <v>609</v>
+      </c>
+      <c r="B610">
+        <v>1</v>
+      </c>
+      <c r="C610">
+        <v>8815</v>
+      </c>
+      <c r="E610">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A611">
+        <v>610</v>
+      </c>
+      <c r="B611">
+        <v>2</v>
+      </c>
+      <c r="C611">
+        <v>8815</v>
+      </c>
+      <c r="E611">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A612">
+        <v>611</v>
+      </c>
+      <c r="B612">
+        <v>101</v>
+      </c>
+      <c r="C612">
+        <v>8815</v>
+      </c>
+      <c r="E612">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A613">
+        <v>612</v>
+      </c>
+      <c r="B613">
+        <v>102</v>
+      </c>
+      <c r="C613">
+        <v>8815</v>
+      </c>
+      <c r="E613">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A614">
+        <v>613</v>
+      </c>
+      <c r="B614">
+        <v>201</v>
+      </c>
+      <c r="C614">
+        <v>8815</v>
+      </c>
+      <c r="E614">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A615">
+        <v>614</v>
+      </c>
+      <c r="B615">
+        <v>202</v>
+      </c>
+      <c r="C615">
+        <v>8815</v>
+      </c>
+      <c r="E615">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A616">
+        <v>615</v>
+      </c>
+      <c r="B616">
+        <v>1</v>
+      </c>
+      <c r="C616">
+        <v>8816</v>
+      </c>
+      <c r="E616">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="617" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A617">
+        <v>616</v>
+      </c>
+      <c r="B617">
+        <v>101</v>
+      </c>
+      <c r="C617">
+        <v>8816</v>
+      </c>
+      <c r="E617">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A618">
+        <v>617</v>
+      </c>
+      <c r="B618">
+        <v>102</v>
+      </c>
+      <c r="C618">
+        <v>8816</v>
+      </c>
+      <c r="E618">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A619">
+        <v>618</v>
+      </c>
+      <c r="B619">
+        <v>103</v>
+      </c>
+      <c r="C619">
+        <v>8816</v>
+      </c>
+      <c r="E619">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A620">
+        <v>619</v>
+      </c>
+      <c r="B620">
+        <v>104</v>
+      </c>
+      <c r="C620">
+        <v>8816</v>
+      </c>
+      <c r="E620">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A621">
+        <v>620</v>
+      </c>
+      <c r="B621">
+        <v>1</v>
+      </c>
+      <c r="C621">
+        <v>8817</v>
+      </c>
+      <c r="E621">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A622">
+        <v>621</v>
+      </c>
+      <c r="B622">
+        <v>101</v>
+      </c>
+      <c r="C622">
+        <v>8817</v>
+      </c>
+      <c r="E622">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A623">
+        <v>622</v>
+      </c>
+      <c r="B623">
+        <v>102</v>
+      </c>
+      <c r="C623">
+        <v>8817</v>
+      </c>
+      <c r="E623">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A624">
+        <v>623</v>
+      </c>
+      <c r="B624">
+        <v>103</v>
+      </c>
+      <c r="C624">
+        <v>8817</v>
+      </c>
+      <c r="E624">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="625" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A625">
+        <v>624</v>
+      </c>
+      <c r="B625">
+        <v>1</v>
+      </c>
+      <c r="C625">
+        <v>8818</v>
+      </c>
+      <c r="E625">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A626">
+        <v>625</v>
+      </c>
+      <c r="B626">
+        <v>101</v>
+      </c>
+      <c r="C626">
+        <v>8818</v>
+      </c>
+      <c r="E626">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A627">
+        <v>626</v>
+      </c>
+      <c r="B627">
+        <v>102</v>
+      </c>
+      <c r="C627">
+        <v>8818</v>
+      </c>
+      <c r="E627">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A628">
+        <v>627</v>
+      </c>
+      <c r="B628">
+        <v>103</v>
+      </c>
+      <c r="C628">
+        <v>8818</v>
+      </c>
+      <c r="E628">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A629">
+        <v>628</v>
+      </c>
+      <c r="B629">
+        <v>1</v>
+      </c>
+      <c r="C629">
+        <v>8819</v>
+      </c>
+      <c r="E629">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A630">
+        <v>629</v>
+      </c>
+      <c r="B630">
+        <v>101</v>
+      </c>
+      <c r="C630">
+        <v>8819</v>
+      </c>
+      <c r="E630">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="631" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A631">
+        <v>630</v>
+      </c>
+      <c r="B631">
+        <v>102</v>
+      </c>
+      <c r="C631">
+        <v>8819</v>
+      </c>
+      <c r="E631">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A632">
+        <v>631</v>
+      </c>
+      <c r="B632">
+        <v>103</v>
+      </c>
+      <c r="C632">
+        <v>8819</v>
+      </c>
+      <c r="E632">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A633">
+        <v>632</v>
+      </c>
+      <c r="B633">
+        <v>1</v>
+      </c>
+      <c r="C633">
+        <v>8820</v>
+      </c>
+      <c r="E633">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A634">
+        <v>633</v>
+      </c>
+      <c r="B634">
+        <v>101</v>
+      </c>
+      <c r="C634">
+        <v>8820</v>
+      </c>
+      <c r="E634">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A635">
+        <v>634</v>
+      </c>
+      <c r="B635">
+        <v>102</v>
+      </c>
+      <c r="C635">
+        <v>8820</v>
+      </c>
+      <c r="E635">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="636" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A636">
+        <v>635</v>
+      </c>
+      <c r="B636">
+        <v>103</v>
+      </c>
+      <c r="C636">
+        <v>8820</v>
+      </c>
+      <c r="E636">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A637">
+        <v>636</v>
+      </c>
+      <c r="B637">
+        <v>1</v>
+      </c>
+      <c r="C637">
+        <v>8824</v>
+      </c>
+      <c r="E637">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A638">
+        <v>637</v>
+      </c>
+      <c r="B638">
+        <v>101</v>
+      </c>
+      <c r="C638">
+        <v>8824</v>
+      </c>
+      <c r="E638">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A639">
+        <v>638</v>
+      </c>
+      <c r="B639">
+        <v>102</v>
+      </c>
+      <c r="C639">
+        <v>8824</v>
+      </c>
+      <c r="E639">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A640">
+        <v>639</v>
+      </c>
+      <c r="B640">
+        <v>103</v>
+      </c>
+      <c r="C640">
+        <v>8824</v>
+      </c>
+      <c r="E640">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="641" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A641">
+        <v>640</v>
+      </c>
+      <c r="B641">
+        <v>1</v>
+      </c>
+      <c r="C641">
+        <v>8823</v>
+      </c>
+      <c r="E641">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A642">
+        <v>641</v>
+      </c>
+      <c r="B642">
+        <v>101</v>
+      </c>
+      <c r="C642">
+        <v>8823</v>
+      </c>
+      <c r="E642">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="643" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A643">
+        <v>642</v>
+      </c>
+      <c r="B643">
+        <v>102</v>
+      </c>
+      <c r="C643">
+        <v>8823</v>
+      </c>
+      <c r="E643">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="644" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A644">
+        <v>643</v>
+      </c>
+      <c r="B644">
+        <v>103</v>
+      </c>
+      <c r="C644">
+        <v>8823</v>
+      </c>
+      <c r="E644">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="645" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A645">
+        <v>644</v>
+      </c>
+      <c r="B645">
+        <v>1</v>
+      </c>
+      <c r="C645">
+        <v>8825</v>
+      </c>
+      <c r="E645">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A646">
+        <v>645</v>
+      </c>
+      <c r="B646">
+        <v>101</v>
+      </c>
+      <c r="C646">
+        <v>8825</v>
+      </c>
+      <c r="E646">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="647" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A647">
+        <v>646</v>
+      </c>
+      <c r="B647">
+        <v>102</v>
+      </c>
+      <c r="C647">
+        <v>8825</v>
+      </c>
+      <c r="E647">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="648" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A648">
+        <v>647</v>
+      </c>
+      <c r="B648">
+        <v>103</v>
+      </c>
+      <c r="C648">
+        <v>8825</v>
+      </c>
+      <c r="E648">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="649" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A649">
+        <v>648</v>
+      </c>
+      <c r="B649">
+        <v>1</v>
+      </c>
+      <c r="C649">
+        <v>8821</v>
+      </c>
+      <c r="E649">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="650" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A650">
+        <v>649</v>
+      </c>
+      <c r="B650">
+        <v>101</v>
+      </c>
+      <c r="C650">
+        <v>8821</v>
+      </c>
+      <c r="E650">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="651" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A651">
+        <v>650</v>
+      </c>
+      <c r="B651">
+        <v>102</v>
+      </c>
+      <c r="C651">
+        <v>8821</v>
+      </c>
+      <c r="E651">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="652" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A652">
+        <v>651</v>
+      </c>
+      <c r="B652">
+        <v>103</v>
+      </c>
+      <c r="C652">
+        <v>8821</v>
+      </c>
+      <c r="E652">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="653" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A653">
+        <v>652</v>
+      </c>
+      <c r="B653">
+        <v>1</v>
+      </c>
+      <c r="C653">
+        <v>8822</v>
+      </c>
+      <c r="E653">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="654" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A654">
+        <v>653</v>
+      </c>
+      <c r="B654">
+        <v>101</v>
+      </c>
+      <c r="C654">
+        <v>8822</v>
+      </c>
+      <c r="E654">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="655" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A655">
+        <v>654</v>
+      </c>
+      <c r="B655">
+        <v>102</v>
+      </c>
+      <c r="C655">
+        <v>8822</v>
+      </c>
+      <c r="E655">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="656" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A656">
+        <v>655</v>
+      </c>
+      <c r="B656">
+        <v>103</v>
+      </c>
+      <c r="C656">
+        <v>8822</v>
+      </c>
+      <c r="E656">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="657" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A657">
+        <v>656</v>
+      </c>
+      <c r="B657">
+        <v>1</v>
+      </c>
+      <c r="C657">
+        <v>8827</v>
+      </c>
+      <c r="E657">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="658" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A658">
+        <v>657</v>
+      </c>
+      <c r="B658">
+        <v>101</v>
+      </c>
+      <c r="C658">
+        <v>8827</v>
+      </c>
+      <c r="E658">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="659" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A659">
+        <v>658</v>
+      </c>
+      <c r="B659">
+        <v>1</v>
+      </c>
+      <c r="C659">
+        <v>8828</v>
+      </c>
+      <c r="E659">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="660" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A660">
+        <v>659</v>
+      </c>
+      <c r="B660">
+        <v>101</v>
+      </c>
+      <c r="C660">
+        <v>8828</v>
+      </c>
+      <c r="E660">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="661" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A661">
+        <v>660</v>
+      </c>
+      <c r="B661">
+        <v>1</v>
+      </c>
+      <c r="C661">
+        <v>8829</v>
+      </c>
+      <c r="E661">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="662" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A662">
+        <v>661</v>
+      </c>
+      <c r="B662">
+        <v>101</v>
+      </c>
+      <c r="C662">
+        <v>8829</v>
+      </c>
+      <c r="E662">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="663" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A663">
+        <v>662</v>
+      </c>
+      <c r="B663">
+        <v>1</v>
+      </c>
+      <c r="C663">
+        <v>8830</v>
+      </c>
+      <c r="E663">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="664" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A664">
+        <v>663</v>
+      </c>
+      <c r="B664">
+        <v>101</v>
+      </c>
+      <c r="C664">
+        <v>8830</v>
+      </c>
+      <c r="E664">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="665" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A665">
+        <v>664</v>
+      </c>
+      <c r="B665">
+        <v>1</v>
+      </c>
+      <c r="C665">
+        <v>8831</v>
+      </c>
+      <c r="E665">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="666" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A666">
+        <v>665</v>
+      </c>
+      <c r="B666">
+        <v>101</v>
+      </c>
+      <c r="C666">
+        <v>8831</v>
+      </c>
+      <c r="E666">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="667" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A667">
+        <v>666</v>
+      </c>
+      <c r="B667">
+        <v>1</v>
+      </c>
+      <c r="C667">
+        <v>8832</v>
+      </c>
+      <c r="E667">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="668" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A668">
+        <v>667</v>
+      </c>
+      <c r="B668">
+        <v>101</v>
+      </c>
+      <c r="C668">
+        <v>8832</v>
+      </c>
+      <c r="E668">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="669" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A669">
+        <v>668</v>
+      </c>
+      <c r="B669">
+        <v>1</v>
+      </c>
+      <c r="C669">
+        <v>8833</v>
+      </c>
+      <c r="E669">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="670" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A670">
+        <v>669</v>
+      </c>
+      <c r="B670">
+        <v>101</v>
+      </c>
+      <c r="C670">
+        <v>8833</v>
+      </c>
+      <c r="E670">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="671" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A671">
+        <v>670</v>
+      </c>
+      <c r="B671">
+        <v>1</v>
+      </c>
+      <c r="C671">
+        <v>8834</v>
+      </c>
+      <c r="E671">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="672" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A672">
+        <v>671</v>
+      </c>
+      <c r="B672">
+        <v>101</v>
+      </c>
+      <c r="C672">
+        <v>8834</v>
+      </c>
+      <c r="E672">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="673" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A673">
+        <v>672</v>
+      </c>
+      <c r="B673">
+        <v>1</v>
+      </c>
+      <c r="C673">
+        <v>8835</v>
+      </c>
+      <c r="E673">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="674" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A674">
+        <v>673</v>
+      </c>
+      <c r="B674">
+        <v>101</v>
+      </c>
+      <c r="C674">
+        <v>8835</v>
+      </c>
+      <c r="E674">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="675" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A675">
+        <v>674</v>
+      </c>
+      <c r="B675">
+        <v>1</v>
+      </c>
+      <c r="C675">
+        <v>8836</v>
+      </c>
+      <c r="E675">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="676" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A676">
+        <v>675</v>
+      </c>
+      <c r="B676">
+        <v>101</v>
+      </c>
+      <c r="C676">
+        <v>8836</v>
+      </c>
+      <c r="E676">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="677" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A677">
+        <v>676</v>
+      </c>
+      <c r="B677">
+        <v>1</v>
+      </c>
+      <c r="C677">
+        <v>8837</v>
+      </c>
+      <c r="E677">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="678" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A678">
+        <v>677</v>
+      </c>
+      <c r="B678">
+        <v>101</v>
+      </c>
+      <c r="C678">
+        <v>8837</v>
+      </c>
+      <c r="E678">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="679" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A679">
+        <v>678</v>
+      </c>
+      <c r="B679">
+        <v>102</v>
+      </c>
+      <c r="C679">
+        <v>8837</v>
+      </c>
+      <c r="E679">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="680" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A680">
+        <v>679</v>
+      </c>
+      <c r="B680">
+        <v>1</v>
+      </c>
+      <c r="C680">
+        <v>8838</v>
+      </c>
+      <c r="E680">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="681" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A681">
+        <v>680</v>
+      </c>
+      <c r="B681">
+        <v>101</v>
+      </c>
+      <c r="C681">
+        <v>8838</v>
+      </c>
+      <c r="E681">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/app_horarios/datos/excel/export-15-04.xlsx
+++ b/app_horarios/datos/excel/export-15-04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\Ingeniería informática\4º Trabajo de Fin de Grado\Trabajo-Fin-de-Grado-2025-2026\app_horarios\datos\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C384CC-F9C5-46C6-954E-24A282A43DA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAEBDE1-2339-4B1C-B4A1-0197CA29D73C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="asignaturas" sheetId="1" r:id="rId1"/>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1114" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1239" uniqueCount="286">
   <si>
     <t>IDASIGNATURA</t>
   </si>
@@ -125,9 +125,6 @@
     <t>ID</t>
   </si>
   <si>
-    <t>NOMBRE_EXCEL</t>
-  </si>
-  <si>
     <t>EDIFICIO</t>
   </si>
   <si>
@@ -164,21 +161,12 @@
     <t>23-A1</t>
   </si>
   <si>
-    <t>Aula 23-A1</t>
-  </si>
-  <si>
     <t>A1</t>
   </si>
   <si>
     <t>25</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20.00</t>
-  </si>
-  <si>
     <t>291</t>
   </si>
   <si>
@@ -191,45 +179,24 @@
     <t>44-A2</t>
   </si>
   <si>
-    <t>Aula 44-A2</t>
-  </si>
-  <si>
     <t>A2</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>15</t>
   </si>
   <si>
-    <t>40.00</t>
-  </si>
-  <si>
     <t>53-A1</t>
   </si>
   <si>
-    <t>Aula 53-A1</t>
-  </si>
-  <si>
     <t>5</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>60.00</t>
-  </si>
-  <si>
     <t>Lab. Automática 1</t>
   </si>
   <si>
-    <t>La. Automática 1</t>
-  </si>
-  <si>
     <t>A1-A2</t>
   </si>
   <si>
@@ -239,15 +206,6 @@
     <t>30</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>30.00</t>
-  </si>
-  <si>
-    <t>Laboratorio de automatización</t>
-  </si>
-  <si>
     <t>147</t>
   </si>
   <si>
@@ -756,6 +714,201 @@
   </si>
   <si>
     <t>DATE_JOINED</t>
+  </si>
+  <si>
+    <t>ID_GRUPO</t>
+  </si>
+  <si>
+    <t>21-A1</t>
+  </si>
+  <si>
+    <t>22-A1</t>
+  </si>
+  <si>
+    <t>24-A1</t>
+  </si>
+  <si>
+    <t>26-A1</t>
+  </si>
+  <si>
+    <t>32-A1</t>
+  </si>
+  <si>
+    <t>34-A1</t>
+  </si>
+  <si>
+    <t>36-A1</t>
+  </si>
+  <si>
+    <t>42-A1</t>
+  </si>
+  <si>
+    <t>44-A1</t>
+  </si>
+  <si>
+    <t>46-A1</t>
+  </si>
+  <si>
+    <t>51-A1</t>
+  </si>
+  <si>
+    <t>Reloj</t>
+  </si>
+  <si>
+    <t>52-A1</t>
+  </si>
+  <si>
+    <t>54-A1</t>
+  </si>
+  <si>
+    <t>Sala 4114</t>
+  </si>
+  <si>
+    <t>32-A2</t>
+  </si>
+  <si>
+    <t>34-A2</t>
+  </si>
+  <si>
+    <t>36-A2</t>
+  </si>
+  <si>
+    <t>31-A2</t>
+  </si>
+  <si>
+    <t>33-A2</t>
+  </si>
+  <si>
+    <t>35-A2</t>
+  </si>
+  <si>
+    <t>42-A2</t>
+  </si>
+  <si>
+    <t>46-A2</t>
+  </si>
+  <si>
+    <t>41-A2</t>
+  </si>
+  <si>
+    <t>*****</t>
+  </si>
+  <si>
+    <t>TV/Sonido</t>
+  </si>
+  <si>
+    <t>51-A2</t>
+  </si>
+  <si>
+    <t>53-A2</t>
+  </si>
+  <si>
+    <t>55-A2</t>
+  </si>
+  <si>
+    <t>52-A2</t>
+  </si>
+  <si>
+    <t>Salón de actos</t>
+  </si>
+  <si>
+    <t>Multimedia/DVD</t>
+  </si>
+  <si>
+    <t>Biblioteca</t>
+  </si>
+  <si>
+    <t>Informática 2A</t>
+  </si>
+  <si>
+    <t>Informática 2B</t>
+  </si>
+  <si>
+    <t>Sala de Juntas I</t>
+  </si>
+  <si>
+    <t>TV/DVD</t>
+  </si>
+  <si>
+    <t>Despacho Sala de Juntas I</t>
+  </si>
+  <si>
+    <t>TV/Videoconferencia</t>
+  </si>
+  <si>
+    <t>Sala de Juntas II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Webcam + </t>
+  </si>
+  <si>
+    <t>Sala de Estudio</t>
+  </si>
+  <si>
+    <t>Laboratorio Electrónica 1</t>
+  </si>
+  <si>
+    <t>Laboratorio Electrónica 3</t>
+  </si>
+  <si>
+    <t>Laboratorio Ing. Eléctrica 1</t>
+  </si>
+  <si>
+    <t>Laboratorio Ing. Eléctrica 2</t>
+  </si>
+  <si>
+    <t>Laboratorio Materiales</t>
+  </si>
+  <si>
+    <t>Laboratorio Química</t>
+  </si>
+  <si>
+    <t>Laboratorio Fisica</t>
+  </si>
+  <si>
+    <t>Laboratorio Automática 1</t>
+  </si>
+  <si>
+    <t>Laboratorio Automática 2</t>
+  </si>
+  <si>
+    <t>Laboratorio Ing. Energética 1</t>
+  </si>
+  <si>
+    <t>Laboratorio Ing. Energética 2</t>
+  </si>
+  <si>
+    <t>Laboratorio Tecn. Mecánica</t>
+  </si>
+  <si>
+    <t>Laboratorio MMC</t>
+  </si>
+  <si>
+    <t>Laboratorio de Ing. Mecánica</t>
+  </si>
+  <si>
+    <t>Aula Empresa</t>
+  </si>
+  <si>
+    <t>Laboratorio Biologia Fac CC</t>
+  </si>
+  <si>
+    <t>Laboratorio Fisiología Fac CS</t>
+  </si>
+  <si>
+    <t>Laboratorio Mecanismos</t>
+  </si>
+  <si>
+    <t>Laboratorio Fac CC</t>
+  </si>
+  <si>
+    <t>Labortorio Fac CS</t>
+  </si>
+  <si>
+    <t>Informática 1A</t>
+  </si>
+  <si>
+    <t>Informática 1B</t>
   </si>
 </sst>
 </file>
@@ -766,7 +919,7 @@
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -787,6 +940,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -824,7 +982,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -832,6 +990,7 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1265,19 +1424,19 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>129</v>
+        <v>115</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -10813,10 +10972,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -10831,7 +10990,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -10846,370 +11005,370 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>134</v>
+        <v>120</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C2" s="2">
         <v>46038</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E2" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F2" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="G2" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C3" s="2">
         <v>46044</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E3" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F3" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="G3" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="2">
         <v>46049</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E4" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F4" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="G4" t="s">
-        <v>147</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2">
         <v>46045</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F5" t="s">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="G5" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C6" s="2">
         <v>46051</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F6" t="s">
-        <v>153</v>
+        <v>139</v>
       </c>
       <c r="G6" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2">
         <v>46049</v>
       </c>
       <c r="D7" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F7" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="G7" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C8" s="2">
         <v>46056</v>
       </c>
       <c r="D8" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F8" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="G8" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C9" s="2">
         <v>46063</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E9" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F9" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="G9" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C10" s="2">
         <v>46070</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E10" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F10" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="G10" t="s">
-        <v>155</v>
+        <v>141</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C11" s="2">
         <v>46056</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F11" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="G11" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C12" s="2">
         <v>46063</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F12" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="G12" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C13" s="2">
         <v>46070</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E13" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F13" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="G13" t="s">
-        <v>161</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="2">
         <v>46058</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E14" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F14" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="G14" t="s">
-        <v>166</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2">
         <v>46059</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E15" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F15" t="s">
-        <v>168</v>
+        <v>154</v>
       </c>
       <c r="G15" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2">
         <v>46112</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="E16" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="F16" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="G16" t="s">
-        <v>171</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -11221,25 +11380,33 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>128</v>
+        <v>221</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>173</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -11254,57 +11421,57 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>172</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>174</v>
+        <v>160</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>179</v>
+        <v>165</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>181</v>
+        <v>167</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>183</v>
+        <v>169</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="B2" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="E2" s="3">
         <v>46038.654861111107</v>
@@ -11333,16 +11500,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="B3" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="E3" s="3">
         <v>46044.75</v>
@@ -11351,7 +11518,7 @@
         <v>46044.791666666657</v>
       </c>
       <c r="G3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -11371,16 +11538,16 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="E4" s="3">
         <v>46049.416666666657</v>
@@ -11389,7 +11556,7 @@
         <v>46049.5</v>
       </c>
       <c r="G4" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -11409,16 +11576,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="B5" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="C5" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D5" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="E5" s="3">
         <v>46045.375</v>
@@ -11427,7 +11594,7 @@
         <v>46045.625</v>
       </c>
       <c r="G5" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -11447,16 +11614,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>138</v>
       </c>
       <c r="B6" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="C6" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D6" t="s">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="E6" s="3">
         <v>46051.666666666657</v>
@@ -11485,16 +11652,16 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="B7" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="E7" s="3">
         <v>46049.416666666657</v>
@@ -11523,16 +11690,16 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="B8" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="E8" s="3">
         <v>46056.416666666657</v>
@@ -11561,16 +11728,16 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="B9" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="E9" s="3">
         <v>46063.416666666657</v>
@@ -11599,16 +11766,16 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="B10" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="E10" s="3">
         <v>46070.416666666657</v>
@@ -11637,16 +11804,16 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>159</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C11" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D11" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="E11" s="3">
         <v>46056.6875</v>
@@ -11655,7 +11822,7 @@
         <v>46056.770833333343</v>
       </c>
       <c r="G11" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -11675,16 +11842,16 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>162</v>
+        <v>148</v>
       </c>
       <c r="B12" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C12" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D12" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="E12" s="3">
         <v>46063.6875</v>
@@ -11693,7 +11860,7 @@
         <v>46063.770833333343</v>
       </c>
       <c r="G12" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -11713,16 +11880,16 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>163</v>
+        <v>149</v>
       </c>
       <c r="B13" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C13" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D13" t="s">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="E13" s="3">
         <v>46070.6875</v>
@@ -11731,7 +11898,7 @@
         <v>46070.770833333343</v>
       </c>
       <c r="G13" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -11751,16 +11918,16 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>164</v>
+        <v>150</v>
       </c>
       <c r="B14" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C14" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="D14" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="E14" s="3">
         <v>46058.479166666657</v>
@@ -11769,7 +11936,7 @@
         <v>46058.520833333343</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -11789,16 +11956,16 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="B15" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="C15" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
       <c r="D15" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="E15" s="3">
         <v>46059.727777777778</v>
@@ -11807,7 +11974,7 @@
         <v>46059.770138888889</v>
       </c>
       <c r="G15" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -11827,16 +11994,16 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="B16" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="C16" t="s">
-        <v>192</v>
+        <v>178</v>
       </c>
       <c r="D16" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="E16" s="3">
         <v>46112.625</v>
@@ -11845,7 +12012,7 @@
         <v>46112.708333333343</v>
       </c>
       <c r="G16" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -11875,130 +12042,130 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>131</v>
+        <v>117</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="B2" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="C2" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B3" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="C3" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>186</v>
+        <v>172</v>
       </c>
       <c r="B4" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="C4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="D4" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="B5" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="C5" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="B6" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="B7" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
       <c r="D7" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C8" t="s">
         <v>204</v>
-      </c>
-      <c r="B8" t="s">
-        <v>217</v>
-      </c>
-      <c r="C8" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>197</v>
+        <v>183</v>
       </c>
       <c r="B9" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="C9" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="B10" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -12013,27 +12180,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
@@ -12047,10 +12214,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
@@ -12074,10 +12241,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -12239,34 +12406,34 @@
         <v>23</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>228</v>
+        <v>214</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>231</v>
+        <v>217</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>232</v>
+        <v>218</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>233</v>
+        <v>219</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>234</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -12276,10 +12443,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P5"/>
+  <dimension ref="A1:O60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.44140625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -12317,207 +12488,1574 @@
         <v>33</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
         <v>36</v>
       </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="D2">
+        <v>2</v>
+      </c>
+      <c r="E2">
         <v>40</v>
       </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
       <c r="H2">
         <v>1</v>
       </c>
       <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" t="s">
-        <v>42</v>
+        <v>81.599999999999994</v>
       </c>
       <c r="O2" t="s">
-        <v>43</v>
-      </c>
-      <c r="P2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>223</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" t="s">
-        <v>50</v>
+        <v>36</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>24</v>
+      </c>
+      <c r="F3">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
       <c r="J3">
         <v>1</v>
       </c>
       <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3" t="s">
-        <v>51</v>
-      </c>
-      <c r="N3" t="s">
-        <v>14</v>
+        <v>83.57</v>
       </c>
       <c r="O3" t="s">
-        <v>48</v>
-      </c>
-      <c r="P3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>224</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-      <c r="G4" t="s">
-        <v>12</v>
+        <v>36</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>24</v>
+      </c>
+      <c r="F4">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
       </c>
       <c r="H4">
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4" t="s">
-        <v>56</v>
-      </c>
-      <c r="N4" t="s">
-        <v>14</v>
+        <v>87.25</v>
       </c>
       <c r="O4" t="s">
-        <v>16</v>
-      </c>
-      <c r="P4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>225</v>
+      </c>
+      <c r="C5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>24</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>87.75</v>
+      </c>
+      <c r="O5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>226</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6">
+        <v>3</v>
+      </c>
+      <c r="E6">
+        <v>30</v>
+      </c>
+      <c r="F6">
+        <v>21</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>85</v>
+      </c>
+      <c r="O6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>227</v>
+      </c>
+      <c r="C7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7">
+        <v>3</v>
+      </c>
+      <c r="E7">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>87.25</v>
+      </c>
+      <c r="O7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
+        <v>24</v>
+      </c>
+      <c r="F8">
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>86.96</v>
+      </c>
+      <c r="O8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>24</v>
+      </c>
+      <c r="F9">
+        <v>13</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>50.55</v>
+      </c>
+      <c r="O9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>230</v>
+      </c>
+      <c r="C10" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>54</v>
+      </c>
+      <c r="F10">
+        <v>20</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>116.43</v>
+      </c>
+      <c r="O10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>40</v>
+      </c>
+      <c r="F11">
+        <v>21</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <v>94.72</v>
+      </c>
+      <c r="O11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>232</v>
+      </c>
+      <c r="C12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12">
+        <v>5</v>
+      </c>
+      <c r="E12">
+        <v>120</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12">
+        <v>1</v>
+      </c>
+      <c r="K12">
+        <v>135.19999999999999</v>
+      </c>
+      <c r="L12" t="s">
+        <v>233</v>
+      </c>
+      <c r="O12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>94</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
+      </c>
+      <c r="J13">
+        <v>1</v>
+      </c>
+      <c r="K13">
+        <v>132.81</v>
+      </c>
+      <c r="L13" t="s">
+        <v>233</v>
+      </c>
+      <c r="O13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14">
+        <v>5</v>
+      </c>
+      <c r="E14">
+        <v>90</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>147.88999999999999</v>
+      </c>
+      <c r="L14" t="s">
+        <v>233</v>
+      </c>
+      <c r="O14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>235</v>
+      </c>
+      <c r="C15" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15">
+        <v>5</v>
+      </c>
+      <c r="E15">
+        <v>91</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>144.63999999999999</v>
+      </c>
+      <c r="L15" t="s">
+        <v>233</v>
+      </c>
+      <c r="O15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>236</v>
+      </c>
+      <c r="C16" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="K16">
+        <v>20.82</v>
+      </c>
+      <c r="O16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17">
+        <v>3</v>
+      </c>
+      <c r="E17">
+        <v>32</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>50.72</v>
+      </c>
+      <c r="O17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>238</v>
+      </c>
+      <c r="C18" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18">
+        <v>3</v>
+      </c>
+      <c r="E18">
+        <v>46</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>0</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="K18">
+        <v>79.3</v>
+      </c>
+      <c r="O18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19">
+        <v>3</v>
+      </c>
+      <c r="E19">
+        <v>80</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
+        <v>1</v>
+      </c>
+      <c r="I19">
+        <v>1</v>
+      </c>
+      <c r="J19">
+        <v>1</v>
+      </c>
+      <c r="K19">
+        <v>104.88</v>
+      </c>
+      <c r="O19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>240</v>
+      </c>
+      <c r="C20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20">
+        <v>3</v>
+      </c>
+      <c r="E20">
         <v>57</v>
       </c>
-      <c r="C5" t="s">
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>0</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="K20">
+        <v>80.319999999999993</v>
+      </c>
+      <c r="O20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>241</v>
+      </c>
+      <c r="C21" t="s">
+        <v>42</v>
+      </c>
+      <c r="D21">
+        <v>3</v>
+      </c>
+      <c r="E21">
+        <v>49</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21">
+        <v>77.52</v>
+      </c>
+      <c r="O21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>242</v>
+      </c>
+      <c r="C22" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22">
+        <v>3</v>
+      </c>
+      <c r="E22">
+        <v>76</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22">
+        <v>0</v>
+      </c>
+      <c r="H22">
+        <v>1</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="K22">
+        <v>105.31</v>
+      </c>
+      <c r="O22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>243</v>
+      </c>
+      <c r="C23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D23">
+        <v>4</v>
+      </c>
+      <c r="E23">
+        <v>30</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1</v>
+      </c>
+      <c r="K23">
+        <v>77.22</v>
+      </c>
+      <c r="O23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24">
+        <v>56</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1</v>
+      </c>
+      <c r="K24">
+        <v>78.69</v>
+      </c>
+      <c r="O24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25" t="s">
+        <v>42</v>
+      </c>
+      <c r="D25">
+        <v>4</v>
+      </c>
+      <c r="E25">
+        <v>56</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1</v>
+      </c>
+      <c r="K25">
+        <v>78.819999999999993</v>
+      </c>
+      <c r="O25" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" t="s">
+        <v>245</v>
+      </c>
+      <c r="C26" t="s">
+        <v>42</v>
+      </c>
+      <c r="D26">
+        <v>4</v>
+      </c>
+      <c r="E26" t="s">
+        <v>246</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>1</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26">
+        <v>1</v>
+      </c>
+      <c r="K26">
+        <v>273.13</v>
+      </c>
+      <c r="L26" t="s">
+        <v>247</v>
+      </c>
+      <c r="O26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>248</v>
+      </c>
+      <c r="C27" t="s">
+        <v>42</v>
+      </c>
+      <c r="D27">
+        <v>5</v>
+      </c>
+      <c r="E27">
+        <v>23</v>
+      </c>
+      <c r="F27">
+        <v>21</v>
+      </c>
+      <c r="H27">
+        <v>1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>80.39</v>
+      </c>
+      <c r="O27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C28" t="s">
+        <v>42</v>
+      </c>
+      <c r="D28">
+        <v>5</v>
+      </c>
+      <c r="E28">
+        <v>32</v>
+      </c>
+      <c r="F28">
+        <v>21</v>
+      </c>
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28">
+        <v>1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>78.94</v>
+      </c>
+      <c r="O28" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>250</v>
+      </c>
+      <c r="C29" t="s">
+        <v>42</v>
+      </c>
+      <c r="D29">
+        <v>5</v>
+      </c>
+      <c r="E29">
+        <v>35</v>
+      </c>
+      <c r="F29">
+        <v>26</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29">
+        <v>1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="K29">
+        <v>97.05</v>
+      </c>
+      <c r="O29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>251</v>
+      </c>
+      <c r="C30" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30">
+        <v>5</v>
+      </c>
+      <c r="E30">
+        <v>26</v>
+      </c>
+      <c r="F30">
+        <v>21</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="O30" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>252</v>
+      </c>
+      <c r="C31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31">
+        <v>1</v>
+      </c>
+      <c r="E31">
+        <v>442</v>
+      </c>
+      <c r="L31" t="s">
+        <v>253</v>
+      </c>
+      <c r="O31" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>254</v>
+      </c>
+      <c r="C32" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32">
+        <v>1</v>
+      </c>
+      <c r="O32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>284</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>32</v>
+      </c>
+      <c r="J33">
+        <v>1</v>
+      </c>
+      <c r="K33">
+        <v>70.75</v>
+      </c>
+      <c r="O33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>285</v>
+      </c>
+      <c r="C34" t="s">
+        <v>48</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="E34">
+        <v>40</v>
+      </c>
+      <c r="F34">
+        <v>21</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>1</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>98.47</v>
+      </c>
+      <c r="O34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>255</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>30</v>
+      </c>
+      <c r="K35">
+        <v>73.23</v>
+      </c>
+      <c r="O35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>256</v>
+      </c>
+      <c r="C36" t="s">
+        <v>48</v>
+      </c>
+      <c r="D36">
+        <v>1</v>
+      </c>
+      <c r="E36">
+        <v>33</v>
+      </c>
+      <c r="F36">
+        <v>13</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="K36">
+        <v>67.77</v>
+      </c>
+      <c r="O36" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>257</v>
+      </c>
+      <c r="C37" t="s">
+        <v>48</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="E37">
+        <v>40</v>
+      </c>
+      <c r="F37">
+        <v>1</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>1</v>
+      </c>
+      <c r="K37">
+        <v>149</v>
+      </c>
+      <c r="L37" t="s">
+        <v>258</v>
+      </c>
+      <c r="O37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>259</v>
+      </c>
+      <c r="C38" t="s">
+        <v>48</v>
+      </c>
+      <c r="D38">
+        <v>1</v>
+      </c>
+      <c r="E38">
+        <v>9</v>
+      </c>
+      <c r="G38">
+        <v>1</v>
+      </c>
+      <c r="L38" t="s">
+        <v>260</v>
+      </c>
+      <c r="O38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>261</v>
+      </c>
+      <c r="C39" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39">
+        <v>1</v>
+      </c>
+      <c r="E39">
+        <v>84</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>1</v>
+      </c>
+      <c r="H39">
+        <v>1</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="L39" t="s">
+        <v>262</v>
+      </c>
+      <c r="O39" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>263</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40">
+        <v>0</v>
+      </c>
+      <c r="E40">
+        <v>105</v>
+      </c>
+      <c r="O40" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>264</v>
+      </c>
+      <c r="O41" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" t="s">
+        <v>265</v>
+      </c>
+      <c r="O42" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" t="s">
+        <v>266</v>
+      </c>
+      <c r="O43" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" t="s">
+        <v>267</v>
+      </c>
+      <c r="O44" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" t="s">
+        <v>268</v>
+      </c>
+      <c r="O45" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" t="s">
+        <v>269</v>
+      </c>
+      <c r="O46" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>270</v>
+      </c>
+      <c r="O47" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" t="s">
+        <v>271</v>
+      </c>
+      <c r="O48" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" t="s">
+        <v>272</v>
+      </c>
+      <c r="O49" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" t="s">
+        <v>273</v>
+      </c>
+      <c r="O50" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" t="s">
+        <v>274</v>
+      </c>
+      <c r="O51" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" t="s">
+        <v>275</v>
+      </c>
+      <c r="O52" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>52</v>
+      </c>
+      <c r="B53" t="s">
+        <v>276</v>
+      </c>
+      <c r="O53" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>53</v>
+      </c>
+      <c r="B54" t="s">
+        <v>277</v>
+      </c>
+      <c r="O54" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>54</v>
+      </c>
+      <c r="B55" t="s">
+        <v>278</v>
+      </c>
+      <c r="O55" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>55</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>279</v>
+      </c>
+      <c r="O56" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>56</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="O57" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>57</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>281</v>
+      </c>
+      <c r="O58" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59">
         <v>58</v>
       </c>
-      <c r="D5" t="s">
+      <c r="B59" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="O59" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A60">
         <v>59</v>
       </c>
-      <c r="E5" t="s">
-        <v>60</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" t="s">
-        <v>62</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5" t="s">
-        <v>63</v>
-      </c>
-      <c r="M5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N5" t="s">
-        <v>65</v>
-      </c>
-      <c r="O5" t="s">
-        <v>12</v>
-      </c>
-      <c r="P5" t="s">
-        <v>44</v>
+      <c r="B60" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="O60" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -12532,10 +14070,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -12543,7 +14081,7 @@
         <v>45993</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -12551,7 +14089,7 @@
         <v>46086</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -12559,7 +14097,7 @@
         <v>46099</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -12567,7 +14105,7 @@
         <v>46163</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -12582,18 +14120,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2">
         <v>45901</v>
@@ -12614,13 +14152,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -12628,7 +14166,7 @@
         <v>45901</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C2" t="s">
         <v>12</v>
@@ -12639,7 +14177,7 @@
         <v>45902</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C3" t="s">
         <v>16</v>
@@ -12650,10 +14188,10 @@
         <v>45903</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -12661,10 +14199,10 @@
         <v>45904</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -12672,10 +14210,10 @@
         <v>45905</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -12683,7 +14221,7 @@
         <v>45906</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
@@ -12694,10 +14232,10 @@
         <v>45907</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -12705,7 +14243,7 @@
         <v>45908</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C9" t="s">
         <v>12</v>
@@ -12716,7 +14254,7 @@
         <v>45909</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
@@ -12727,10 +14265,10 @@
         <v>45910</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -12738,10 +14276,10 @@
         <v>45911</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -12749,10 +14287,10 @@
         <v>45912</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -12760,7 +14298,7 @@
         <v>45913</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C14" t="s">
         <v>13</v>
@@ -12771,10 +14309,10 @@
         <v>45914</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C15" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -12782,7 +14320,7 @@
         <v>45915</v>
       </c>
       <c r="B16" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
         <v>12</v>
@@ -12793,7 +14331,7 @@
         <v>45916</v>
       </c>
       <c r="B17" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C17" t="s">
         <v>16</v>
@@ -12804,10 +14342,10 @@
         <v>45917</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C18" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -12815,10 +14353,10 @@
         <v>45918</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C19" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -12826,10 +14364,10 @@
         <v>45919</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -12837,7 +14375,7 @@
         <v>45920</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
         <v>13</v>
@@ -12848,10 +14386,10 @@
         <v>45921</v>
       </c>
       <c r="B22" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -12859,7 +14397,7 @@
         <v>45922</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
@@ -12870,7 +14408,7 @@
         <v>45923</v>
       </c>
       <c r="B24" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
         <v>16</v>
@@ -12881,10 +14419,10 @@
         <v>45924</v>
       </c>
       <c r="B25" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -12892,10 +14430,10 @@
         <v>45925</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -12903,10 +14441,10 @@
         <v>45926</v>
       </c>
       <c r="B27" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -12914,7 +14452,7 @@
         <v>45927</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
         <v>13</v>
@@ -12925,10 +14463,10 @@
         <v>45928</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -12936,7 +14474,7 @@
         <v>45929</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -12947,7 +14485,7 @@
         <v>45930</v>
       </c>
       <c r="B31" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C31" t="s">
         <v>16</v>
@@ -12958,10 +14496,10 @@
         <v>45931</v>
       </c>
       <c r="B32" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C32" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -12969,10 +14507,10 @@
         <v>45932</v>
       </c>
       <c r="B33" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -12980,10 +14518,10 @@
         <v>45933</v>
       </c>
       <c r="B34" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C34" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -12991,7 +14529,7 @@
         <v>45934</v>
       </c>
       <c r="B35" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C35" t="s">
         <v>13</v>
@@ -13002,10 +14540,10 @@
         <v>45935</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C36" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -13013,7 +14551,7 @@
         <v>45936</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C37" t="s">
         <v>12</v>
@@ -13024,7 +14562,7 @@
         <v>45937</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C38" t="s">
         <v>16</v>
@@ -13035,10 +14573,10 @@
         <v>45938</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -13046,10 +14584,10 @@
         <v>45939</v>
       </c>
       <c r="B40" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C40" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -13057,10 +14595,10 @@
         <v>45940</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C41" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -13068,7 +14606,7 @@
         <v>45941</v>
       </c>
       <c r="B42" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C42" t="s">
         <v>13</v>
@@ -13079,10 +14617,10 @@
         <v>45942</v>
       </c>
       <c r="B43" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C43" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -13090,7 +14628,7 @@
         <v>45943</v>
       </c>
       <c r="B44" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -13101,7 +14639,7 @@
         <v>45944</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C45" t="s">
         <v>16</v>
@@ -13112,10 +14650,10 @@
         <v>45945</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C46" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -13123,10 +14661,10 @@
         <v>45946</v>
       </c>
       <c r="B47" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -13134,10 +14672,10 @@
         <v>45947</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C48" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -13145,7 +14683,7 @@
         <v>45948</v>
       </c>
       <c r="B49" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C49" t="s">
         <v>13</v>
@@ -13156,10 +14694,10 @@
         <v>45949</v>
       </c>
       <c r="B50" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C50" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -13167,7 +14705,7 @@
         <v>45950</v>
       </c>
       <c r="B51" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C51" t="s">
         <v>12</v>
@@ -13178,7 +14716,7 @@
         <v>45951</v>
       </c>
       <c r="B52" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C52" t="s">
         <v>16</v>
@@ -13189,10 +14727,10 @@
         <v>45952</v>
       </c>
       <c r="B53" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C53" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -13200,10 +14738,10 @@
         <v>45953</v>
       </c>
       <c r="B54" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C54" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -13211,10 +14749,10 @@
         <v>45954</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -13222,7 +14760,7 @@
         <v>45955</v>
       </c>
       <c r="B56" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C56" t="s">
         <v>13</v>
@@ -13233,10 +14771,10 @@
         <v>45956</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C57" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -13244,7 +14782,7 @@
         <v>45957</v>
       </c>
       <c r="B58" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C58" t="s">
         <v>12</v>
@@ -13255,7 +14793,7 @@
         <v>45958</v>
       </c>
       <c r="B59" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C59" t="s">
         <v>16</v>
@@ -13266,10 +14804,10 @@
         <v>45959</v>
       </c>
       <c r="B60" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C60" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -13277,10 +14815,10 @@
         <v>45960</v>
       </c>
       <c r="B61" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C61" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -13288,10 +14826,10 @@
         <v>45961</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C62" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -13299,7 +14837,7 @@
         <v>45962</v>
       </c>
       <c r="B63" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C63" t="s">
         <v>13</v>
@@ -13310,10 +14848,10 @@
         <v>45963</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C64" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -13321,7 +14859,7 @@
         <v>45964</v>
       </c>
       <c r="B65" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C65" t="s">
         <v>12</v>
@@ -13332,7 +14870,7 @@
         <v>45965</v>
       </c>
       <c r="B66" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C66" t="s">
         <v>16</v>
@@ -13343,10 +14881,10 @@
         <v>45966</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C67" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -13354,10 +14892,10 @@
         <v>45967</v>
       </c>
       <c r="B68" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C68" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -13365,10 +14903,10 @@
         <v>45968</v>
       </c>
       <c r="B69" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C69" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -13376,7 +14914,7 @@
         <v>45969</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C70" t="s">
         <v>13</v>
@@ -13387,10 +14925,10 @@
         <v>45970</v>
       </c>
       <c r="B71" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C71" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -13398,7 +14936,7 @@
         <v>45971</v>
       </c>
       <c r="B72" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C72" t="s">
         <v>12</v>
@@ -13409,7 +14947,7 @@
         <v>45972</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C73" t="s">
         <v>16</v>
@@ -13420,10 +14958,10 @@
         <v>45973</v>
       </c>
       <c r="B74" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C74" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -13431,10 +14969,10 @@
         <v>45974</v>
       </c>
       <c r="B75" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C75" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -13442,10 +14980,10 @@
         <v>45975</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C76" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -13453,7 +14991,7 @@
         <v>45976</v>
       </c>
       <c r="B77" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C77" t="s">
         <v>13</v>
@@ -13464,10 +15002,10 @@
         <v>45977</v>
       </c>
       <c r="B78" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C78" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -13475,7 +15013,7 @@
         <v>45978</v>
       </c>
       <c r="B79" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C79" t="s">
         <v>12</v>
@@ -13486,7 +15024,7 @@
         <v>45979</v>
       </c>
       <c r="B80" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C80" t="s">
         <v>16</v>
@@ -13497,10 +15035,10 @@
         <v>45980</v>
       </c>
       <c r="B81" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C81" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -13508,10 +15046,10 @@
         <v>45981</v>
       </c>
       <c r="B82" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C82" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -13519,10 +15057,10 @@
         <v>45982</v>
       </c>
       <c r="B83" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C83" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -13530,7 +15068,7 @@
         <v>45983</v>
       </c>
       <c r="B84" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C84" t="s">
         <v>13</v>
@@ -13541,10 +15079,10 @@
         <v>45984</v>
       </c>
       <c r="B85" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C85" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -13552,7 +15090,7 @@
         <v>45985</v>
       </c>
       <c r="B86" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C86" t="s">
         <v>12</v>
@@ -13563,7 +15101,7 @@
         <v>45986</v>
       </c>
       <c r="B87" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C87" t="s">
         <v>16</v>
@@ -13574,10 +15112,10 @@
         <v>45987</v>
       </c>
       <c r="B88" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C88" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -13585,10 +15123,10 @@
         <v>45988</v>
       </c>
       <c r="B89" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C89" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -13596,10 +15134,10 @@
         <v>45989</v>
       </c>
       <c r="B90" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C90" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -13607,7 +15145,7 @@
         <v>45990</v>
       </c>
       <c r="B91" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C91" t="s">
         <v>13</v>
@@ -13618,10 +15156,10 @@
         <v>45991</v>
       </c>
       <c r="B92" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C92" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -13629,7 +15167,7 @@
         <v>45992</v>
       </c>
       <c r="B93" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C93" t="s">
         <v>12</v>
@@ -13640,7 +15178,7 @@
         <v>45993</v>
       </c>
       <c r="B94" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C94" t="s">
         <v>16</v>
@@ -13651,10 +15189,10 @@
         <v>45994</v>
       </c>
       <c r="B95" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C95" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -13662,10 +15200,10 @@
         <v>45995</v>
       </c>
       <c r="B96" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C96" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -13673,10 +15211,10 @@
         <v>45996</v>
       </c>
       <c r="B97" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C97" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -13684,7 +15222,7 @@
         <v>45997</v>
       </c>
       <c r="B98" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C98" t="s">
         <v>13</v>
@@ -13695,10 +15233,10 @@
         <v>45998</v>
       </c>
       <c r="B99" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C99" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -13706,7 +15244,7 @@
         <v>45999</v>
       </c>
       <c r="B100" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C100" t="s">
         <v>12</v>
@@ -13717,7 +15255,7 @@
         <v>46000</v>
       </c>
       <c r="B101" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C101" t="s">
         <v>16</v>
@@ -13728,10 +15266,10 @@
         <v>46001</v>
       </c>
       <c r="B102" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C102" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -13739,10 +15277,10 @@
         <v>46002</v>
       </c>
       <c r="B103" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C103" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -13750,10 +15288,10 @@
         <v>46003</v>
       </c>
       <c r="B104" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C104" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
@@ -13761,7 +15299,7 @@
         <v>46004</v>
       </c>
       <c r="B105" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C105" t="s">
         <v>13</v>
@@ -13772,10 +15310,10 @@
         <v>46005</v>
       </c>
       <c r="B106" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C106" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -13783,7 +15321,7 @@
         <v>46006</v>
       </c>
       <c r="B107" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C107" t="s">
         <v>12</v>
@@ -13794,7 +15332,7 @@
         <v>46007</v>
       </c>
       <c r="B108" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C108" t="s">
         <v>16</v>
@@ -13805,10 +15343,10 @@
         <v>46008</v>
       </c>
       <c r="B109" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C109" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -13816,10 +15354,10 @@
         <v>46009</v>
       </c>
       <c r="B110" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C110" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -13827,10 +15365,10 @@
         <v>46010</v>
       </c>
       <c r="B111" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C111" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -13838,7 +15376,7 @@
         <v>46011</v>
       </c>
       <c r="B112" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C112" t="s">
         <v>13</v>
@@ -13849,10 +15387,10 @@
         <v>46012</v>
       </c>
       <c r="B113" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C113" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -13860,7 +15398,7 @@
         <v>46013</v>
       </c>
       <c r="B114" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C114" t="s">
         <v>12</v>
@@ -13871,7 +15409,7 @@
         <v>46014</v>
       </c>
       <c r="B115" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C115" t="s">
         <v>16</v>
@@ -13882,10 +15420,10 @@
         <v>46015</v>
       </c>
       <c r="B116" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C116" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -13893,10 +15431,10 @@
         <v>46016</v>
       </c>
       <c r="B117" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C117" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -13904,10 +15442,10 @@
         <v>46017</v>
       </c>
       <c r="B118" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C118" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -13915,7 +15453,7 @@
         <v>46018</v>
       </c>
       <c r="B119" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C119" t="s">
         <v>13</v>
@@ -13926,10 +15464,10 @@
         <v>46019</v>
       </c>
       <c r="B120" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C120" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -13937,7 +15475,7 @@
         <v>46020</v>
       </c>
       <c r="B121" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C121" t="s">
         <v>12</v>
@@ -13948,7 +15486,7 @@
         <v>46021</v>
       </c>
       <c r="B122" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C122" t="s">
         <v>16</v>
@@ -13959,10 +15497,10 @@
         <v>46022</v>
       </c>
       <c r="B123" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C123" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
@@ -13970,10 +15508,10 @@
         <v>46023</v>
       </c>
       <c r="B124" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C124" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
@@ -13981,10 +15519,10 @@
         <v>46024</v>
       </c>
       <c r="B125" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C125" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -13992,7 +15530,7 @@
         <v>46025</v>
       </c>
       <c r="B126" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C126" t="s">
         <v>13</v>
@@ -14003,10 +15541,10 @@
         <v>46026</v>
       </c>
       <c r="B127" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C127" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -14014,7 +15552,7 @@
         <v>46027</v>
       </c>
       <c r="B128" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C128" t="s">
         <v>12</v>
@@ -14025,7 +15563,7 @@
         <v>46028</v>
       </c>
       <c r="B129" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C129" t="s">
         <v>16</v>
@@ -14036,10 +15574,10 @@
         <v>46029</v>
       </c>
       <c r="B130" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C130" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -14047,10 +15585,10 @@
         <v>46030</v>
       </c>
       <c r="B131" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C131" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -14058,10 +15596,10 @@
         <v>46031</v>
       </c>
       <c r="B132" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C132" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -14069,7 +15607,7 @@
         <v>46032</v>
       </c>
       <c r="B133" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C133" t="s">
         <v>13</v>
@@ -14080,10 +15618,10 @@
         <v>46033</v>
       </c>
       <c r="B134" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C134" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -14091,7 +15629,7 @@
         <v>46034</v>
       </c>
       <c r="B135" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C135" t="s">
         <v>12</v>
@@ -14102,7 +15640,7 @@
         <v>46035</v>
       </c>
       <c r="B136" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C136" t="s">
         <v>16</v>
@@ -14113,10 +15651,10 @@
         <v>46036</v>
       </c>
       <c r="B137" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C137" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -14124,10 +15662,10 @@
         <v>46037</v>
       </c>
       <c r="B138" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C138" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -14135,10 +15673,10 @@
         <v>46038</v>
       </c>
       <c r="B139" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C139" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -14146,7 +15684,7 @@
         <v>46039</v>
       </c>
       <c r="B140" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C140" t="s">
         <v>13</v>
@@ -14157,10 +15695,10 @@
         <v>46040</v>
       </c>
       <c r="B141" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C141" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -14168,7 +15706,7 @@
         <v>46041</v>
       </c>
       <c r="B142" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C142" t="s">
         <v>12</v>
@@ -14179,7 +15717,7 @@
         <v>46042</v>
       </c>
       <c r="B143" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C143" t="s">
         <v>16</v>
@@ -14190,10 +15728,10 @@
         <v>46043</v>
       </c>
       <c r="B144" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C144" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -14201,10 +15739,10 @@
         <v>46044</v>
       </c>
       <c r="B145" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C145" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
@@ -14212,10 +15750,10 @@
         <v>46045</v>
       </c>
       <c r="B146" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C146" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
@@ -14223,7 +15761,7 @@
         <v>46046</v>
       </c>
       <c r="B147" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C147" t="s">
         <v>13</v>
@@ -14234,10 +15772,10 @@
         <v>46047</v>
       </c>
       <c r="B148" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C148" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
@@ -14245,7 +15783,7 @@
         <v>46048</v>
       </c>
       <c r="B149" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C149" t="s">
         <v>12</v>
@@ -14256,7 +15794,7 @@
         <v>46049</v>
       </c>
       <c r="B150" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C150" t="s">
         <v>16</v>
@@ -14267,10 +15805,10 @@
         <v>46050</v>
       </c>
       <c r="B151" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C151" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
@@ -14278,10 +15816,10 @@
         <v>46051</v>
       </c>
       <c r="B152" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C152" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
@@ -14289,10 +15827,10 @@
         <v>46052</v>
       </c>
       <c r="B153" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C153" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
@@ -14300,7 +15838,7 @@
         <v>46053</v>
       </c>
       <c r="B154" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C154" t="s">
         <v>13</v>
@@ -14311,10 +15849,10 @@
         <v>46054</v>
       </c>
       <c r="B155" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C155" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
@@ -14322,7 +15860,7 @@
         <v>46055</v>
       </c>
       <c r="B156" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C156" t="s">
         <v>12</v>
@@ -14333,7 +15871,7 @@
         <v>46056</v>
       </c>
       <c r="B157" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C157" t="s">
         <v>16</v>
@@ -14344,10 +15882,10 @@
         <v>46057</v>
       </c>
       <c r="B158" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C158" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
@@ -14355,10 +15893,10 @@
         <v>46058</v>
       </c>
       <c r="B159" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C159" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
@@ -14366,10 +15904,10 @@
         <v>46059</v>
       </c>
       <c r="B160" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C160" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
@@ -14377,7 +15915,7 @@
         <v>46060</v>
       </c>
       <c r="B161" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C161" t="s">
         <v>13</v>
@@ -14388,10 +15926,10 @@
         <v>46061</v>
       </c>
       <c r="B162" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C162" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
@@ -14399,7 +15937,7 @@
         <v>46062</v>
       </c>
       <c r="B163" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C163" t="s">
         <v>12</v>
@@ -14410,7 +15948,7 @@
         <v>46063</v>
       </c>
       <c r="B164" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C164" t="s">
         <v>16</v>
@@ -14421,10 +15959,10 @@
         <v>46064</v>
       </c>
       <c r="B165" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C165" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
@@ -14432,10 +15970,10 @@
         <v>46065</v>
       </c>
       <c r="B166" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C166" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
@@ -14443,10 +15981,10 @@
         <v>46066</v>
       </c>
       <c r="B167" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C167" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
@@ -14454,7 +15992,7 @@
         <v>46067</v>
       </c>
       <c r="B168" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C168" t="s">
         <v>13</v>
@@ -14465,10 +16003,10 @@
         <v>46068</v>
       </c>
       <c r="B169" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C169" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -14476,7 +16014,7 @@
         <v>46069</v>
       </c>
       <c r="B170" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C170" t="s">
         <v>12</v>
@@ -14487,7 +16025,7 @@
         <v>46070</v>
       </c>
       <c r="B171" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C171" t="s">
         <v>16</v>
@@ -14498,10 +16036,10 @@
         <v>46071</v>
       </c>
       <c r="B172" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C172" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
@@ -14509,10 +16047,10 @@
         <v>46072</v>
       </c>
       <c r="B173" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C173" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
@@ -14520,10 +16058,10 @@
         <v>46073</v>
       </c>
       <c r="B174" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C174" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
@@ -14531,7 +16069,7 @@
         <v>46074</v>
       </c>
       <c r="B175" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C175" t="s">
         <v>13</v>
@@ -14542,10 +16080,10 @@
         <v>46075</v>
       </c>
       <c r="B176" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C176" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
@@ -14553,7 +16091,7 @@
         <v>46076</v>
       </c>
       <c r="B177" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C177" t="s">
         <v>12</v>
@@ -14564,7 +16102,7 @@
         <v>46077</v>
       </c>
       <c r="B178" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C178" t="s">
         <v>16</v>
@@ -14575,10 +16113,10 @@
         <v>46078</v>
       </c>
       <c r="B179" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C179" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
@@ -14586,10 +16124,10 @@
         <v>46079</v>
       </c>
       <c r="B180" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C180" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -14597,10 +16135,10 @@
         <v>46080</v>
       </c>
       <c r="B181" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C181" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
@@ -14608,7 +16146,7 @@
         <v>46081</v>
       </c>
       <c r="B182" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C182" t="s">
         <v>13</v>
@@ -14619,10 +16157,10 @@
         <v>46082</v>
       </c>
       <c r="B183" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C183" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
@@ -14630,7 +16168,7 @@
         <v>46083</v>
       </c>
       <c r="B184" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C184" t="s">
         <v>12</v>
@@ -14641,7 +16179,7 @@
         <v>46084</v>
       </c>
       <c r="B185" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C185" t="s">
         <v>16</v>
@@ -14652,10 +16190,10 @@
         <v>46085</v>
       </c>
       <c r="B186" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C186" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
@@ -14663,10 +16201,10 @@
         <v>46086</v>
       </c>
       <c r="B187" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C187" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
@@ -14674,10 +16212,10 @@
         <v>46087</v>
       </c>
       <c r="B188" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C188" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
@@ -14685,7 +16223,7 @@
         <v>46088</v>
       </c>
       <c r="B189" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C189" t="s">
         <v>13</v>
@@ -14696,10 +16234,10 @@
         <v>46089</v>
       </c>
       <c r="B190" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C190" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
@@ -14707,7 +16245,7 @@
         <v>46090</v>
       </c>
       <c r="B191" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C191" t="s">
         <v>12</v>
@@ -14718,7 +16256,7 @@
         <v>46091</v>
       </c>
       <c r="B192" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C192" t="s">
         <v>16</v>
@@ -14729,10 +16267,10 @@
         <v>46092</v>
       </c>
       <c r="B193" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C193" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
@@ -14740,10 +16278,10 @@
         <v>46093</v>
       </c>
       <c r="B194" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C194" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
@@ -14751,10 +16289,10 @@
         <v>46094</v>
       </c>
       <c r="B195" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C195" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
@@ -14762,7 +16300,7 @@
         <v>46095</v>
       </c>
       <c r="B196" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C196" t="s">
         <v>13</v>
@@ -14773,10 +16311,10 @@
         <v>46096</v>
       </c>
       <c r="B197" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C197" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
@@ -14784,7 +16322,7 @@
         <v>46097</v>
       </c>
       <c r="B198" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C198" t="s">
         <v>12</v>
@@ -14795,7 +16333,7 @@
         <v>46098</v>
       </c>
       <c r="B199" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C199" t="s">
         <v>16</v>
@@ -14806,10 +16344,10 @@
         <v>46099</v>
       </c>
       <c r="B200" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C200" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
@@ -14817,10 +16355,10 @@
         <v>46100</v>
       </c>
       <c r="B201" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C201" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
@@ -14828,10 +16366,10 @@
         <v>46101</v>
       </c>
       <c r="B202" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C202" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
@@ -14839,7 +16377,7 @@
         <v>46102</v>
       </c>
       <c r="B203" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C203" t="s">
         <v>13</v>
@@ -14850,10 +16388,10 @@
         <v>46103</v>
       </c>
       <c r="B204" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C204" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
@@ -14861,7 +16399,7 @@
         <v>46104</v>
       </c>
       <c r="B205" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C205" t="s">
         <v>12</v>
@@ -14872,7 +16410,7 @@
         <v>46105</v>
       </c>
       <c r="B206" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C206" t="s">
         <v>16</v>
@@ -14883,10 +16421,10 @@
         <v>46106</v>
       </c>
       <c r="B207" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C207" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
@@ -14894,10 +16432,10 @@
         <v>46107</v>
       </c>
       <c r="B208" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C208" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
@@ -14905,10 +16443,10 @@
         <v>46108</v>
       </c>
       <c r="B209" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C209" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
@@ -14916,7 +16454,7 @@
         <v>46109</v>
       </c>
       <c r="B210" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C210" t="s">
         <v>13</v>
@@ -14927,10 +16465,10 @@
         <v>46110</v>
       </c>
       <c r="B211" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C211" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
@@ -14938,7 +16476,7 @@
         <v>46111</v>
       </c>
       <c r="B212" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C212" t="s">
         <v>12</v>
@@ -14949,7 +16487,7 @@
         <v>46112</v>
       </c>
       <c r="B213" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C213" t="s">
         <v>16</v>
@@ -14960,10 +16498,10 @@
         <v>46113</v>
       </c>
       <c r="B214" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C214" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
@@ -14971,10 +16509,10 @@
         <v>46114</v>
       </c>
       <c r="B215" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C215" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
@@ -14982,10 +16520,10 @@
         <v>46115</v>
       </c>
       <c r="B216" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C216" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
@@ -14993,7 +16531,7 @@
         <v>46116</v>
       </c>
       <c r="B217" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C217" t="s">
         <v>13</v>
@@ -15004,10 +16542,10 @@
         <v>46117</v>
       </c>
       <c r="B218" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C218" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
@@ -15015,7 +16553,7 @@
         <v>46118</v>
       </c>
       <c r="B219" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C219" t="s">
         <v>12</v>
@@ -15026,7 +16564,7 @@
         <v>46119</v>
       </c>
       <c r="B220" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C220" t="s">
         <v>16</v>
@@ -15037,10 +16575,10 @@
         <v>46120</v>
       </c>
       <c r="B221" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C221" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
@@ -15048,10 +16586,10 @@
         <v>46121</v>
       </c>
       <c r="B222" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C222" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
@@ -15059,10 +16597,10 @@
         <v>46122</v>
       </c>
       <c r="B223" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C223" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
@@ -15070,7 +16608,7 @@
         <v>46123</v>
       </c>
       <c r="B224" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C224" t="s">
         <v>13</v>
@@ -15081,10 +16619,10 @@
         <v>46124</v>
       </c>
       <c r="B225" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C225" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
@@ -15092,7 +16630,7 @@
         <v>46125</v>
       </c>
       <c r="B226" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C226" t="s">
         <v>12</v>
@@ -15103,7 +16641,7 @@
         <v>46126</v>
       </c>
       <c r="B227" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C227" t="s">
         <v>16</v>
@@ -15114,10 +16652,10 @@
         <v>46127</v>
       </c>
       <c r="B228" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C228" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
@@ -15125,10 +16663,10 @@
         <v>46128</v>
       </c>
       <c r="B229" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C229" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
@@ -15136,10 +16674,10 @@
         <v>46129</v>
       </c>
       <c r="B230" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C230" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
@@ -15147,7 +16685,7 @@
         <v>46130</v>
       </c>
       <c r="B231" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C231" t="s">
         <v>13</v>
@@ -15158,10 +16696,10 @@
         <v>46131</v>
       </c>
       <c r="B232" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C232" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
@@ -15169,7 +16707,7 @@
         <v>46132</v>
       </c>
       <c r="B233" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C233" t="s">
         <v>12</v>
@@ -15180,7 +16718,7 @@
         <v>46133</v>
       </c>
       <c r="B234" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C234" t="s">
         <v>16</v>
@@ -15191,10 +16729,10 @@
         <v>46134</v>
       </c>
       <c r="B235" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C235" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
@@ -15202,10 +16740,10 @@
         <v>46135</v>
       </c>
       <c r="B236" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C236" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
@@ -15213,10 +16751,10 @@
         <v>46136</v>
       </c>
       <c r="B237" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C237" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
@@ -15224,7 +16762,7 @@
         <v>46137</v>
       </c>
       <c r="B238" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C238" t="s">
         <v>13</v>
@@ -15235,10 +16773,10 @@
         <v>46138</v>
       </c>
       <c r="B239" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C239" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
@@ -15246,7 +16784,7 @@
         <v>46139</v>
       </c>
       <c r="B240" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C240" t="s">
         <v>12</v>
@@ -15257,7 +16795,7 @@
         <v>46140</v>
       </c>
       <c r="B241" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C241" t="s">
         <v>16</v>
@@ -15268,10 +16806,10 @@
         <v>46141</v>
       </c>
       <c r="B242" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C242" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
@@ -15279,10 +16817,10 @@
         <v>46142</v>
       </c>
       <c r="B243" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C243" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
@@ -15290,10 +16828,10 @@
         <v>46143</v>
       </c>
       <c r="B244" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C244" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
@@ -15301,7 +16839,7 @@
         <v>46144</v>
       </c>
       <c r="B245" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C245" t="s">
         <v>13</v>
@@ -15312,10 +16850,10 @@
         <v>46145</v>
       </c>
       <c r="B246" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C246" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
@@ -15323,7 +16861,7 @@
         <v>46146</v>
       </c>
       <c r="B247" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C247" t="s">
         <v>12</v>
@@ -15334,7 +16872,7 @@
         <v>46147</v>
       </c>
       <c r="B248" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C248" t="s">
         <v>16</v>
@@ -15345,10 +16883,10 @@
         <v>46148</v>
       </c>
       <c r="B249" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C249" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
@@ -15356,10 +16894,10 @@
         <v>46149</v>
       </c>
       <c r="B250" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C250" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
@@ -15367,10 +16905,10 @@
         <v>46150</v>
       </c>
       <c r="B251" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C251" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
@@ -15378,7 +16916,7 @@
         <v>46151</v>
       </c>
       <c r="B252" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C252" t="s">
         <v>13</v>
@@ -15389,10 +16927,10 @@
         <v>46152</v>
       </c>
       <c r="B253" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C253" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
@@ -15400,7 +16938,7 @@
         <v>46153</v>
       </c>
       <c r="B254" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C254" t="s">
         <v>12</v>
@@ -15411,7 +16949,7 @@
         <v>46154</v>
       </c>
       <c r="B255" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C255" t="s">
         <v>16</v>
@@ -15422,10 +16960,10 @@
         <v>46155</v>
       </c>
       <c r="B256" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C256" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
@@ -15433,10 +16971,10 @@
         <v>46156</v>
       </c>
       <c r="B257" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C257" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
@@ -15444,10 +16982,10 @@
         <v>46157</v>
       </c>
       <c r="B258" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C258" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
@@ -15455,7 +16993,7 @@
         <v>46158</v>
       </c>
       <c r="B259" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C259" t="s">
         <v>13</v>
@@ -15466,10 +17004,10 @@
         <v>46159</v>
       </c>
       <c r="B260" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C260" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
@@ -15477,7 +17015,7 @@
         <v>46160</v>
       </c>
       <c r="B261" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C261" t="s">
         <v>12</v>
@@ -15488,7 +17026,7 @@
         <v>46161</v>
       </c>
       <c r="B262" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C262" t="s">
         <v>16</v>
@@ -15499,10 +17037,10 @@
         <v>46162</v>
       </c>
       <c r="B263" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C263" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
@@ -15510,10 +17048,10 @@
         <v>46163</v>
       </c>
       <c r="B264" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C264" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
@@ -15521,10 +17059,10 @@
         <v>46164</v>
       </c>
       <c r="B265" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C265" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
@@ -15532,7 +17070,7 @@
         <v>46165</v>
       </c>
       <c r="B266" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C266" t="s">
         <v>13</v>
@@ -15543,10 +17081,10 @@
         <v>46166</v>
       </c>
       <c r="B267" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C267" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
@@ -15554,7 +17092,7 @@
         <v>46167</v>
       </c>
       <c r="B268" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C268" t="s">
         <v>12</v>
@@ -15565,7 +17103,7 @@
         <v>46168</v>
       </c>
       <c r="B269" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C269" t="s">
         <v>16</v>
@@ -15576,10 +17114,10 @@
         <v>46169</v>
       </c>
       <c r="B270" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C270" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
@@ -15587,10 +17125,10 @@
         <v>46170</v>
       </c>
       <c r="B271" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C271" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
@@ -15598,10 +17136,10 @@
         <v>46171</v>
       </c>
       <c r="B272" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C272" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
@@ -15609,7 +17147,7 @@
         <v>46172</v>
       </c>
       <c r="B273" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C273" t="s">
         <v>13</v>
@@ -15620,10 +17158,10 @@
         <v>46173</v>
       </c>
       <c r="B274" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C274" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
@@ -15631,7 +17169,7 @@
         <v>46174</v>
       </c>
       <c r="B275" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C275" t="s">
         <v>12</v>
@@ -15642,7 +17180,7 @@
         <v>46175</v>
       </c>
       <c r="B276" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C276" t="s">
         <v>16</v>
@@ -15653,10 +17191,10 @@
         <v>46176</v>
       </c>
       <c r="B277" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C277" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
@@ -15664,10 +17202,10 @@
         <v>46177</v>
       </c>
       <c r="B278" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C278" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
@@ -15675,10 +17213,10 @@
         <v>46178</v>
       </c>
       <c r="B279" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C279" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
@@ -15686,7 +17224,7 @@
         <v>46179</v>
       </c>
       <c r="B280" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C280" t="s">
         <v>13</v>
@@ -15697,10 +17235,10 @@
         <v>46180</v>
       </c>
       <c r="B281" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C281" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
@@ -15708,7 +17246,7 @@
         <v>46181</v>
       </c>
       <c r="B282" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C282" t="s">
         <v>12</v>
@@ -15719,7 +17257,7 @@
         <v>46182</v>
       </c>
       <c r="B283" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C283" t="s">
         <v>16</v>
@@ -15730,10 +17268,10 @@
         <v>46183</v>
       </c>
       <c r="B284" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C284" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
@@ -15741,10 +17279,10 @@
         <v>46184</v>
       </c>
       <c r="B285" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C285" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
@@ -15752,10 +17290,10 @@
         <v>46185</v>
       </c>
       <c r="B286" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C286" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
@@ -15763,7 +17301,7 @@
         <v>46186</v>
       </c>
       <c r="B287" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C287" t="s">
         <v>13</v>
@@ -15774,10 +17312,10 @@
         <v>46187</v>
       </c>
       <c r="B288" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C288" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
@@ -15785,7 +17323,7 @@
         <v>46188</v>
       </c>
       <c r="B289" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C289" t="s">
         <v>12</v>
@@ -15796,7 +17334,7 @@
         <v>46189</v>
       </c>
       <c r="B290" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C290" t="s">
         <v>16</v>
@@ -15807,10 +17345,10 @@
         <v>46190</v>
       </c>
       <c r="B291" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C291" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
@@ -15818,10 +17356,10 @@
         <v>46191</v>
       </c>
       <c r="B292" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C292" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
@@ -15829,10 +17367,10 @@
         <v>46192</v>
       </c>
       <c r="B293" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C293" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
@@ -15840,7 +17378,7 @@
         <v>46193</v>
       </c>
       <c r="B294" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C294" t="s">
         <v>13</v>
@@ -15851,10 +17389,10 @@
         <v>46194</v>
       </c>
       <c r="B295" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C295" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
@@ -15862,7 +17400,7 @@
         <v>46195</v>
       </c>
       <c r="B296" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C296" t="s">
         <v>12</v>
@@ -15873,7 +17411,7 @@
         <v>46196</v>
       </c>
       <c r="B297" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C297" t="s">
         <v>16</v>
@@ -15884,10 +17422,10 @@
         <v>46197</v>
       </c>
       <c r="B298" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C298" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
@@ -15895,10 +17433,10 @@
         <v>46198</v>
       </c>
       <c r="B299" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C299" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
@@ -15906,10 +17444,10 @@
         <v>46199</v>
       </c>
       <c r="B300" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C300" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
@@ -15917,7 +17455,7 @@
         <v>46200</v>
       </c>
       <c r="B301" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C301" t="s">
         <v>13</v>
@@ -15928,10 +17466,10 @@
         <v>46201</v>
       </c>
       <c r="B302" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C302" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
@@ -15939,7 +17477,7 @@
         <v>46202</v>
       </c>
       <c r="B303" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C303" t="s">
         <v>12</v>
@@ -15950,7 +17488,7 @@
         <v>46203</v>
       </c>
       <c r="B304" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C304" t="s">
         <v>16</v>
@@ -15961,10 +17499,10 @@
         <v>46204</v>
       </c>
       <c r="B305" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C305" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
@@ -15972,10 +17510,10 @@
         <v>46205</v>
       </c>
       <c r="B306" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C306" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
@@ -15983,10 +17521,10 @@
         <v>46206</v>
       </c>
       <c r="B307" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C307" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
@@ -15994,7 +17532,7 @@
         <v>46207</v>
       </c>
       <c r="B308" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C308" t="s">
         <v>13</v>
@@ -16005,10 +17543,10 @@
         <v>46208</v>
       </c>
       <c r="B309" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C309" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
@@ -16016,7 +17554,7 @@
         <v>46209</v>
       </c>
       <c r="B310" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C310" t="s">
         <v>12</v>
@@ -16027,7 +17565,7 @@
         <v>46210</v>
       </c>
       <c r="B311" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C311" t="s">
         <v>16</v>
@@ -16038,10 +17576,10 @@
         <v>46211</v>
       </c>
       <c r="B312" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C312" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
@@ -16049,10 +17587,10 @@
         <v>46212</v>
       </c>
       <c r="B313" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C313" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
@@ -16060,10 +17598,10 @@
         <v>46213</v>
       </c>
       <c r="B314" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C314" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
@@ -16071,7 +17609,7 @@
         <v>46214</v>
       </c>
       <c r="B315" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C315" t="s">
         <v>13</v>
@@ -16082,10 +17620,10 @@
         <v>46215</v>
       </c>
       <c r="B316" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C316" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
@@ -16093,7 +17631,7 @@
         <v>46216</v>
       </c>
       <c r="B317" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C317" t="s">
         <v>12</v>
@@ -16104,7 +17642,7 @@
         <v>46217</v>
       </c>
       <c r="B318" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C318" t="s">
         <v>16</v>
@@ -16115,10 +17653,10 @@
         <v>46218</v>
       </c>
       <c r="B319" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C319" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
@@ -16126,10 +17664,10 @@
         <v>46219</v>
       </c>
       <c r="B320" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C320" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
@@ -16137,10 +17675,10 @@
         <v>46220</v>
       </c>
       <c r="B321" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C321" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
@@ -16148,7 +17686,7 @@
         <v>46221</v>
       </c>
       <c r="B322" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C322" t="s">
         <v>13</v>
@@ -16159,10 +17697,10 @@
         <v>46222</v>
       </c>
       <c r="B323" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C323" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
@@ -16170,7 +17708,7 @@
         <v>46223</v>
       </c>
       <c r="B324" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C324" t="s">
         <v>12</v>
@@ -16181,7 +17719,7 @@
         <v>46224</v>
       </c>
       <c r="B325" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C325" t="s">
         <v>16</v>
@@ -16192,10 +17730,10 @@
         <v>46225</v>
       </c>
       <c r="B326" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C326" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
@@ -16203,10 +17741,10 @@
         <v>46226</v>
       </c>
       <c r="B327" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C327" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
@@ -16214,10 +17752,10 @@
         <v>46227</v>
       </c>
       <c r="B328" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C328" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
@@ -16225,7 +17763,7 @@
         <v>46228</v>
       </c>
       <c r="B329" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C329" t="s">
         <v>13</v>
@@ -16236,10 +17774,10 @@
         <v>46229</v>
       </c>
       <c r="B330" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C330" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
@@ -16247,7 +17785,7 @@
         <v>46230</v>
       </c>
       <c r="B331" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C331" t="s">
         <v>12</v>
@@ -16258,7 +17796,7 @@
         <v>46231</v>
       </c>
       <c r="B332" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C332" t="s">
         <v>16</v>
@@ -16269,10 +17807,10 @@
         <v>46232</v>
       </c>
       <c r="B333" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C333" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
@@ -16280,10 +17818,10 @@
         <v>46233</v>
       </c>
       <c r="B334" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C334" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
@@ -16291,10 +17829,10 @@
         <v>46234</v>
       </c>
       <c r="B335" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C335" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -16309,36 +17847,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -16353,10 +17891,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -16371,13 +17909,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -16385,10 +17923,10 @@
         <v>45926</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C2" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -16396,10 +17934,10 @@
         <v>45943</v>
       </c>
       <c r="B3" t="s">
-        <v>91</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -16407,10 +17945,10 @@
         <v>45999</v>
       </c>
       <c r="B4" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C4" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -16418,10 +17956,10 @@
         <v>46050</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C5" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -16429,10 +17967,10 @@
         <v>46087</v>
       </c>
       <c r="B6" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -16440,10 +17978,10 @@
         <v>46101</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -16451,10 +17989,10 @@
         <v>46135</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C8" t="s">
-        <v>99</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -16462,10 +18000,10 @@
         <v>46143</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="C9" t="s">
-        <v>92</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -16473,10 +18011,10 @@
         <v>46185</v>
       </c>
       <c r="B10" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -16484,10 +18022,10 @@
         <v>46202</v>
       </c>
       <c r="B11" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="C11" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
@@ -16502,7 +18040,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -16511,63 +18049,63 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>109</v>
+        <v>95</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="D4" t="s">
-        <v>116</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>117</v>
+        <v>103</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>104</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>120</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -16575,27 +18113,27 @@
         <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>110</v>
       </c>
       <c r="C7" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="D7" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/app_horarios/datos/excel/export-15-04.xlsx
+++ b/app_horarios/datos/excel/export-15-04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\Ingeniería informática\4º Trabajo de Fin de Grado\Trabajo-Fin-de-Grado-2025-2026\app_horarios\datos\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{758A42FB-0A6B-41CC-94C9-A8095C3397BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D8BE3B-B62A-4F90-AC16-170140AFF7EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="asignaturas" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1851" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="583">
   <si>
     <t>IDASIGNATURA</t>
   </si>
@@ -149,9 +149,6 @@
     <t>CAMPUS</t>
   </si>
   <si>
-    <t>23-A1</t>
-  </si>
-  <si>
     <t>A1</t>
   </si>
   <si>
@@ -185,9 +182,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>Lab. Automática 1</t>
-  </si>
-  <si>
     <t>A1-A2</t>
   </si>
   <si>
@@ -401,9 +395,6 @@
     <t>IDRESERVA</t>
   </si>
   <si>
-    <t>NOMBRE_AULA</t>
-  </si>
-  <si>
     <t>ESTADO</t>
   </si>
   <si>
@@ -782,9 +773,6 @@
     <t>41-A2</t>
   </si>
   <si>
-    <t>*****</t>
-  </si>
-  <si>
     <t>TV/Sonido</t>
   </si>
   <si>
@@ -1725,6 +1713,96 @@
   </si>
   <si>
     <t>Inglés Aplicado a la Ing Mecánica</t>
+  </si>
+  <si>
+    <t>81.6</t>
+  </si>
+  <si>
+    <t>83.57</t>
+  </si>
+  <si>
+    <t>87.25</t>
+  </si>
+  <si>
+    <t>87.75</t>
+  </si>
+  <si>
+    <t>86.96</t>
+  </si>
+  <si>
+    <t>50.55</t>
+  </si>
+  <si>
+    <t>116.43</t>
+  </si>
+  <si>
+    <t>94.72</t>
+  </si>
+  <si>
+    <t>135.2</t>
+  </si>
+  <si>
+    <t>132.81</t>
+  </si>
+  <si>
+    <t>147.89</t>
+  </si>
+  <si>
+    <t>144.64</t>
+  </si>
+  <si>
+    <t>20.82</t>
+  </si>
+  <si>
+    <t>50.72</t>
+  </si>
+  <si>
+    <t>79.3</t>
+  </si>
+  <si>
+    <t>104.88</t>
+  </si>
+  <si>
+    <t>80.32</t>
+  </si>
+  <si>
+    <t>77.52</t>
+  </si>
+  <si>
+    <t>105.31</t>
+  </si>
+  <si>
+    <t>77.22</t>
+  </si>
+  <si>
+    <t>78.69</t>
+  </si>
+  <si>
+    <t>78.82</t>
+  </si>
+  <si>
+    <t>273.13</t>
+  </si>
+  <si>
+    <t>80.39</t>
+  </si>
+  <si>
+    <t>78.94</t>
+  </si>
+  <si>
+    <t>97.05</t>
+  </si>
+  <si>
+    <t>70.75</t>
+  </si>
+  <si>
+    <t>98.47</t>
+  </si>
+  <si>
+    <t>73.23</t>
+  </si>
+  <si>
+    <t>67.77</t>
   </si>
 </sst>
 </file>
@@ -2188,6 +2266,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I214"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="44.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -2223,7 +2304,7 @@
         <v>8797</v>
       </c>
       <c r="B2" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -2286,7 +2367,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2313,10 +2394,10 @@
         <v>8800</v>
       </c>
       <c r="B5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="C5" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2343,10 +2424,10 @@
         <v>8796</v>
       </c>
       <c r="B6" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C6" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2373,10 +2454,10 @@
         <v>8801</v>
       </c>
       <c r="B7" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="C7" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2403,10 +2484,10 @@
         <v>8802</v>
       </c>
       <c r="B8" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C8" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2433,10 +2514,10 @@
         <v>8803</v>
       </c>
       <c r="B9" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="C9" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2463,10 +2544,10 @@
         <v>8804</v>
       </c>
       <c r="B10" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C10" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2493,10 +2574,10 @@
         <v>8805</v>
       </c>
       <c r="B11" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C11" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2523,10 +2604,10 @@
         <v>8806</v>
       </c>
       <c r="B12" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C12" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -2553,10 +2634,10 @@
         <v>8807</v>
       </c>
       <c r="B13" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="C13" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -2583,10 +2664,10 @@
         <v>8808</v>
       </c>
       <c r="B14" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C14" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -2613,10 +2694,10 @@
         <v>8809</v>
       </c>
       <c r="B15" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C15" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -2643,10 +2724,10 @@
         <v>8810</v>
       </c>
       <c r="B16" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C16" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2673,10 +2754,10 @@
         <v>8811</v>
       </c>
       <c r="B17" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C17" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -2703,10 +2784,10 @@
         <v>8812</v>
       </c>
       <c r="B18" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="C18" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -2733,10 +2814,10 @@
         <v>8813</v>
       </c>
       <c r="B19" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="C19" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2763,10 +2844,10 @@
         <v>8814</v>
       </c>
       <c r="B20" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="C20" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -2793,10 +2874,10 @@
         <v>8815</v>
       </c>
       <c r="B21" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C21" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -2823,10 +2904,10 @@
         <v>8816</v>
       </c>
       <c r="B22" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="C22" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -2853,10 +2934,10 @@
         <v>8817</v>
       </c>
       <c r="B23" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C23" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -2883,10 +2964,10 @@
         <v>8818</v>
       </c>
       <c r="B24" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C24" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -2913,10 +2994,10 @@
         <v>8819</v>
       </c>
       <c r="B25" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C25" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -2943,10 +3024,10 @@
         <v>8820</v>
       </c>
       <c r="B26" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C26" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -2973,10 +3054,10 @@
         <v>8824</v>
       </c>
       <c r="B27" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C27" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -3003,10 +3084,10 @@
         <v>8823</v>
       </c>
       <c r="B28" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C28" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -3033,10 +3114,10 @@
         <v>8825</v>
       </c>
       <c r="B29" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C29" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -3063,10 +3144,10 @@
         <v>8821</v>
       </c>
       <c r="B30" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C30" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -3093,10 +3174,10 @@
         <v>8822</v>
       </c>
       <c r="B31" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C31" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -3123,10 +3204,10 @@
         <v>8827</v>
       </c>
       <c r="B32" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="C32" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -3142,7 +3223,7 @@
         <v>281</v>
       </c>
       <c r="H32" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I32">
         <v>2</v>
@@ -3153,10 +3234,10 @@
         <v>8828</v>
       </c>
       <c r="B33" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C33" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -3172,7 +3253,7 @@
         <v>281</v>
       </c>
       <c r="H33" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I33">
         <v>2</v>
@@ -3183,10 +3264,10 @@
         <v>8829</v>
       </c>
       <c r="B34" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C34" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -3202,7 +3283,7 @@
         <v>281</v>
       </c>
       <c r="H34" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I34">
         <v>2</v>
@@ -3213,10 +3294,10 @@
         <v>8830</v>
       </c>
       <c r="B35" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="C35" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D35">
         <v>4</v>
@@ -3232,7 +3313,7 @@
         <v>281</v>
       </c>
       <c r="H35" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I35">
         <v>2</v>
@@ -3243,10 +3324,10 @@
         <v>8831</v>
       </c>
       <c r="B36" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="C36" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -3262,7 +3343,7 @@
         <v>281</v>
       </c>
       <c r="H36" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I36">
         <v>2</v>
@@ -3273,10 +3354,10 @@
         <v>8832</v>
       </c>
       <c r="B37" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="C37" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -3292,7 +3373,7 @@
         <v>281</v>
       </c>
       <c r="H37" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I37">
         <v>2</v>
@@ -3303,10 +3384,10 @@
         <v>8833</v>
       </c>
       <c r="B38" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C38" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -3322,7 +3403,7 @@
         <v>281</v>
       </c>
       <c r="H38" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I38">
         <v>2</v>
@@ -3333,10 +3414,10 @@
         <v>8834</v>
       </c>
       <c r="B39" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="C39" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -3352,7 +3433,7 @@
         <v>281</v>
       </c>
       <c r="H39" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I39">
         <v>2</v>
@@ -3363,10 +3444,10 @@
         <v>8835</v>
       </c>
       <c r="B40" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="C40" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -3382,7 +3463,7 @@
         <v>281</v>
       </c>
       <c r="H40" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I40">
         <v>2</v>
@@ -3393,10 +3474,10 @@
         <v>8836</v>
       </c>
       <c r="B41" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="C41" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -3412,7 +3493,7 @@
         <v>281</v>
       </c>
       <c r="H41" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I41">
         <v>2</v>
@@ -3423,10 +3504,10 @@
         <v>8837</v>
       </c>
       <c r="B42" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C42" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -3442,7 +3523,7 @@
         <v>281</v>
       </c>
       <c r="H42" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I42">
         <v>2</v>
@@ -3453,10 +3534,10 @@
         <v>8838</v>
       </c>
       <c r="B43" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="C43" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -3472,7 +3553,7 @@
         <v>281</v>
       </c>
       <c r="H43" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I43">
         <v>2</v>
@@ -3483,10 +3564,10 @@
         <v>8842</v>
       </c>
       <c r="B44" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="C44" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -3502,7 +3583,7 @@
         <v>281</v>
       </c>
       <c r="H44" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I44">
         <v>2</v>
@@ -3513,10 +3594,10 @@
         <v>8843</v>
       </c>
       <c r="B45" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="C45" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -3532,7 +3613,7 @@
         <v>281</v>
       </c>
       <c r="H45" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I45">
         <v>2</v>
@@ -3543,7 +3624,7 @@
         <v>6392</v>
       </c>
       <c r="B46" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
@@ -3573,10 +3654,10 @@
         <v>6393</v>
       </c>
       <c r="B47" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C47" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -3603,10 +3684,10 @@
         <v>6394</v>
       </c>
       <c r="B48" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C48" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3633,10 +3714,10 @@
         <v>6395</v>
       </c>
       <c r="B49" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C49" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -3693,10 +3774,10 @@
         <v>6397</v>
       </c>
       <c r="B51" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C51" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -3723,10 +3804,10 @@
         <v>6398</v>
       </c>
       <c r="B52" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C52" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -3753,10 +3834,10 @@
         <v>6399</v>
       </c>
       <c r="B53" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C53" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -3783,10 +3864,10 @@
         <v>6400</v>
       </c>
       <c r="B54" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C54" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -3813,10 +3894,10 @@
         <v>6401</v>
       </c>
       <c r="B55" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C55" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3843,10 +3924,10 @@
         <v>6402</v>
       </c>
       <c r="B56" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C56" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -3873,10 +3954,10 @@
         <v>6403</v>
       </c>
       <c r="B57" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C57" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -3903,10 +3984,10 @@
         <v>6404</v>
       </c>
       <c r="B58" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C58" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -3933,10 +4014,10 @@
         <v>6405</v>
       </c>
       <c r="B59" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C59" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="D59">
         <v>2</v>
@@ -3963,10 +4044,10 @@
         <v>6406</v>
       </c>
       <c r="B60" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C60" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -3993,10 +4074,10 @@
         <v>6407</v>
       </c>
       <c r="B61" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C61" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D61">
         <v>2</v>
@@ -4023,10 +4104,10 @@
         <v>6408</v>
       </c>
       <c r="B62" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C62" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -4053,10 +4134,10 @@
         <v>6409</v>
       </c>
       <c r="B63" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C63" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -4083,10 +4164,10 @@
         <v>6410</v>
       </c>
       <c r="B64" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C64" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D64">
         <v>2</v>
@@ -4113,10 +4194,10 @@
         <v>6411</v>
       </c>
       <c r="B65" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C65" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -4143,10 +4224,10 @@
         <v>6412</v>
       </c>
       <c r="B66" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C66" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -4173,10 +4254,10 @@
         <v>6413</v>
       </c>
       <c r="B67" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C67" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="D67">
         <v>3</v>
@@ -4203,10 +4284,10 @@
         <v>6414</v>
       </c>
       <c r="B68" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C68" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D68">
         <v>3</v>
@@ -4233,10 +4314,10 @@
         <v>6415</v>
       </c>
       <c r="B69" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C69" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="D69">
         <v>3</v>
@@ -4263,10 +4344,10 @@
         <v>6416</v>
       </c>
       <c r="B70" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C70" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -4293,10 +4374,10 @@
         <v>6417</v>
       </c>
       <c r="B71" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C71" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -4323,10 +4404,10 @@
         <v>6418</v>
       </c>
       <c r="B72" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="C72" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -4353,10 +4434,10 @@
         <v>6419</v>
       </c>
       <c r="B73" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C73" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="D73">
         <v>3</v>
@@ -4383,10 +4464,10 @@
         <v>6420</v>
       </c>
       <c r="B74" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C74" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D74">
         <v>3</v>
@@ -4413,10 +4494,10 @@
         <v>6421</v>
       </c>
       <c r="B75" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C75" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D75">
         <v>3</v>
@@ -4443,10 +4524,10 @@
         <v>6422</v>
       </c>
       <c r="B76" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C76" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="D76">
         <v>4</v>
@@ -4473,10 +4554,10 @@
         <v>6423</v>
       </c>
       <c r="B77" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C77" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D77">
         <v>4</v>
@@ -4503,10 +4584,10 @@
         <v>6424</v>
       </c>
       <c r="B78" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C78" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="D78">
         <v>4</v>
@@ -4522,7 +4603,7 @@
         <v>147</v>
       </c>
       <c r="H78" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I78">
         <v>2</v>
@@ -4533,10 +4614,10 @@
         <v>6425</v>
       </c>
       <c r="B79" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="C79" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="D79">
         <v>4</v>
@@ -4552,7 +4633,7 @@
         <v>147</v>
       </c>
       <c r="H79" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I79">
         <v>2</v>
@@ -4563,10 +4644,10 @@
         <v>6426</v>
       </c>
       <c r="B80" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="C80" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D80">
         <v>4</v>
@@ -4582,7 +4663,7 @@
         <v>147</v>
       </c>
       <c r="H80" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I80">
         <v>2</v>
@@ -4593,10 +4674,10 @@
         <v>6427</v>
       </c>
       <c r="B81" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="C81" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="D81">
         <v>4</v>
@@ -4612,7 +4693,7 @@
         <v>147</v>
       </c>
       <c r="H81" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I81">
         <v>2</v>
@@ -4623,10 +4704,10 @@
         <v>6428</v>
       </c>
       <c r="B82" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="C82" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="D82">
         <v>4</v>
@@ -4642,7 +4723,7 @@
         <v>147</v>
       </c>
       <c r="H82" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I82">
         <v>2</v>
@@ -4653,10 +4734,10 @@
         <v>6429</v>
       </c>
       <c r="B83" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="C83" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D83">
         <v>4</v>
@@ -4672,7 +4753,7 @@
         <v>147</v>
       </c>
       <c r="H83" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I83">
         <v>2</v>
@@ -4683,10 +4764,10 @@
         <v>6430</v>
       </c>
       <c r="B84" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="C84" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D84">
         <v>4</v>
@@ -4702,7 +4783,7 @@
         <v>147</v>
       </c>
       <c r="H84" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I84">
         <v>2</v>
@@ -4713,10 +4794,10 @@
         <v>6431</v>
       </c>
       <c r="B85" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C85" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="D85">
         <v>4</v>
@@ -4743,10 +4824,10 @@
         <v>6432</v>
       </c>
       <c r="B86" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C86" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D86">
         <v>4</v>
@@ -4773,10 +4854,10 @@
         <v>6302</v>
       </c>
       <c r="B87" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C87" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4803,7 +4884,7 @@
         <v>6303</v>
       </c>
       <c r="B88" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C88" t="s">
         <v>9</v>
@@ -4833,10 +4914,10 @@
         <v>6304</v>
       </c>
       <c r="B89" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C89" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -4863,10 +4944,10 @@
         <v>6305</v>
       </c>
       <c r="B90" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C90" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -4893,10 +4974,10 @@
         <v>6306</v>
       </c>
       <c r="B91" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="C91" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -4923,10 +5004,10 @@
         <v>6307</v>
       </c>
       <c r="B92" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C92" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -4983,10 +5064,10 @@
         <v>6309</v>
       </c>
       <c r="B94" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C94" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -5013,10 +5094,10 @@
         <v>6310</v>
       </c>
       <c r="B95" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C95" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -5043,10 +5124,10 @@
         <v>6311</v>
       </c>
       <c r="B96" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C96" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -5073,10 +5154,10 @@
         <v>6312</v>
       </c>
       <c r="B97" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C97" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -5103,10 +5184,10 @@
         <v>6313</v>
       </c>
       <c r="B98" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C98" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -5133,10 +5214,10 @@
         <v>6314</v>
       </c>
       <c r="B99" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C99" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -5163,10 +5244,10 @@
         <v>6315</v>
       </c>
       <c r="B100" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C100" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D100">
         <v>2</v>
@@ -5193,10 +5274,10 @@
         <v>6316</v>
       </c>
       <c r="B101" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="C101" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D101">
         <v>2</v>
@@ -5223,10 +5304,10 @@
         <v>6317</v>
       </c>
       <c r="B102" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C102" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -5253,10 +5334,10 @@
         <v>6318</v>
       </c>
       <c r="B103" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C103" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -5283,10 +5364,10 @@
         <v>6319</v>
       </c>
       <c r="B104" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C104" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D104">
         <v>2</v>
@@ -5313,10 +5394,10 @@
         <v>6320</v>
       </c>
       <c r="B105" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C105" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -5343,10 +5424,10 @@
         <v>6321</v>
       </c>
       <c r="B106" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C106" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -5373,10 +5454,10 @@
         <v>6322</v>
       </c>
       <c r="B107" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C107" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D107">
         <v>3</v>
@@ -5403,10 +5484,10 @@
         <v>6323</v>
       </c>
       <c r="B108" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C108" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="D108">
         <v>3</v>
@@ -5433,10 +5514,10 @@
         <v>6324</v>
       </c>
       <c r="B109" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C109" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D109">
         <v>3</v>
@@ -5463,10 +5544,10 @@
         <v>6325</v>
       </c>
       <c r="B110" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C110" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -5493,10 +5574,10 @@
         <v>6326</v>
       </c>
       <c r="B111" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C111" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D111">
         <v>3</v>
@@ -5523,10 +5604,10 @@
         <v>6327</v>
       </c>
       <c r="B112" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C112" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D112">
         <v>3</v>
@@ -5553,10 +5634,10 @@
         <v>6328</v>
       </c>
       <c r="B113" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C113" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="D113">
         <v>3</v>
@@ -5583,10 +5664,10 @@
         <v>6329</v>
       </c>
       <c r="B114" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C114" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="D114">
         <v>3</v>
@@ -5613,10 +5694,10 @@
         <v>6330</v>
       </c>
       <c r="B115" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C115" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D115">
         <v>3</v>
@@ -5643,10 +5724,10 @@
         <v>6331</v>
       </c>
       <c r="B116" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C116" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="D116">
         <v>3</v>
@@ -5673,10 +5754,10 @@
         <v>6332</v>
       </c>
       <c r="B117" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C117" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="D117">
         <v>4</v>
@@ -5703,10 +5784,10 @@
         <v>6333</v>
       </c>
       <c r="B118" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C118" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="D118">
         <v>4</v>
@@ -5733,10 +5814,10 @@
         <v>6334</v>
       </c>
       <c r="B119" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C119" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D119">
         <v>4</v>
@@ -5763,10 +5844,10 @@
         <v>6335</v>
       </c>
       <c r="B120" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C120" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D120">
         <v>4</v>
@@ -5793,10 +5874,10 @@
         <v>6336</v>
       </c>
       <c r="B121" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C121" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D121">
         <v>4</v>
@@ -5823,10 +5904,10 @@
         <v>8507</v>
       </c>
       <c r="B122" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="C122" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="D122">
         <v>4</v>
@@ -5842,7 +5923,7 @@
         <v>166</v>
       </c>
       <c r="H122" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I122">
         <v>2</v>
@@ -5853,10 +5934,10 @@
         <v>6338</v>
       </c>
       <c r="B123" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="C123" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D123">
         <v>4</v>
@@ -5872,7 +5953,7 @@
         <v>166</v>
       </c>
       <c r="H123" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I123">
         <v>2</v>
@@ -5883,10 +5964,10 @@
         <v>6339</v>
       </c>
       <c r="B124" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="C124" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="D124">
         <v>4</v>
@@ -5902,7 +5983,7 @@
         <v>166</v>
       </c>
       <c r="H124" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I124">
         <v>2</v>
@@ -5913,10 +5994,10 @@
         <v>6340</v>
       </c>
       <c r="B125" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C125" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="D125">
         <v>4</v>
@@ -5932,7 +6013,7 @@
         <v>166</v>
       </c>
       <c r="H125" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I125">
         <v>2</v>
@@ -5943,10 +6024,10 @@
         <v>6341</v>
       </c>
       <c r="B126" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="C126" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D126">
         <v>4</v>
@@ -5962,7 +6043,7 @@
         <v>166</v>
       </c>
       <c r="H126" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I126">
         <v>2</v>
@@ -5973,10 +6054,10 @@
         <v>9115</v>
       </c>
       <c r="B127" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C127" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -6003,7 +6084,7 @@
         <v>9116</v>
       </c>
       <c r="B128" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -6033,10 +6114,10 @@
         <v>9117</v>
       </c>
       <c r="B129" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="C129" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -6093,10 +6174,10 @@
         <v>9119</v>
       </c>
       <c r="B131" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C131" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -6123,7 +6204,7 @@
         <v>9120</v>
       </c>
       <c r="B132" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C132" t="s">
         <v>9</v>
@@ -6153,10 +6234,10 @@
         <v>9121</v>
       </c>
       <c r="B133" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C133" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -6183,10 +6264,10 @@
         <v>9122</v>
       </c>
       <c r="B134" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C134" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -6213,10 +6294,10 @@
         <v>9123</v>
       </c>
       <c r="B135" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C135" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -6243,10 +6324,10 @@
         <v>9124</v>
       </c>
       <c r="B136" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C136" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -6273,10 +6354,10 @@
         <v>9125</v>
       </c>
       <c r="B137" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="C137" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D137">
         <v>2</v>
@@ -6303,10 +6384,10 @@
         <v>9126</v>
       </c>
       <c r="B138" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C138" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="D138">
         <v>2</v>
@@ -6333,10 +6414,10 @@
         <v>9127</v>
       </c>
       <c r="B139" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="C139" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="D139">
         <v>2</v>
@@ -6363,10 +6444,10 @@
         <v>9128</v>
       </c>
       <c r="B140" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="C140" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D140">
         <v>2</v>
@@ -6393,10 +6474,10 @@
         <v>9129</v>
       </c>
       <c r="B141" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="C141" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D141">
         <v>2</v>
@@ -6423,10 +6504,10 @@
         <v>9130</v>
       </c>
       <c r="B142" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C142" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D142">
         <v>2</v>
@@ -6453,10 +6534,10 @@
         <v>9131</v>
       </c>
       <c r="B143" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C143" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D143">
         <v>2</v>
@@ -6483,10 +6564,10 @@
         <v>9132</v>
       </c>
       <c r="B144" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C144" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="D144">
         <v>2</v>
@@ -6513,10 +6594,10 @@
         <v>9133</v>
       </c>
       <c r="B145" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C145" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D145">
         <v>2</v>
@@ -6543,10 +6624,10 @@
         <v>9134</v>
       </c>
       <c r="B146" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C146" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -6573,10 +6654,10 @@
         <v>9135</v>
       </c>
       <c r="B147" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="C147" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="D147">
         <v>3</v>
@@ -6603,10 +6684,10 @@
         <v>9136</v>
       </c>
       <c r="B148" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="C148" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="D148">
         <v>3</v>
@@ -6633,10 +6714,10 @@
         <v>9137</v>
       </c>
       <c r="B149" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="C149" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="D149">
         <v>3</v>
@@ -6663,10 +6744,10 @@
         <v>9138</v>
       </c>
       <c r="B150" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="C150" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D150">
         <v>3</v>
@@ -6693,10 +6774,10 @@
         <v>9139</v>
       </c>
       <c r="B151" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C151" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="D151">
         <v>3</v>
@@ -6723,10 +6804,10 @@
         <v>9140</v>
       </c>
       <c r="B152" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="C152" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="D152">
         <v>3</v>
@@ -6753,10 +6834,10 @@
         <v>9141</v>
       </c>
       <c r="B153" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="C153" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="D153">
         <v>3</v>
@@ -6783,10 +6864,10 @@
         <v>9142</v>
       </c>
       <c r="B154" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="C154" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="D154">
         <v>3</v>
@@ -6813,10 +6894,10 @@
         <v>9143</v>
       </c>
       <c r="B155" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="C155" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D155">
         <v>3</v>
@@ -6843,10 +6924,10 @@
         <v>9144</v>
       </c>
       <c r="B156" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C156" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D156">
         <v>3</v>
@@ -6873,10 +6954,10 @@
         <v>9145</v>
       </c>
       <c r="B157" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C157" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D157">
         <v>4</v>
@@ -6903,10 +6984,10 @@
         <v>9146</v>
       </c>
       <c r="B158" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="C158" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="D158">
         <v>4</v>
@@ -6933,10 +7014,10 @@
         <v>9147</v>
       </c>
       <c r="B159" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="C159" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D159">
         <v>4</v>
@@ -6963,10 +7044,10 @@
         <v>9148</v>
       </c>
       <c r="B160" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C160" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="D160">
         <v>4</v>
@@ -6993,10 +7074,10 @@
         <v>9149</v>
       </c>
       <c r="B161" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C161" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D161">
         <v>4</v>
@@ -7023,10 +7104,10 @@
         <v>9151</v>
       </c>
       <c r="B162" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C162" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D162">
         <v>4</v>
@@ -7042,7 +7123,7 @@
         <v>291</v>
       </c>
       <c r="H162" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I162">
         <v>2</v>
@@ -7053,10 +7134,10 @@
         <v>9152</v>
       </c>
       <c r="B163" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C163" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="D163">
         <v>4</v>
@@ -7072,7 +7153,7 @@
         <v>291</v>
       </c>
       <c r="H163" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I163">
         <v>2</v>
@@ -7083,10 +7164,10 @@
         <v>9153</v>
       </c>
       <c r="B164" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C164" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="D164">
         <v>4</v>
@@ -7102,7 +7183,7 @@
         <v>291</v>
       </c>
       <c r="H164" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I164">
         <v>2</v>
@@ -7113,10 +7194,10 @@
         <v>7711</v>
       </c>
       <c r="B165" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="C165" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -7143,10 +7224,10 @@
         <v>7712</v>
       </c>
       <c r="B166" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="C166" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -7173,10 +7254,10 @@
         <v>7713</v>
       </c>
       <c r="B167" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="C167" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D167">
         <v>1</v>
@@ -7203,10 +7284,10 @@
         <v>7714</v>
       </c>
       <c r="B168" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C168" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -7233,10 +7314,10 @@
         <v>7715</v>
       </c>
       <c r="B169" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="C169" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -7263,10 +7344,10 @@
         <v>7716</v>
       </c>
       <c r="B170" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C170" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -7323,10 +7404,10 @@
         <v>7718</v>
       </c>
       <c r="B172" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="C172" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -7353,10 +7434,10 @@
         <v>7719</v>
       </c>
       <c r="B173" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="C173" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -7383,10 +7464,10 @@
         <v>7720</v>
       </c>
       <c r="B174" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C174" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -7413,10 +7494,10 @@
         <v>7721</v>
       </c>
       <c r="B175" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C175" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="D175">
         <v>1</v>
@@ -7443,10 +7524,10 @@
         <v>7722</v>
       </c>
       <c r="B176" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="C176" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D176">
         <v>2</v>
@@ -7473,10 +7554,10 @@
         <v>7723</v>
       </c>
       <c r="B177" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C177" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D177">
         <v>2</v>
@@ -7503,10 +7584,10 @@
         <v>7724</v>
       </c>
       <c r="B178" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C178" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="D178">
         <v>2</v>
@@ -7533,10 +7614,10 @@
         <v>7725</v>
       </c>
       <c r="B179" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="C179" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="D179">
         <v>2</v>
@@ -7563,10 +7644,10 @@
         <v>7726</v>
       </c>
       <c r="B180" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C180" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D180">
         <v>2</v>
@@ -7593,10 +7674,10 @@
         <v>7727</v>
       </c>
       <c r="B181" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="C181" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D181">
         <v>2</v>
@@ -7623,10 +7704,10 @@
         <v>7728</v>
       </c>
       <c r="B182" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="C182" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="D182">
         <v>2</v>
@@ -7653,10 +7734,10 @@
         <v>7729</v>
       </c>
       <c r="B183" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C183" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D183">
         <v>2</v>
@@ -7683,10 +7764,10 @@
         <v>7730</v>
       </c>
       <c r="B184" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C184" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="D184">
         <v>2</v>
@@ -7713,10 +7794,10 @@
         <v>7731</v>
       </c>
       <c r="B185" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="C185" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D185">
         <v>2</v>
@@ -7743,10 +7824,10 @@
         <v>7732</v>
       </c>
       <c r="B186" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="C186" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D186">
         <v>2</v>
@@ -7773,10 +7854,10 @@
         <v>7733</v>
       </c>
       <c r="B187" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C187" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D187">
         <v>3</v>
@@ -7803,10 +7884,10 @@
         <v>7740</v>
       </c>
       <c r="B188" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="C188" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="D188">
         <v>3</v>
@@ -7833,10 +7914,10 @@
         <v>7735</v>
       </c>
       <c r="B189" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="C189" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D189">
         <v>3</v>
@@ -7863,10 +7944,10 @@
         <v>7736</v>
       </c>
       <c r="B190" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="C190" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="D190">
         <v>3</v>
@@ -7893,10 +7974,10 @@
         <v>7737</v>
       </c>
       <c r="B191" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="C191" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="D191">
         <v>3</v>
@@ -7923,10 +8004,10 @@
         <v>7738</v>
       </c>
       <c r="B192" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="C192" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D192">
         <v>3</v>
@@ -7953,10 +8034,10 @@
         <v>7739</v>
       </c>
       <c r="B193" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="C193" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="D193">
         <v>3</v>
@@ -7983,10 +8064,10 @@
         <v>7734</v>
       </c>
       <c r="B194" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="C194" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D194">
         <v>3</v>
@@ -8013,10 +8094,10 @@
         <v>7741</v>
       </c>
       <c r="B195" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="C195" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="D195">
         <v>3</v>
@@ -8043,10 +8124,10 @@
         <v>7742</v>
       </c>
       <c r="B196" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="C196" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D196">
         <v>3</v>
@@ -8073,10 +8154,10 @@
         <v>7743</v>
       </c>
       <c r="B197" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="C197" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="D197">
         <v>3</v>
@@ -8103,10 +8184,10 @@
         <v>7749</v>
       </c>
       <c r="B198" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="C198" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="D198">
         <v>4</v>
@@ -8133,10 +8214,10 @@
         <v>7745</v>
       </c>
       <c r="B199" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="C199" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D199">
         <v>4</v>
@@ -8163,10 +8244,10 @@
         <v>7746</v>
       </c>
       <c r="B200" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="C200" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="D200">
         <v>4</v>
@@ -8193,10 +8274,10 @@
         <v>7747</v>
       </c>
       <c r="B201" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="C201" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="D201">
         <v>4</v>
@@ -8223,10 +8304,10 @@
         <v>7748</v>
       </c>
       <c r="B202" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="C202" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="D202">
         <v>4</v>
@@ -8253,10 +8334,10 @@
         <v>7744</v>
       </c>
       <c r="B203" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="C203" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D203">
         <v>4</v>
@@ -8283,10 +8364,10 @@
         <v>7750</v>
       </c>
       <c r="B204" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="C204" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="D204">
         <v>4</v>
@@ -8313,10 +8394,10 @@
         <v>7751</v>
       </c>
       <c r="B205" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="C205" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="D205">
         <v>4</v>
@@ -8343,10 +8424,10 @@
         <v>7752</v>
       </c>
       <c r="B206" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="C206" t="s">
-        <v>551</v>
+        <v>547</v>
       </c>
       <c r="D206">
         <v>4</v>
@@ -8373,10 +8454,10 @@
         <v>7753</v>
       </c>
       <c r="B207" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="C207" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D207">
         <v>4</v>
@@ -8403,10 +8484,10 @@
         <v>7763</v>
       </c>
       <c r="B208" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="C208" t="s">
-        <v>552</v>
+        <v>548</v>
       </c>
       <c r="D208">
         <v>4</v>
@@ -8433,10 +8514,10 @@
         <v>7754</v>
       </c>
       <c r="B209" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="C209" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="D209">
         <v>5</v>
@@ -8463,10 +8544,10 @@
         <v>7755</v>
       </c>
       <c r="B210" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="C210" t="s">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="D210">
         <v>5</v>
@@ -8493,10 +8574,10 @@
         <v>7756</v>
       </c>
       <c r="B211" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="C211" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="D211">
         <v>5</v>
@@ -8523,10 +8604,10 @@
         <v>7757</v>
       </c>
       <c r="B212" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="C212" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="D212">
         <v>5</v>
@@ -8553,10 +8634,10 @@
         <v>7758</v>
       </c>
       <c r="B213" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="C213" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D213">
         <v>5</v>
@@ -8583,10 +8664,10 @@
         <v>7760</v>
       </c>
       <c r="B214" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="C214" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="D214">
         <v>5</v>
@@ -8602,7 +8683,7 @@
         <v>254</v>
       </c>
       <c r="H214" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="I214">
         <v>2</v>
@@ -8620,19 +8701,19 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -18168,10 +18249,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -18186,7 +18267,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -18201,370 +18282,370 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" t="s">
-        <v>31</v>
+        <v>116</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
       </c>
       <c r="C2" s="2">
         <v>46038</v>
       </c>
       <c r="D2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E2" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="G2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>123</v>
-      </c>
-      <c r="B3" t="s">
-        <v>37</v>
+        <v>120</v>
+      </c>
+      <c r="B3">
+        <v>23</v>
       </c>
       <c r="C3" s="2">
         <v>46044</v>
       </c>
       <c r="D3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="G3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B4" t="s">
-        <v>31</v>
+        <v>123</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
       </c>
       <c r="C4" s="2">
         <v>46049</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E4" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F4" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G4" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>130</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
+        <v>127</v>
+      </c>
+      <c r="B5">
+        <v>12</v>
       </c>
       <c r="C5" s="2">
         <v>46045</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="G5" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>134</v>
-      </c>
-      <c r="B6" t="s">
-        <v>43</v>
+        <v>131</v>
+      </c>
+      <c r="B6">
+        <v>47</v>
       </c>
       <c r="C6" s="2">
         <v>46051</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E6" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F6" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>136</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
+        <v>133</v>
+      </c>
+      <c r="B7">
+        <v>12</v>
       </c>
       <c r="C7" s="2">
         <v>46049</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E7" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F7" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G7" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" t="s">
-        <v>37</v>
+        <v>135</v>
+      </c>
+      <c r="B8">
+        <v>23</v>
       </c>
       <c r="C8" s="2">
         <v>46056</v>
       </c>
       <c r="D8" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F8" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G8" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>139</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
+        <v>136</v>
+      </c>
+      <c r="B9">
+        <v>23</v>
       </c>
       <c r="C9" s="2">
         <v>46063</v>
       </c>
       <c r="D9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E9" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>140</v>
-      </c>
-      <c r="B10" t="s">
-        <v>37</v>
+        <v>137</v>
+      </c>
+      <c r="B10">
+        <v>23</v>
       </c>
       <c r="C10" s="2">
         <v>46070</v>
       </c>
       <c r="D10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G10" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>141</v>
-      </c>
-      <c r="B11" t="s">
-        <v>41</v>
+        <v>138</v>
+      </c>
+      <c r="B11">
+        <v>12</v>
       </c>
       <c r="C11" s="2">
         <v>46056</v>
       </c>
       <c r="D11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F11" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G11" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>144</v>
-      </c>
-      <c r="B12" t="s">
-        <v>41</v>
+        <v>141</v>
+      </c>
+      <c r="B12">
+        <v>12</v>
       </c>
       <c r="C12" s="2">
         <v>46063</v>
       </c>
       <c r="D12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E12" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F12" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G12" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>145</v>
-      </c>
-      <c r="B13" t="s">
-        <v>41</v>
+        <v>142</v>
+      </c>
+      <c r="B13">
+        <v>12</v>
       </c>
       <c r="C13" s="2">
         <v>46070</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E13" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F13" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G13" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>146</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
+        <v>143</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
       </c>
       <c r="C14" s="2">
         <v>46058</v>
       </c>
       <c r="D14" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F14" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="G14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
+        <v>146</v>
+      </c>
+      <c r="B15">
+        <v>23</v>
       </c>
       <c r="C15" s="2">
         <v>46059</v>
       </c>
       <c r="D15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E15" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G15" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>152</v>
-      </c>
-      <c r="B16" t="s">
-        <v>41</v>
+        <v>149</v>
+      </c>
+      <c r="B16">
+        <v>12</v>
       </c>
       <c r="C16" s="2">
         <v>46112</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="E16" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F16" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="G16" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -18587,22 +18668,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -18617,57 +18698,57 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="B2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E2" s="3">
         <v>46038.654861111107</v>
@@ -18696,16 +18777,16 @@
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E3" s="3">
         <v>46044.75</v>
@@ -18714,7 +18795,7 @@
         <v>46044.791666666657</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -18734,16 +18815,16 @@
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="B4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E4" s="3">
         <v>46049.416666666657</v>
@@ -18752,7 +18833,7 @@
         <v>46049.5</v>
       </c>
       <c r="G4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -18772,16 +18853,16 @@
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E5" s="3">
         <v>46045.375</v>
@@ -18790,7 +18871,7 @@
         <v>46045.625</v>
       </c>
       <c r="G5" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -18810,16 +18891,16 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E6" s="3">
         <v>46051.666666666657</v>
@@ -18848,16 +18929,16 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E7" s="3">
         <v>46049.416666666657</v>
@@ -18886,16 +18967,16 @@
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B8" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E8" s="3">
         <v>46056.416666666657</v>
@@ -18924,16 +19005,16 @@
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E9" s="3">
         <v>46063.416666666657</v>
@@ -18962,16 +19043,16 @@
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B10" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E10" s="3">
         <v>46070.416666666657</v>
@@ -19000,16 +19081,16 @@
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C11" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D11" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E11" s="3">
         <v>46056.6875</v>
@@ -19018,7 +19099,7 @@
         <v>46056.770833333343</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -19038,16 +19119,16 @@
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B12" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C12" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D12" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E12" s="3">
         <v>46063.6875</v>
@@ -19056,7 +19137,7 @@
         <v>46063.770833333343</v>
       </c>
       <c r="G12" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -19076,16 +19157,16 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B13" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C13" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D13" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E13" s="3">
         <v>46070.6875</v>
@@ -19094,7 +19175,7 @@
         <v>46070.770833333343</v>
       </c>
       <c r="G13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -19114,16 +19195,16 @@
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="B14" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D14" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E14" s="3">
         <v>46058.479166666657</v>
@@ -19132,7 +19213,7 @@
         <v>46058.520833333343</v>
       </c>
       <c r="G14" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -19152,16 +19233,16 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B15" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C15" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D15" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E15" s="3">
         <v>46059.727777777778</v>
@@ -19170,7 +19251,7 @@
         <v>46059.770138888889</v>
       </c>
       <c r="G15" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H15">
         <v>0</v>
@@ -19190,16 +19271,16 @@
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D16" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E16" s="3">
         <v>46112.625</v>
@@ -19208,7 +19289,7 @@
         <v>46112.708333333343</v>
       </c>
       <c r="G16" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -19238,130 +19319,130 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="B2" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="C2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="C3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B4" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B5" t="s">
+        <v>189</v>
+      </c>
+      <c r="C5" t="s">
         <v>192</v>
-      </c>
-      <c r="C5" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" t="s">
         <v>66</v>
       </c>
-      <c r="D6" t="s">
-        <v>68</v>
-      </c>
       <c r="E6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="B7" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C7" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D7" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B10" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C10" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -19376,27 +19457,27 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -19410,10 +19491,10 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -19437,10 +19518,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -19602,34 +19683,34 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>213</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>216</v>
       </c>
     </row>
   </sheetData>
@@ -19698,10 +19779,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2">
         <v>2</v>
@@ -19721,11 +19802,11 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="K2">
-        <v>81.599999999999994</v>
+      <c r="K2" t="s">
+        <v>553</v>
       </c>
       <c r="O2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -19733,10 +19814,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -19759,11 +19840,11 @@
       <c r="J3">
         <v>1</v>
       </c>
-      <c r="K3">
-        <v>83.57</v>
+      <c r="K3" t="s">
+        <v>554</v>
       </c>
       <c r="O3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -19771,10 +19852,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -19797,11 +19878,11 @@
       <c r="J4">
         <v>1</v>
       </c>
-      <c r="K4">
-        <v>87.25</v>
+      <c r="K4" t="s">
+        <v>555</v>
       </c>
       <c r="O4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -19809,10 +19890,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>2</v>
@@ -19832,11 +19913,11 @@
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="K5">
-        <v>87.75</v>
+      <c r="K5" t="s">
+        <v>556</v>
       </c>
       <c r="O5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -19844,10 +19925,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D6">
         <v>3</v>
@@ -19874,7 +19955,7 @@
         <v>85</v>
       </c>
       <c r="O6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -19882,10 +19963,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>3</v>
@@ -19908,11 +19989,11 @@
       <c r="J7">
         <v>1</v>
       </c>
-      <c r="K7">
-        <v>87.25</v>
+      <c r="K7" t="s">
+        <v>555</v>
       </c>
       <c r="O7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -19920,10 +20001,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D8">
         <v>3</v>
@@ -19946,11 +20027,11 @@
       <c r="J8">
         <v>1</v>
       </c>
-      <c r="K8">
-        <v>86.96</v>
+      <c r="K8" t="s">
+        <v>557</v>
       </c>
       <c r="O8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -19958,10 +20039,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>4</v>
@@ -19984,11 +20065,11 @@
       <c r="J9">
         <v>1</v>
       </c>
-      <c r="K9">
-        <v>50.55</v>
+      <c r="K9" t="s">
+        <v>558</v>
       </c>
       <c r="O9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -19996,10 +20077,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -20022,11 +20103,11 @@
       <c r="J10">
         <v>1</v>
       </c>
-      <c r="K10">
-        <v>116.43</v>
+      <c r="K10" t="s">
+        <v>559</v>
       </c>
       <c r="O10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -20034,10 +20115,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D11">
         <v>4</v>
@@ -20060,11 +20141,11 @@
       <c r="J11">
         <v>1</v>
       </c>
-      <c r="K11">
-        <v>94.72</v>
+      <c r="K11" t="s">
+        <v>560</v>
       </c>
       <c r="O11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -20072,10 +20153,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12">
         <v>5</v>
@@ -20098,14 +20179,14 @@
       <c r="J12">
         <v>1</v>
       </c>
-      <c r="K12">
-        <v>135.19999999999999</v>
+      <c r="K12" t="s">
+        <v>561</v>
       </c>
       <c r="L12" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -20113,10 +20194,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -20139,14 +20220,14 @@
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="K13">
-        <v>132.81</v>
+      <c r="K13" t="s">
+        <v>562</v>
       </c>
       <c r="L13" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
@@ -20154,10 +20235,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -20177,14 +20258,14 @@
       <c r="I14">
         <v>1</v>
       </c>
-      <c r="K14">
-        <v>147.88999999999999</v>
+      <c r="K14" t="s">
+        <v>563</v>
       </c>
       <c r="L14" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
@@ -20192,10 +20273,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -20215,14 +20296,14 @@
       <c r="I15">
         <v>1</v>
       </c>
-      <c r="K15">
-        <v>144.63999999999999</v>
+      <c r="K15" t="s">
+        <v>564</v>
       </c>
       <c r="L15" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
@@ -20230,19 +20311,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
-      <c r="K16">
-        <v>20.82</v>
+      <c r="K16" t="s">
+        <v>565</v>
       </c>
       <c r="O16" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
@@ -20250,10 +20331,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D17">
         <v>3</v>
@@ -20276,11 +20357,11 @@
       <c r="J17">
         <v>1</v>
       </c>
-      <c r="K17">
-        <v>50.72</v>
+      <c r="K17" t="s">
+        <v>566</v>
       </c>
       <c r="O17" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -20288,10 +20369,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C18" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -20314,11 +20395,11 @@
       <c r="J18">
         <v>1</v>
       </c>
-      <c r="K18">
-        <v>79.3</v>
+      <c r="K18" t="s">
+        <v>567</v>
       </c>
       <c r="O18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
@@ -20326,10 +20407,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -20352,11 +20433,11 @@
       <c r="J19">
         <v>1</v>
       </c>
-      <c r="K19">
-        <v>104.88</v>
+      <c r="K19" t="s">
+        <v>568</v>
       </c>
       <c r="O19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
@@ -20364,10 +20445,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C20" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D20">
         <v>3</v>
@@ -20390,11 +20471,11 @@
       <c r="J20">
         <v>1</v>
       </c>
-      <c r="K20">
-        <v>80.319999999999993</v>
+      <c r="K20" t="s">
+        <v>569</v>
       </c>
       <c r="O20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
@@ -20402,10 +20483,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D21">
         <v>3</v>
@@ -20428,11 +20509,11 @@
       <c r="J21">
         <v>1</v>
       </c>
-      <c r="K21">
-        <v>77.52</v>
+      <c r="K21" t="s">
+        <v>570</v>
       </c>
       <c r="O21" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -20440,10 +20521,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -20466,11 +20547,11 @@
       <c r="J22">
         <v>1</v>
       </c>
-      <c r="K22">
-        <v>105.31</v>
+      <c r="K22" t="s">
+        <v>571</v>
       </c>
       <c r="O22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
@@ -20478,10 +20559,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D23">
         <v>4</v>
@@ -20504,11 +20585,11 @@
       <c r="J23">
         <v>1</v>
       </c>
-      <c r="K23">
-        <v>77.22</v>
+      <c r="K23" t="s">
+        <v>572</v>
       </c>
       <c r="O23" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -20516,10 +20597,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" t="s">
         <v>37</v>
-      </c>
-      <c r="C24" t="s">
-        <v>38</v>
       </c>
       <c r="D24">
         <v>4</v>
@@ -20542,11 +20623,11 @@
       <c r="J24">
         <v>1</v>
       </c>
-      <c r="K24">
-        <v>78.69</v>
+      <c r="K24" t="s">
+        <v>573</v>
       </c>
       <c r="O24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -20554,10 +20635,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C25" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D25">
         <v>4</v>
@@ -20580,11 +20661,11 @@
       <c r="J25">
         <v>1</v>
       </c>
-      <c r="K25">
-        <v>78.819999999999993</v>
+      <c r="K25" t="s">
+        <v>574</v>
       </c>
       <c r="O25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -20592,17 +20673,14 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="C26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D26">
         <v>4</v>
       </c>
-      <c r="E26" t="s">
-        <v>242</v>
-      </c>
       <c r="F26">
         <v>1</v>
       </c>
@@ -20618,14 +20696,14 @@
       <c r="J26">
         <v>1</v>
       </c>
-      <c r="K26">
-        <v>273.13</v>
+      <c r="K26" t="s">
+        <v>575</v>
       </c>
       <c r="L26" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="O26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
@@ -20633,10 +20711,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D27">
         <v>5</v>
@@ -20653,11 +20731,11 @@
       <c r="I27">
         <v>0</v>
       </c>
-      <c r="K27">
-        <v>80.39</v>
+      <c r="K27" t="s">
+        <v>576</v>
       </c>
       <c r="O27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -20665,10 +20743,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="C28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D28">
         <v>5</v>
@@ -20688,11 +20766,11 @@
       <c r="I28">
         <v>0</v>
       </c>
-      <c r="K28">
-        <v>78.94</v>
+      <c r="K28" t="s">
+        <v>577</v>
       </c>
       <c r="O28" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -20700,10 +20778,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="C29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D29">
         <v>5</v>
@@ -20723,11 +20801,11 @@
       <c r="I29">
         <v>0</v>
       </c>
-      <c r="K29">
-        <v>97.05</v>
+      <c r="K29" t="s">
+        <v>578</v>
       </c>
       <c r="O29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -20735,10 +20813,10 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="C30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -20756,7 +20834,7 @@
         <v>1</v>
       </c>
       <c r="O30" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -20764,10 +20842,10 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -20776,10 +20854,10 @@
         <v>442</v>
       </c>
       <c r="L31" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="O31" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
@@ -20787,16 +20865,16 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D32">
         <v>1</v>
       </c>
       <c r="O32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
@@ -20804,10 +20882,10 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -20818,11 +20896,11 @@
       <c r="J33">
         <v>1</v>
       </c>
-      <c r="K33">
-        <v>70.75</v>
+      <c r="K33" t="s">
+        <v>579</v>
       </c>
       <c r="O33" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
@@ -20830,10 +20908,10 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="C34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -20853,11 +20931,11 @@
       <c r="I34">
         <v>0</v>
       </c>
-      <c r="K34">
-        <v>98.47</v>
+      <c r="K34" t="s">
+        <v>580</v>
       </c>
       <c r="O34" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
@@ -20865,10 +20943,10 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="C35" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -20876,11 +20954,11 @@
       <c r="E35">
         <v>30</v>
       </c>
-      <c r="K35">
-        <v>73.23</v>
+      <c r="K35" t="s">
+        <v>581</v>
       </c>
       <c r="O35" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
@@ -20888,10 +20966,10 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -20911,11 +20989,11 @@
       <c r="I36">
         <v>0</v>
       </c>
-      <c r="K36">
-        <v>67.77</v>
+      <c r="K36" t="s">
+        <v>582</v>
       </c>
       <c r="O36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
@@ -20923,10 +21001,10 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -20947,10 +21025,10 @@
         <v>149</v>
       </c>
       <c r="L37" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="O37" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
@@ -20958,10 +21036,10 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="C38" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -20973,10 +21051,10 @@
         <v>1</v>
       </c>
       <c r="L38" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="O38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
@@ -20984,10 +21062,10 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="C39" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -21008,10 +21086,10 @@
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="O39" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
@@ -21019,10 +21097,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C40" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -21031,7 +21109,7 @@
         <v>105</v>
       </c>
       <c r="O40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
@@ -21039,10 +21117,10 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="O41" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
@@ -21050,10 +21128,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="O42" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
@@ -21061,10 +21139,10 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="O43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
@@ -21072,10 +21150,10 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="O44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
@@ -21083,10 +21161,10 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="O45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
@@ -21094,10 +21172,10 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="O46" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
@@ -21105,10 +21183,10 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="O47" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
@@ -21116,10 +21194,10 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="O48" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.3">
@@ -21127,10 +21205,10 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="O49" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
@@ -21138,10 +21216,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="O50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
@@ -21149,10 +21227,10 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="O51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
@@ -21160,10 +21238,10 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="O52" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
@@ -21171,10 +21249,10 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="O53" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
@@ -21182,10 +21260,10 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="O54" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
@@ -21193,10 +21271,10 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="O55" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
@@ -21204,10 +21282,10 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="O56" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
@@ -21215,10 +21293,10 @@
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="O57" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
@@ -21226,10 +21304,10 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="O58" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
@@ -21237,10 +21315,10 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="O59" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
@@ -21248,10 +21326,10 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="O60" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -21266,10 +21344,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
@@ -21277,7 +21355,7 @@
         <v>45993</v>
       </c>
       <c r="B2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
@@ -21285,7 +21363,7 @@
         <v>46086</v>
       </c>
       <c r="B3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
@@ -21293,7 +21371,7 @@
         <v>46099</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
@@ -21301,7 +21379,7 @@
         <v>46163</v>
       </c>
       <c r="B5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -21316,18 +21394,18 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2">
         <v>45901</v>
@@ -21348,13 +21426,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -21362,7 +21440,7 @@
         <v>45901</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
         <v>10</v>
@@ -21373,7 +21451,7 @@
         <v>45902</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -21384,10 +21462,10 @@
         <v>45903</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -21395,10 +21473,10 @@
         <v>45904</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -21406,10 +21484,10 @@
         <v>45905</v>
       </c>
       <c r="B6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -21417,7 +21495,7 @@
         <v>45906</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
         <v>11</v>
@@ -21428,10 +21506,10 @@
         <v>45907</v>
       </c>
       <c r="B8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -21439,7 +21517,7 @@
         <v>45908</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C9" t="s">
         <v>10</v>
@@ -21450,7 +21528,7 @@
         <v>45909</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
@@ -21461,10 +21539,10 @@
         <v>45910</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -21472,10 +21550,10 @@
         <v>45911</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
@@ -21483,10 +21561,10 @@
         <v>45912</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
@@ -21494,7 +21572,7 @@
         <v>45913</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
         <v>11</v>
@@ -21505,10 +21583,10 @@
         <v>45914</v>
       </c>
       <c r="B15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
@@ -21516,7 +21594,7 @@
         <v>45915</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C16" t="s">
         <v>10</v>
@@ -21527,7 +21605,7 @@
         <v>45916</v>
       </c>
       <c r="B17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
@@ -21538,10 +21616,10 @@
         <v>45917</v>
       </c>
       <c r="B18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
@@ -21549,10 +21627,10 @@
         <v>45918</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
@@ -21560,10 +21638,10 @@
         <v>45919</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.3">
@@ -21571,7 +21649,7 @@
         <v>45920</v>
       </c>
       <c r="B21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
@@ -21582,10 +21660,10 @@
         <v>45921</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
@@ -21593,7 +21671,7 @@
         <v>45922</v>
       </c>
       <c r="B23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
         <v>10</v>
@@ -21604,7 +21682,7 @@
         <v>45923</v>
       </c>
       <c r="B24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C24" t="s">
         <v>14</v>
@@ -21615,10 +21693,10 @@
         <v>45924</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C25" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.3">
@@ -21626,10 +21704,10 @@
         <v>45925</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C26" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.3">
@@ -21637,10 +21715,10 @@
         <v>45926</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.3">
@@ -21648,7 +21726,7 @@
         <v>45927</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C28" t="s">
         <v>11</v>
@@ -21659,10 +21737,10 @@
         <v>45928</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.3">
@@ -21670,7 +21748,7 @@
         <v>45929</v>
       </c>
       <c r="B30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C30" t="s">
         <v>10</v>
@@ -21681,7 +21759,7 @@
         <v>45930</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
@@ -21692,10 +21770,10 @@
         <v>45931</v>
       </c>
       <c r="B32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.3">
@@ -21703,10 +21781,10 @@
         <v>45932</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C33" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.3">
@@ -21714,10 +21792,10 @@
         <v>45933</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.3">
@@ -21725,7 +21803,7 @@
         <v>45934</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C35" t="s">
         <v>11</v>
@@ -21736,10 +21814,10 @@
         <v>45935</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.3">
@@ -21747,7 +21825,7 @@
         <v>45936</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
         <v>10</v>
@@ -21758,7 +21836,7 @@
         <v>45937</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C38" t="s">
         <v>14</v>
@@ -21769,10 +21847,10 @@
         <v>45938</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.3">
@@ -21780,10 +21858,10 @@
         <v>45939</v>
       </c>
       <c r="B40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C40" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.3">
@@ -21791,10 +21869,10 @@
         <v>45940</v>
       </c>
       <c r="B41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.3">
@@ -21802,7 +21880,7 @@
         <v>45941</v>
       </c>
       <c r="B42" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C42" t="s">
         <v>11</v>
@@ -21813,10 +21891,10 @@
         <v>45942</v>
       </c>
       <c r="B43" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.3">
@@ -21824,7 +21902,7 @@
         <v>45943</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C44" t="s">
         <v>10</v>
@@ -21835,7 +21913,7 @@
         <v>45944</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
@@ -21846,10 +21924,10 @@
         <v>45945</v>
       </c>
       <c r="B46" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C46" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.3">
@@ -21857,10 +21935,10 @@
         <v>45946</v>
       </c>
       <c r="B47" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.3">
@@ -21868,10 +21946,10 @@
         <v>45947</v>
       </c>
       <c r="B48" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C48" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.3">
@@ -21879,7 +21957,7 @@
         <v>45948</v>
       </c>
       <c r="B49" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C49" t="s">
         <v>11</v>
@@ -21890,10 +21968,10 @@
         <v>45949</v>
       </c>
       <c r="B50" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C50" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.3">
@@ -21901,7 +21979,7 @@
         <v>45950</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C51" t="s">
         <v>10</v>
@@ -21912,7 +21990,7 @@
         <v>45951</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
         <v>14</v>
@@ -21923,10 +22001,10 @@
         <v>45952</v>
       </c>
       <c r="B53" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C53" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.3">
@@ -21934,10 +22012,10 @@
         <v>45953</v>
       </c>
       <c r="B54" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C54" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.3">
@@ -21945,10 +22023,10 @@
         <v>45954</v>
       </c>
       <c r="B55" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.3">
@@ -21956,7 +22034,7 @@
         <v>45955</v>
       </c>
       <c r="B56" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C56" t="s">
         <v>11</v>
@@ -21967,10 +22045,10 @@
         <v>45956</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.3">
@@ -21978,7 +22056,7 @@
         <v>45957</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C58" t="s">
         <v>10</v>
@@ -21989,7 +22067,7 @@
         <v>45958</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C59" t="s">
         <v>14</v>
@@ -22000,10 +22078,10 @@
         <v>45959</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C60" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.3">
@@ -22011,10 +22089,10 @@
         <v>45960</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C61" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.3">
@@ -22022,10 +22100,10 @@
         <v>45961</v>
       </c>
       <c r="B62" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.3">
@@ -22033,7 +22111,7 @@
         <v>45962</v>
       </c>
       <c r="B63" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C63" t="s">
         <v>11</v>
@@ -22044,10 +22122,10 @@
         <v>45963</v>
       </c>
       <c r="B64" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C64" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.3">
@@ -22055,7 +22133,7 @@
         <v>45964</v>
       </c>
       <c r="B65" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C65" t="s">
         <v>10</v>
@@ -22066,7 +22144,7 @@
         <v>45965</v>
       </c>
       <c r="B66" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -22077,10 +22155,10 @@
         <v>45966</v>
       </c>
       <c r="B67" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C67" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.3">
@@ -22088,10 +22166,10 @@
         <v>45967</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C68" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.3">
@@ -22099,10 +22177,10 @@
         <v>45968</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C69" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.3">
@@ -22110,7 +22188,7 @@
         <v>45969</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C70" t="s">
         <v>11</v>
@@ -22121,10 +22199,10 @@
         <v>45970</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C71" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.3">
@@ -22132,7 +22210,7 @@
         <v>45971</v>
       </c>
       <c r="B72" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C72" t="s">
         <v>10</v>
@@ -22143,7 +22221,7 @@
         <v>45972</v>
       </c>
       <c r="B73" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C73" t="s">
         <v>14</v>
@@ -22154,10 +22232,10 @@
         <v>45973</v>
       </c>
       <c r="B74" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C74" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.3">
@@ -22165,10 +22243,10 @@
         <v>45974</v>
       </c>
       <c r="B75" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C75" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.3">
@@ -22176,10 +22254,10 @@
         <v>45975</v>
       </c>
       <c r="B76" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C76" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.3">
@@ -22187,7 +22265,7 @@
         <v>45976</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C77" t="s">
         <v>11</v>
@@ -22198,10 +22276,10 @@
         <v>45977</v>
       </c>
       <c r="B78" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C78" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.3">
@@ -22209,7 +22287,7 @@
         <v>45978</v>
       </c>
       <c r="B79" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C79" t="s">
         <v>10</v>
@@ -22220,7 +22298,7 @@
         <v>45979</v>
       </c>
       <c r="B80" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C80" t="s">
         <v>14</v>
@@ -22231,10 +22309,10 @@
         <v>45980</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C81" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.3">
@@ -22242,10 +22320,10 @@
         <v>45981</v>
       </c>
       <c r="B82" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C82" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.3">
@@ -22253,10 +22331,10 @@
         <v>45982</v>
       </c>
       <c r="B83" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C83" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.3">
@@ -22264,7 +22342,7 @@
         <v>45983</v>
       </c>
       <c r="B84" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C84" t="s">
         <v>11</v>
@@ -22275,10 +22353,10 @@
         <v>45984</v>
       </c>
       <c r="B85" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C85" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.3">
@@ -22286,7 +22364,7 @@
         <v>45985</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C86" t="s">
         <v>10</v>
@@ -22297,7 +22375,7 @@
         <v>45986</v>
       </c>
       <c r="B87" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C87" t="s">
         <v>14</v>
@@ -22308,10 +22386,10 @@
         <v>45987</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C88" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.3">
@@ -22319,10 +22397,10 @@
         <v>45988</v>
       </c>
       <c r="B89" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C89" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.3">
@@ -22330,10 +22408,10 @@
         <v>45989</v>
       </c>
       <c r="B90" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C90" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.3">
@@ -22341,7 +22419,7 @@
         <v>45990</v>
       </c>
       <c r="B91" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C91" t="s">
         <v>11</v>
@@ -22352,10 +22430,10 @@
         <v>45991</v>
       </c>
       <c r="B92" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C92" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.3">
@@ -22363,7 +22441,7 @@
         <v>45992</v>
       </c>
       <c r="B93" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C93" t="s">
         <v>10</v>
@@ -22374,7 +22452,7 @@
         <v>45993</v>
       </c>
       <c r="B94" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C94" t="s">
         <v>14</v>
@@ -22385,10 +22463,10 @@
         <v>45994</v>
       </c>
       <c r="B95" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C95" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.3">
@@ -22396,10 +22474,10 @@
         <v>45995</v>
       </c>
       <c r="B96" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C96" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.3">
@@ -22407,10 +22485,10 @@
         <v>45996</v>
       </c>
       <c r="B97" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C97" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.3">
@@ -22418,7 +22496,7 @@
         <v>45997</v>
       </c>
       <c r="B98" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C98" t="s">
         <v>11</v>
@@ -22429,10 +22507,10 @@
         <v>45998</v>
       </c>
       <c r="B99" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C99" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.3">
@@ -22440,7 +22518,7 @@
         <v>45999</v>
       </c>
       <c r="B100" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C100" t="s">
         <v>10</v>
@@ -22451,7 +22529,7 @@
         <v>46000</v>
       </c>
       <c r="B101" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C101" t="s">
         <v>14</v>
@@ -22462,10 +22540,10 @@
         <v>46001</v>
       </c>
       <c r="B102" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C102" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.3">
@@ -22473,10 +22551,10 @@
         <v>46002</v>
       </c>
       <c r="B103" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C103" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.3">
@@ -22484,10 +22562,10 @@
         <v>46003</v>
       </c>
       <c r="B104" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C104" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.3">
@@ -22495,7 +22573,7 @@
         <v>46004</v>
       </c>
       <c r="B105" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C105" t="s">
         <v>11</v>
@@ -22506,10 +22584,10 @@
         <v>46005</v>
       </c>
       <c r="B106" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C106" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.3">
@@ -22517,7 +22595,7 @@
         <v>46006</v>
       </c>
       <c r="B107" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C107" t="s">
         <v>10</v>
@@ -22528,7 +22606,7 @@
         <v>46007</v>
       </c>
       <c r="B108" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C108" t="s">
         <v>14</v>
@@ -22539,10 +22617,10 @@
         <v>46008</v>
       </c>
       <c r="B109" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C109" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.3">
@@ -22550,10 +22628,10 @@
         <v>46009</v>
       </c>
       <c r="B110" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C110" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.3">
@@ -22561,10 +22639,10 @@
         <v>46010</v>
       </c>
       <c r="B111" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C111" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.3">
@@ -22572,7 +22650,7 @@
         <v>46011</v>
       </c>
       <c r="B112" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C112" t="s">
         <v>11</v>
@@ -22583,10 +22661,10 @@
         <v>46012</v>
       </c>
       <c r="B113" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C113" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.3">
@@ -22594,7 +22672,7 @@
         <v>46013</v>
       </c>
       <c r="B114" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C114" t="s">
         <v>10</v>
@@ -22605,7 +22683,7 @@
         <v>46014</v>
       </c>
       <c r="B115" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C115" t="s">
         <v>14</v>
@@ -22616,10 +22694,10 @@
         <v>46015</v>
       </c>
       <c r="B116" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C116" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.3">
@@ -22627,10 +22705,10 @@
         <v>46016</v>
       </c>
       <c r="B117" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C117" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.3">
@@ -22638,10 +22716,10 @@
         <v>46017</v>
       </c>
       <c r="B118" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C118" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.3">
@@ -22649,7 +22727,7 @@
         <v>46018</v>
       </c>
       <c r="B119" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C119" t="s">
         <v>11</v>
@@ -22660,10 +22738,10 @@
         <v>46019</v>
       </c>
       <c r="B120" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C120" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.3">
@@ -22671,7 +22749,7 @@
         <v>46020</v>
       </c>
       <c r="B121" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C121" t="s">
         <v>10</v>
@@ -22682,7 +22760,7 @@
         <v>46021</v>
       </c>
       <c r="B122" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C122" t="s">
         <v>14</v>
@@ -22693,10 +22771,10 @@
         <v>46022</v>
       </c>
       <c r="B123" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C123" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.3">
@@ -22704,10 +22782,10 @@
         <v>46023</v>
       </c>
       <c r="B124" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C124" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.3">
@@ -22715,10 +22793,10 @@
         <v>46024</v>
       </c>
       <c r="B125" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C125" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.3">
@@ -22726,7 +22804,7 @@
         <v>46025</v>
       </c>
       <c r="B126" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C126" t="s">
         <v>11</v>
@@ -22737,10 +22815,10 @@
         <v>46026</v>
       </c>
       <c r="B127" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C127" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.3">
@@ -22748,7 +22826,7 @@
         <v>46027</v>
       </c>
       <c r="B128" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C128" t="s">
         <v>10</v>
@@ -22759,7 +22837,7 @@
         <v>46028</v>
       </c>
       <c r="B129" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C129" t="s">
         <v>14</v>
@@ -22770,10 +22848,10 @@
         <v>46029</v>
       </c>
       <c r="B130" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C130" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.3">
@@ -22781,10 +22859,10 @@
         <v>46030</v>
       </c>
       <c r="B131" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C131" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.3">
@@ -22792,10 +22870,10 @@
         <v>46031</v>
       </c>
       <c r="B132" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C132" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.3">
@@ -22803,7 +22881,7 @@
         <v>46032</v>
       </c>
       <c r="B133" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C133" t="s">
         <v>11</v>
@@ -22814,10 +22892,10 @@
         <v>46033</v>
       </c>
       <c r="B134" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C134" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.3">
@@ -22825,7 +22903,7 @@
         <v>46034</v>
       </c>
       <c r="B135" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C135" t="s">
         <v>10</v>
@@ -22836,7 +22914,7 @@
         <v>46035</v>
       </c>
       <c r="B136" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C136" t="s">
         <v>14</v>
@@ -22847,10 +22925,10 @@
         <v>46036</v>
       </c>
       <c r="B137" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C137" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.3">
@@ -22858,10 +22936,10 @@
         <v>46037</v>
       </c>
       <c r="B138" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C138" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.3">
@@ -22869,10 +22947,10 @@
         <v>46038</v>
       </c>
       <c r="B139" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C139" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.3">
@@ -22880,7 +22958,7 @@
         <v>46039</v>
       </c>
       <c r="B140" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C140" t="s">
         <v>11</v>
@@ -22891,10 +22969,10 @@
         <v>46040</v>
       </c>
       <c r="B141" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C141" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.3">
@@ -22902,7 +22980,7 @@
         <v>46041</v>
       </c>
       <c r="B142" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C142" t="s">
         <v>10</v>
@@ -22913,7 +22991,7 @@
         <v>46042</v>
       </c>
       <c r="B143" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C143" t="s">
         <v>14</v>
@@ -22924,10 +23002,10 @@
         <v>46043</v>
       </c>
       <c r="B144" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C144" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.3">
@@ -22935,10 +23013,10 @@
         <v>46044</v>
       </c>
       <c r="B145" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C145" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.3">
@@ -22946,10 +23024,10 @@
         <v>46045</v>
       </c>
       <c r="B146" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C146" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.3">
@@ -22957,7 +23035,7 @@
         <v>46046</v>
       </c>
       <c r="B147" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C147" t="s">
         <v>11</v>
@@ -22968,10 +23046,10 @@
         <v>46047</v>
       </c>
       <c r="B148" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C148" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.3">
@@ -22979,7 +23057,7 @@
         <v>46048</v>
       </c>
       <c r="B149" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C149" t="s">
         <v>10</v>
@@ -22990,7 +23068,7 @@
         <v>46049</v>
       </c>
       <c r="B150" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C150" t="s">
         <v>14</v>
@@ -23001,10 +23079,10 @@
         <v>46050</v>
       </c>
       <c r="B151" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C151" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.3">
@@ -23012,10 +23090,10 @@
         <v>46051</v>
       </c>
       <c r="B152" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C152" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.3">
@@ -23023,10 +23101,10 @@
         <v>46052</v>
       </c>
       <c r="B153" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C153" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.3">
@@ -23034,7 +23112,7 @@
         <v>46053</v>
       </c>
       <c r="B154" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C154" t="s">
         <v>11</v>
@@ -23045,10 +23123,10 @@
         <v>46054</v>
       </c>
       <c r="B155" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C155" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.3">
@@ -23056,7 +23134,7 @@
         <v>46055</v>
       </c>
       <c r="B156" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C156" t="s">
         <v>10</v>
@@ -23067,7 +23145,7 @@
         <v>46056</v>
       </c>
       <c r="B157" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C157" t="s">
         <v>14</v>
@@ -23078,10 +23156,10 @@
         <v>46057</v>
       </c>
       <c r="B158" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C158" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.3">
@@ -23089,10 +23167,10 @@
         <v>46058</v>
       </c>
       <c r="B159" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C159" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.3">
@@ -23100,10 +23178,10 @@
         <v>46059</v>
       </c>
       <c r="B160" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C160" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.3">
@@ -23111,7 +23189,7 @@
         <v>46060</v>
       </c>
       <c r="B161" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C161" t="s">
         <v>11</v>
@@ -23122,10 +23200,10 @@
         <v>46061</v>
       </c>
       <c r="B162" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C162" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.3">
@@ -23133,7 +23211,7 @@
         <v>46062</v>
       </c>
       <c r="B163" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C163" t="s">
         <v>10</v>
@@ -23144,7 +23222,7 @@
         <v>46063</v>
       </c>
       <c r="B164" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C164" t="s">
         <v>14</v>
@@ -23155,10 +23233,10 @@
         <v>46064</v>
       </c>
       <c r="B165" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C165" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.3">
@@ -23166,10 +23244,10 @@
         <v>46065</v>
       </c>
       <c r="B166" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C166" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.3">
@@ -23177,10 +23255,10 @@
         <v>46066</v>
       </c>
       <c r="B167" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C167" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.3">
@@ -23188,7 +23266,7 @@
         <v>46067</v>
       </c>
       <c r="B168" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C168" t="s">
         <v>11</v>
@@ -23199,10 +23277,10 @@
         <v>46068</v>
       </c>
       <c r="B169" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C169" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.3">
@@ -23210,7 +23288,7 @@
         <v>46069</v>
       </c>
       <c r="B170" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C170" t="s">
         <v>10</v>
@@ -23221,7 +23299,7 @@
         <v>46070</v>
       </c>
       <c r="B171" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C171" t="s">
         <v>14</v>
@@ -23232,10 +23310,10 @@
         <v>46071</v>
       </c>
       <c r="B172" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C172" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.3">
@@ -23243,10 +23321,10 @@
         <v>46072</v>
       </c>
       <c r="B173" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C173" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.3">
@@ -23254,10 +23332,10 @@
         <v>46073</v>
       </c>
       <c r="B174" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C174" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.3">
@@ -23265,7 +23343,7 @@
         <v>46074</v>
       </c>
       <c r="B175" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C175" t="s">
         <v>11</v>
@@ -23276,10 +23354,10 @@
         <v>46075</v>
       </c>
       <c r="B176" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C176" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.3">
@@ -23287,7 +23365,7 @@
         <v>46076</v>
       </c>
       <c r="B177" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C177" t="s">
         <v>10</v>
@@ -23298,7 +23376,7 @@
         <v>46077</v>
       </c>
       <c r="B178" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C178" t="s">
         <v>14</v>
@@ -23309,10 +23387,10 @@
         <v>46078</v>
       </c>
       <c r="B179" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C179" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.3">
@@ -23320,10 +23398,10 @@
         <v>46079</v>
       </c>
       <c r="B180" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C180" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.3">
@@ -23331,10 +23409,10 @@
         <v>46080</v>
       </c>
       <c r="B181" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C181" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.3">
@@ -23342,7 +23420,7 @@
         <v>46081</v>
       </c>
       <c r="B182" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C182" t="s">
         <v>11</v>
@@ -23353,10 +23431,10 @@
         <v>46082</v>
       </c>
       <c r="B183" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C183" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.3">
@@ -23364,7 +23442,7 @@
         <v>46083</v>
       </c>
       <c r="B184" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C184" t="s">
         <v>10</v>
@@ -23375,7 +23453,7 @@
         <v>46084</v>
       </c>
       <c r="B185" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C185" t="s">
         <v>14</v>
@@ -23386,10 +23464,10 @@
         <v>46085</v>
       </c>
       <c r="B186" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C186" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.3">
@@ -23397,10 +23475,10 @@
         <v>46086</v>
       </c>
       <c r="B187" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C187" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.3">
@@ -23408,10 +23486,10 @@
         <v>46087</v>
       </c>
       <c r="B188" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C188" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.3">
@@ -23419,7 +23497,7 @@
         <v>46088</v>
       </c>
       <c r="B189" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C189" t="s">
         <v>11</v>
@@ -23430,10 +23508,10 @@
         <v>46089</v>
       </c>
       <c r="B190" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C190" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.3">
@@ -23441,7 +23519,7 @@
         <v>46090</v>
       </c>
       <c r="B191" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C191" t="s">
         <v>10</v>
@@ -23452,7 +23530,7 @@
         <v>46091</v>
       </c>
       <c r="B192" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C192" t="s">
         <v>14</v>
@@ -23463,10 +23541,10 @@
         <v>46092</v>
       </c>
       <c r="B193" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C193" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.3">
@@ -23474,10 +23552,10 @@
         <v>46093</v>
       </c>
       <c r="B194" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C194" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.3">
@@ -23485,10 +23563,10 @@
         <v>46094</v>
       </c>
       <c r="B195" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C195" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.3">
@@ -23496,7 +23574,7 @@
         <v>46095</v>
       </c>
       <c r="B196" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C196" t="s">
         <v>11</v>
@@ -23507,10 +23585,10 @@
         <v>46096</v>
       </c>
       <c r="B197" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C197" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.3">
@@ -23518,7 +23596,7 @@
         <v>46097</v>
       </c>
       <c r="B198" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C198" t="s">
         <v>10</v>
@@ -23529,7 +23607,7 @@
         <v>46098</v>
       </c>
       <c r="B199" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C199" t="s">
         <v>14</v>
@@ -23540,10 +23618,10 @@
         <v>46099</v>
       </c>
       <c r="B200" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C200" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.3">
@@ -23551,10 +23629,10 @@
         <v>46100</v>
       </c>
       <c r="B201" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C201" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.3">
@@ -23562,10 +23640,10 @@
         <v>46101</v>
       </c>
       <c r="B202" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C202" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.3">
@@ -23573,7 +23651,7 @@
         <v>46102</v>
       </c>
       <c r="B203" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C203" t="s">
         <v>11</v>
@@ -23584,10 +23662,10 @@
         <v>46103</v>
       </c>
       <c r="B204" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C204" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.3">
@@ -23595,7 +23673,7 @@
         <v>46104</v>
       </c>
       <c r="B205" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C205" t="s">
         <v>10</v>
@@ -23606,7 +23684,7 @@
         <v>46105</v>
       </c>
       <c r="B206" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C206" t="s">
         <v>14</v>
@@ -23617,10 +23695,10 @@
         <v>46106</v>
       </c>
       <c r="B207" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C207" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.3">
@@ -23628,10 +23706,10 @@
         <v>46107</v>
       </c>
       <c r="B208" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C208" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.3">
@@ -23639,10 +23717,10 @@
         <v>46108</v>
       </c>
       <c r="B209" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C209" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.3">
@@ -23650,7 +23728,7 @@
         <v>46109</v>
       </c>
       <c r="B210" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C210" t="s">
         <v>11</v>
@@ -23661,10 +23739,10 @@
         <v>46110</v>
       </c>
       <c r="B211" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C211" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.3">
@@ -23672,7 +23750,7 @@
         <v>46111</v>
       </c>
       <c r="B212" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C212" t="s">
         <v>10</v>
@@ -23683,7 +23761,7 @@
         <v>46112</v>
       </c>
       <c r="B213" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C213" t="s">
         <v>14</v>
@@ -23694,10 +23772,10 @@
         <v>46113</v>
       </c>
       <c r="B214" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C214" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.3">
@@ -23705,10 +23783,10 @@
         <v>46114</v>
       </c>
       <c r="B215" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C215" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.3">
@@ -23716,10 +23794,10 @@
         <v>46115</v>
       </c>
       <c r="B216" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C216" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.3">
@@ -23727,7 +23805,7 @@
         <v>46116</v>
       </c>
       <c r="B217" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C217" t="s">
         <v>11</v>
@@ -23738,10 +23816,10 @@
         <v>46117</v>
       </c>
       <c r="B218" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C218" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.3">
@@ -23749,7 +23827,7 @@
         <v>46118</v>
       </c>
       <c r="B219" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C219" t="s">
         <v>10</v>
@@ -23760,7 +23838,7 @@
         <v>46119</v>
       </c>
       <c r="B220" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C220" t="s">
         <v>14</v>
@@ -23771,10 +23849,10 @@
         <v>46120</v>
       </c>
       <c r="B221" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C221" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.3">
@@ -23782,10 +23860,10 @@
         <v>46121</v>
       </c>
       <c r="B222" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C222" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.3">
@@ -23793,10 +23871,10 @@
         <v>46122</v>
       </c>
       <c r="B223" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C223" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.3">
@@ -23804,7 +23882,7 @@
         <v>46123</v>
       </c>
       <c r="B224" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C224" t="s">
         <v>11</v>
@@ -23815,10 +23893,10 @@
         <v>46124</v>
       </c>
       <c r="B225" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C225" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.3">
@@ -23826,7 +23904,7 @@
         <v>46125</v>
       </c>
       <c r="B226" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C226" t="s">
         <v>10</v>
@@ -23837,7 +23915,7 @@
         <v>46126</v>
       </c>
       <c r="B227" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C227" t="s">
         <v>14</v>
@@ -23848,10 +23926,10 @@
         <v>46127</v>
       </c>
       <c r="B228" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C228" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.3">
@@ -23859,10 +23937,10 @@
         <v>46128</v>
       </c>
       <c r="B229" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C229" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.3">
@@ -23870,10 +23948,10 @@
         <v>46129</v>
       </c>
       <c r="B230" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C230" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.3">
@@ -23881,7 +23959,7 @@
         <v>46130</v>
       </c>
       <c r="B231" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C231" t="s">
         <v>11</v>
@@ -23892,10 +23970,10 @@
         <v>46131</v>
       </c>
       <c r="B232" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C232" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.3">
@@ -23903,7 +23981,7 @@
         <v>46132</v>
       </c>
       <c r="B233" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C233" t="s">
         <v>10</v>
@@ -23914,7 +23992,7 @@
         <v>46133</v>
       </c>
       <c r="B234" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C234" t="s">
         <v>14</v>
@@ -23925,10 +24003,10 @@
         <v>46134</v>
       </c>
       <c r="B235" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C235" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="236" spans="1:3" x14ac:dyDescent="0.3">
@@ -23936,10 +24014,10 @@
         <v>46135</v>
       </c>
       <c r="B236" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C236" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="237" spans="1:3" x14ac:dyDescent="0.3">
@@ -23947,10 +24025,10 @@
         <v>46136</v>
       </c>
       <c r="B237" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C237" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="238" spans="1:3" x14ac:dyDescent="0.3">
@@ -23958,7 +24036,7 @@
         <v>46137</v>
       </c>
       <c r="B238" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C238" t="s">
         <v>11</v>
@@ -23969,10 +24047,10 @@
         <v>46138</v>
       </c>
       <c r="B239" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C239" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.3">
@@ -23980,7 +24058,7 @@
         <v>46139</v>
       </c>
       <c r="B240" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C240" t="s">
         <v>10</v>
@@ -23991,7 +24069,7 @@
         <v>46140</v>
       </c>
       <c r="B241" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C241" t="s">
         <v>14</v>
@@ -24002,10 +24080,10 @@
         <v>46141</v>
       </c>
       <c r="B242" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C242" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.3">
@@ -24013,10 +24091,10 @@
         <v>46142</v>
       </c>
       <c r="B243" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C243" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.3">
@@ -24024,10 +24102,10 @@
         <v>46143</v>
       </c>
       <c r="B244" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C244" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="245" spans="1:3" x14ac:dyDescent="0.3">
@@ -24035,7 +24113,7 @@
         <v>46144</v>
       </c>
       <c r="B245" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C245" t="s">
         <v>11</v>
@@ -24046,10 +24124,10 @@
         <v>46145</v>
       </c>
       <c r="B246" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C246" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.3">
@@ -24057,7 +24135,7 @@
         <v>46146</v>
       </c>
       <c r="B247" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C247" t="s">
         <v>10</v>
@@ -24068,7 +24146,7 @@
         <v>46147</v>
       </c>
       <c r="B248" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C248" t="s">
         <v>14</v>
@@ -24079,10 +24157,10 @@
         <v>46148</v>
       </c>
       <c r="B249" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C249" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="250" spans="1:3" x14ac:dyDescent="0.3">
@@ -24090,10 +24168,10 @@
         <v>46149</v>
       </c>
       <c r="B250" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C250" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="251" spans="1:3" x14ac:dyDescent="0.3">
@@ -24101,10 +24179,10 @@
         <v>46150</v>
       </c>
       <c r="B251" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C251" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.3">
@@ -24112,7 +24190,7 @@
         <v>46151</v>
       </c>
       <c r="B252" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C252" t="s">
         <v>11</v>
@@ -24123,10 +24201,10 @@
         <v>46152</v>
       </c>
       <c r="B253" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C253" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.3">
@@ -24134,7 +24212,7 @@
         <v>46153</v>
       </c>
       <c r="B254" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C254" t="s">
         <v>10</v>
@@ -24145,7 +24223,7 @@
         <v>46154</v>
       </c>
       <c r="B255" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C255" t="s">
         <v>14</v>
@@ -24156,10 +24234,10 @@
         <v>46155</v>
       </c>
       <c r="B256" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C256" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="257" spans="1:3" x14ac:dyDescent="0.3">
@@ -24167,10 +24245,10 @@
         <v>46156</v>
       </c>
       <c r="B257" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C257" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="258" spans="1:3" x14ac:dyDescent="0.3">
@@ -24178,10 +24256,10 @@
         <v>46157</v>
       </c>
       <c r="B258" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C258" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="259" spans="1:3" x14ac:dyDescent="0.3">
@@ -24189,7 +24267,7 @@
         <v>46158</v>
       </c>
       <c r="B259" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C259" t="s">
         <v>11</v>
@@ -24200,10 +24278,10 @@
         <v>46159</v>
       </c>
       <c r="B260" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C260" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="261" spans="1:3" x14ac:dyDescent="0.3">
@@ -24211,7 +24289,7 @@
         <v>46160</v>
       </c>
       <c r="B261" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C261" t="s">
         <v>10</v>
@@ -24222,7 +24300,7 @@
         <v>46161</v>
       </c>
       <c r="B262" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C262" t="s">
         <v>14</v>
@@ -24233,10 +24311,10 @@
         <v>46162</v>
       </c>
       <c r="B263" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C263" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="264" spans="1:3" x14ac:dyDescent="0.3">
@@ -24244,10 +24322,10 @@
         <v>46163</v>
       </c>
       <c r="B264" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C264" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="265" spans="1:3" x14ac:dyDescent="0.3">
@@ -24255,10 +24333,10 @@
         <v>46164</v>
       </c>
       <c r="B265" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C265" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.3">
@@ -24266,7 +24344,7 @@
         <v>46165</v>
       </c>
       <c r="B266" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C266" t="s">
         <v>11</v>
@@ -24277,10 +24355,10 @@
         <v>46166</v>
       </c>
       <c r="B267" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C267" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.3">
@@ -24288,7 +24366,7 @@
         <v>46167</v>
       </c>
       <c r="B268" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C268" t="s">
         <v>10</v>
@@ -24299,7 +24377,7 @@
         <v>46168</v>
       </c>
       <c r="B269" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C269" t="s">
         <v>14</v>
@@ -24310,10 +24388,10 @@
         <v>46169</v>
       </c>
       <c r="B270" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C270" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="271" spans="1:3" x14ac:dyDescent="0.3">
@@ -24321,10 +24399,10 @@
         <v>46170</v>
       </c>
       <c r="B271" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C271" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="272" spans="1:3" x14ac:dyDescent="0.3">
@@ -24332,10 +24410,10 @@
         <v>46171</v>
       </c>
       <c r="B272" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C272" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.3">
@@ -24343,7 +24421,7 @@
         <v>46172</v>
       </c>
       <c r="B273" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C273" t="s">
         <v>11</v>
@@ -24354,10 +24432,10 @@
         <v>46173</v>
       </c>
       <c r="B274" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C274" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.3">
@@ -24365,7 +24443,7 @@
         <v>46174</v>
       </c>
       <c r="B275" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C275" t="s">
         <v>10</v>
@@ -24376,7 +24454,7 @@
         <v>46175</v>
       </c>
       <c r="B276" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C276" t="s">
         <v>14</v>
@@ -24387,10 +24465,10 @@
         <v>46176</v>
       </c>
       <c r="B277" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C277" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.3">
@@ -24398,10 +24476,10 @@
         <v>46177</v>
       </c>
       <c r="B278" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C278" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="279" spans="1:3" x14ac:dyDescent="0.3">
@@ -24409,10 +24487,10 @@
         <v>46178</v>
       </c>
       <c r="B279" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C279" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.3">
@@ -24420,7 +24498,7 @@
         <v>46179</v>
       </c>
       <c r="B280" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C280" t="s">
         <v>11</v>
@@ -24431,10 +24509,10 @@
         <v>46180</v>
       </c>
       <c r="B281" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C281" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="282" spans="1:3" x14ac:dyDescent="0.3">
@@ -24442,7 +24520,7 @@
         <v>46181</v>
       </c>
       <c r="B282" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C282" t="s">
         <v>10</v>
@@ -24453,7 +24531,7 @@
         <v>46182</v>
       </c>
       <c r="B283" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C283" t="s">
         <v>14</v>
@@ -24464,10 +24542,10 @@
         <v>46183</v>
       </c>
       <c r="B284" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C284" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="285" spans="1:3" x14ac:dyDescent="0.3">
@@ -24475,10 +24553,10 @@
         <v>46184</v>
       </c>
       <c r="B285" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C285" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.3">
@@ -24486,10 +24564,10 @@
         <v>46185</v>
       </c>
       <c r="B286" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C286" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.3">
@@ -24497,7 +24575,7 @@
         <v>46186</v>
       </c>
       <c r="B287" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C287" t="s">
         <v>11</v>
@@ -24508,10 +24586,10 @@
         <v>46187</v>
       </c>
       <c r="B288" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C288" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.3">
@@ -24519,7 +24597,7 @@
         <v>46188</v>
       </c>
       <c r="B289" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C289" t="s">
         <v>10</v>
@@ -24530,7 +24608,7 @@
         <v>46189</v>
       </c>
       <c r="B290" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C290" t="s">
         <v>14</v>
@@ -24541,10 +24619,10 @@
         <v>46190</v>
       </c>
       <c r="B291" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C291" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.3">
@@ -24552,10 +24630,10 @@
         <v>46191</v>
       </c>
       <c r="B292" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C292" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.3">
@@ -24563,10 +24641,10 @@
         <v>46192</v>
       </c>
       <c r="B293" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C293" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="294" spans="1:3" x14ac:dyDescent="0.3">
@@ -24574,7 +24652,7 @@
         <v>46193</v>
       </c>
       <c r="B294" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C294" t="s">
         <v>11</v>
@@ -24585,10 +24663,10 @@
         <v>46194</v>
       </c>
       <c r="B295" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C295" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.3">
@@ -24596,7 +24674,7 @@
         <v>46195</v>
       </c>
       <c r="B296" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C296" t="s">
         <v>10</v>
@@ -24607,7 +24685,7 @@
         <v>46196</v>
       </c>
       <c r="B297" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C297" t="s">
         <v>14</v>
@@ -24618,10 +24696,10 @@
         <v>46197</v>
       </c>
       <c r="B298" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C298" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="299" spans="1:3" x14ac:dyDescent="0.3">
@@ -24629,10 +24707,10 @@
         <v>46198</v>
       </c>
       <c r="B299" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C299" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="300" spans="1:3" x14ac:dyDescent="0.3">
@@ -24640,10 +24718,10 @@
         <v>46199</v>
       </c>
       <c r="B300" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C300" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.3">
@@ -24651,7 +24729,7 @@
         <v>46200</v>
       </c>
       <c r="B301" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C301" t="s">
         <v>11</v>
@@ -24662,10 +24740,10 @@
         <v>46201</v>
       </c>
       <c r="B302" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C302" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.3">
@@ -24673,7 +24751,7 @@
         <v>46202</v>
       </c>
       <c r="B303" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C303" t="s">
         <v>10</v>
@@ -24684,7 +24762,7 @@
         <v>46203</v>
       </c>
       <c r="B304" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C304" t="s">
         <v>14</v>
@@ -24695,10 +24773,10 @@
         <v>46204</v>
       </c>
       <c r="B305" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C305" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.3">
@@ -24706,10 +24784,10 @@
         <v>46205</v>
       </c>
       <c r="B306" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C306" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="307" spans="1:3" x14ac:dyDescent="0.3">
@@ -24717,10 +24795,10 @@
         <v>46206</v>
       </c>
       <c r="B307" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C307" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="308" spans="1:3" x14ac:dyDescent="0.3">
@@ -24728,7 +24806,7 @@
         <v>46207</v>
       </c>
       <c r="B308" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C308" t="s">
         <v>11</v>
@@ -24739,10 +24817,10 @@
         <v>46208</v>
       </c>
       <c r="B309" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C309" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="310" spans="1:3" x14ac:dyDescent="0.3">
@@ -24750,7 +24828,7 @@
         <v>46209</v>
       </c>
       <c r="B310" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C310" t="s">
         <v>10</v>
@@ -24761,7 +24839,7 @@
         <v>46210</v>
       </c>
       <c r="B311" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C311" t="s">
         <v>14</v>
@@ -24772,10 +24850,10 @@
         <v>46211</v>
       </c>
       <c r="B312" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C312" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="313" spans="1:3" x14ac:dyDescent="0.3">
@@ -24783,10 +24861,10 @@
         <v>46212</v>
       </c>
       <c r="B313" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C313" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="314" spans="1:3" x14ac:dyDescent="0.3">
@@ -24794,10 +24872,10 @@
         <v>46213</v>
       </c>
       <c r="B314" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C314" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="315" spans="1:3" x14ac:dyDescent="0.3">
@@ -24805,7 +24883,7 @@
         <v>46214</v>
       </c>
       <c r="B315" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C315" t="s">
         <v>11</v>
@@ -24816,10 +24894,10 @@
         <v>46215</v>
       </c>
       <c r="B316" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C316" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.3">
@@ -24827,7 +24905,7 @@
         <v>46216</v>
       </c>
       <c r="B317" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C317" t="s">
         <v>10</v>
@@ -24838,7 +24916,7 @@
         <v>46217</v>
       </c>
       <c r="B318" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C318" t="s">
         <v>14</v>
@@ -24849,10 +24927,10 @@
         <v>46218</v>
       </c>
       <c r="B319" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C319" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="320" spans="1:3" x14ac:dyDescent="0.3">
@@ -24860,10 +24938,10 @@
         <v>46219</v>
       </c>
       <c r="B320" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C320" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="321" spans="1:3" x14ac:dyDescent="0.3">
@@ -24871,10 +24949,10 @@
         <v>46220</v>
       </c>
       <c r="B321" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C321" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="322" spans="1:3" x14ac:dyDescent="0.3">
@@ -24882,7 +24960,7 @@
         <v>46221</v>
       </c>
       <c r="B322" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C322" t="s">
         <v>11</v>
@@ -24893,10 +24971,10 @@
         <v>46222</v>
       </c>
       <c r="B323" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C323" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="324" spans="1:3" x14ac:dyDescent="0.3">
@@ -24904,7 +24982,7 @@
         <v>46223</v>
       </c>
       <c r="B324" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C324" t="s">
         <v>10</v>
@@ -24915,7 +24993,7 @@
         <v>46224</v>
       </c>
       <c r="B325" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C325" t="s">
         <v>14</v>
@@ -24926,10 +25004,10 @@
         <v>46225</v>
       </c>
       <c r="B326" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C326" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="327" spans="1:3" x14ac:dyDescent="0.3">
@@ -24937,10 +25015,10 @@
         <v>46226</v>
       </c>
       <c r="B327" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C327" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="328" spans="1:3" x14ac:dyDescent="0.3">
@@ -24948,10 +25026,10 @@
         <v>46227</v>
       </c>
       <c r="B328" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C328" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="329" spans="1:3" x14ac:dyDescent="0.3">
@@ -24959,7 +25037,7 @@
         <v>46228</v>
       </c>
       <c r="B329" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C329" t="s">
         <v>11</v>
@@ -24970,10 +25048,10 @@
         <v>46229</v>
       </c>
       <c r="B330" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C330" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="331" spans="1:3" x14ac:dyDescent="0.3">
@@ -24981,7 +25059,7 @@
         <v>46230</v>
       </c>
       <c r="B331" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C331" t="s">
         <v>10</v>
@@ -24992,7 +25070,7 @@
         <v>46231</v>
       </c>
       <c r="B332" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C332" t="s">
         <v>14</v>
@@ -25003,10 +25081,10 @@
         <v>46232</v>
       </c>
       <c r="B333" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C333" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="334" spans="1:3" x14ac:dyDescent="0.3">
@@ -25014,10 +25092,10 @@
         <v>46233</v>
       </c>
       <c r="B334" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C334" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="335" spans="1:3" x14ac:dyDescent="0.3">
@@ -25025,10 +25103,10 @@
         <v>46234</v>
       </c>
       <c r="B335" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C335" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -25043,36 +25121,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
         <v>64</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D2" t="s">
         <v>65</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>66</v>
-      </c>
-      <c r="D2" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -25087,10 +25165,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>
@@ -25105,13 +25183,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -25119,10 +25197,10 @@
         <v>45926</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
@@ -25130,10 +25208,10 @@
         <v>45943</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -25141,10 +25219,10 @@
         <v>45999</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -25152,10 +25230,10 @@
         <v>46050</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
@@ -25163,10 +25241,10 @@
         <v>46087</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
@@ -25174,10 +25252,10 @@
         <v>46101</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -25185,10 +25263,10 @@
         <v>46135</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
@@ -25196,10 +25274,10 @@
         <v>46143</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -25207,10 +25285,10 @@
         <v>46185</v>
       </c>
       <c r="B10" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
@@ -25218,10 +25296,10 @@
         <v>46202</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -25236,7 +25314,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -25245,63 +25323,63 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" t="s">
         <v>88</v>
-      </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C3" t="s">
         <v>91</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>92</v>
-      </c>
-      <c r="C3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" t="s">
+        <v>94</v>
+      </c>
+      <c r="C4" t="s">
         <v>95</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" t="s">
         <v>96</v>
-      </c>
-      <c r="C4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
+        <v>97</v>
+      </c>
+      <c r="B5" t="s">
+        <v>98</v>
+      </c>
+      <c r="C5" t="s">
         <v>99</v>
       </c>
-      <c r="B5" t="s">
+      <c r="D5" t="s">
         <v>100</v>
-      </c>
-      <c r="C5" t="s">
-        <v>101</v>
-      </c>
-      <c r="D5" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -25309,27 +25387,27 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D6" t="s">
         <v>103</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" t="s">
         <v>106</v>
-      </c>
-      <c r="C7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/app_horarios/datos/excel/export-15-04.xlsx
+++ b/app_horarios/datos/excel/export-15-04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\Ingeniería informática\4º Trabajo de Fin de Grado\Trabajo-Fin-de-Grado-2025-2026\app_horarios\datos\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86D8BE3B-B62A-4F90-AC16-170140AFF7EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52115464-5F14-462F-868F-4460992DB328}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="asignaturas" sheetId="1" r:id="rId1"/>
@@ -8727,7 +8727,7 @@
         <v>6392</v>
       </c>
       <c r="E2">
-        <v>25</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">

--- a/app_horarios/datos/excel/export-15-04.xlsx
+++ b/app_horarios/datos/excel/export-15-04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\Ingeniería informática\4º Trabajo de Fin de Grado\Trabajo-Fin-de-Grado-2025-2026\app_horarios\datos\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E5D0545-00F3-4165-92C4-376C6897CCA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F8DCF0-5CDF-4DBA-AC33-6495C1219F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="asignaturas" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1864" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="582">
   <si>
     <t>IDASIGNATURA</t>
   </si>
@@ -1797,6 +1797,9 @@
   </si>
   <si>
     <t>Lab 46-A1</t>
+  </si>
+  <si>
+    <t>Aula 0</t>
   </si>
 </sst>
 </file>
@@ -2262,6 +2265,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="44.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
@@ -15628,7 +15632,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O60"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
@@ -17237,6 +17241,17 @@
         <v>267</v>
       </c>
       <c r="O60" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>60</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>581</v>
+      </c>
+      <c r="O61" t="s">
         <v>35</v>
       </c>
     </row>

--- a/app_horarios/datos/excel/export-15-04.xlsx
+++ b/app_horarios/datos/excel/export-15-04.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\usuario\Desktop\Ingeniería informática\4º Trabajo de Fin de Grado\Trabajo-Fin-de-Grado-2025-2026\app_horarios\datos\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F8DCF0-5CDF-4DBA-AC33-6495C1219F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0932203-CB09-4436-8A1E-E503933AFB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="asignaturas" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1866" uniqueCount="582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1836" uniqueCount="567">
   <si>
     <t>IDASIGNATURA</t>
   </si>
@@ -398,9 +398,6 @@
     <t>HORA_FIN</t>
   </si>
   <si>
-    <t>R0001</t>
-  </si>
-  <si>
     <t>P</t>
   </si>
   <si>
@@ -410,18 +407,12 @@
     <t>17:43:00</t>
   </si>
   <si>
-    <t>R0002</t>
-  </si>
-  <si>
     <t>18:00:00</t>
   </si>
   <si>
     <t>19:00:00</t>
   </si>
   <si>
-    <t>R0003</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
@@ -431,9 +422,6 @@
     <t>12:00:00</t>
   </si>
   <si>
-    <t>R0004</t>
-  </si>
-  <si>
     <t>R</t>
   </si>
   <si>
@@ -443,61 +431,28 @@
     <t>15:00:00</t>
   </si>
   <si>
-    <t>R0005</t>
-  </si>
-  <si>
     <t>16:00:00</t>
   </si>
   <si>
-    <t>R0006</t>
-  </si>
-  <si>
     <t>11:00:00</t>
   </si>
   <si>
-    <t>R0007</t>
-  </si>
-  <si>
-    <t>R0008</t>
-  </si>
-  <si>
-    <t>R0009</t>
-  </si>
-  <si>
-    <t>R0010</t>
-  </si>
-  <si>
     <t>16:30:00</t>
   </si>
   <si>
     <t>18:30:00</t>
   </si>
   <si>
-    <t>R0011</t>
-  </si>
-  <si>
-    <t>R0012</t>
-  </si>
-  <si>
-    <t>R0013</t>
-  </si>
-  <si>
     <t>11:30:00</t>
   </si>
   <si>
     <t>12:30:00</t>
   </si>
   <si>
-    <t>R0014</t>
-  </si>
-  <si>
     <t>17:28:00</t>
   </si>
   <si>
     <t>18:29:00</t>
-  </si>
-  <si>
-    <t>R0015</t>
   </si>
   <si>
     <t>17:00:00</t>
@@ -2302,7 +2257,7 @@
         <v>8797</v>
       </c>
       <c r="B2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="C2" t="s">
         <v>9</v>
@@ -2365,7 +2320,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2392,10 +2347,10 @@
         <v>8800</v>
       </c>
       <c r="B5" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="C5" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2422,10 +2377,10 @@
         <v>8796</v>
       </c>
       <c r="B6" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="C6" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2452,10 +2407,10 @@
         <v>8801</v>
       </c>
       <c r="B7" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
       <c r="C7" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2482,10 +2437,10 @@
         <v>8802</v>
       </c>
       <c r="B8" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="C8" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2512,10 +2467,10 @@
         <v>8803</v>
       </c>
       <c r="B9" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
       <c r="C9" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2542,10 +2497,10 @@
         <v>8804</v>
       </c>
       <c r="B10" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="C10" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2572,10 +2527,10 @@
         <v>8805</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="C11" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2602,10 +2557,10 @@
         <v>8806</v>
       </c>
       <c r="B12" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="C12" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -2632,10 +2587,10 @@
         <v>8807</v>
       </c>
       <c r="B13" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="C13" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -2662,10 +2617,10 @@
         <v>8808</v>
       </c>
       <c r="B14" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="C14" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="D14">
         <v>2</v>
@@ -2692,10 +2647,10 @@
         <v>8809</v>
       </c>
       <c r="B15" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="C15" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="D15">
         <v>2</v>
@@ -2722,10 +2677,10 @@
         <v>8810</v>
       </c>
       <c r="B16" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="C16" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="D16">
         <v>2</v>
@@ -2752,10 +2707,10 @@
         <v>8811</v>
       </c>
       <c r="B17" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="C17" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -2782,10 +2737,10 @@
         <v>8812</v>
       </c>
       <c r="B18" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="C18" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="D18">
         <v>2</v>
@@ -2812,10 +2767,10 @@
         <v>8813</v>
       </c>
       <c r="B19" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="C19" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="D19">
         <v>2</v>
@@ -2842,10 +2797,10 @@
         <v>8814</v>
       </c>
       <c r="B20" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="C20" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="D20">
         <v>2</v>
@@ -2872,10 +2827,10 @@
         <v>8815</v>
       </c>
       <c r="B21" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="C21" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="D21">
         <v>2</v>
@@ -2902,10 +2857,10 @@
         <v>8816</v>
       </c>
       <c r="B22" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="C22" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
       <c r="D22">
         <v>3</v>
@@ -2932,10 +2887,10 @@
         <v>8817</v>
       </c>
       <c r="B23" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="C23" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -2962,10 +2917,10 @@
         <v>8818</v>
       </c>
       <c r="B24" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="C24" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="D24">
         <v>3</v>
@@ -2992,10 +2947,10 @@
         <v>8819</v>
       </c>
       <c r="B25" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="C25" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="D25">
         <v>3</v>
@@ -3022,10 +2977,10 @@
         <v>8820</v>
       </c>
       <c r="B26" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="C26" t="s">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="D26">
         <v>3</v>
@@ -3052,10 +3007,10 @@
         <v>8824</v>
       </c>
       <c r="B27" t="s">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="C27" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="D27">
         <v>3</v>
@@ -3082,10 +3037,10 @@
         <v>8823</v>
       </c>
       <c r="B28" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="C28" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -3112,10 +3067,10 @@
         <v>8825</v>
       </c>
       <c r="B29" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="C29" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -3142,10 +3097,10 @@
         <v>8821</v>
       </c>
       <c r="B30" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="C30" t="s">
-        <v>323</v>
+        <v>308</v>
       </c>
       <c r="D30">
         <v>3</v>
@@ -3172,10 +3127,10 @@
         <v>8822</v>
       </c>
       <c r="B31" t="s">
-        <v>324</v>
+        <v>309</v>
       </c>
       <c r="C31" t="s">
-        <v>325</v>
+        <v>310</v>
       </c>
       <c r="D31">
         <v>3</v>
@@ -3202,10 +3157,10 @@
         <v>8827</v>
       </c>
       <c r="B32" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
       <c r="C32" t="s">
-        <v>327</v>
+        <v>312</v>
       </c>
       <c r="D32">
         <v>4</v>
@@ -3221,7 +3176,7 @@
         <v>281</v>
       </c>
       <c r="H32" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I32">
         <v>2</v>
@@ -3232,10 +3187,10 @@
         <v>8828</v>
       </c>
       <c r="B33" t="s">
-        <v>328</v>
+        <v>313</v>
       </c>
       <c r="C33" t="s">
-        <v>329</v>
+        <v>314</v>
       </c>
       <c r="D33">
         <v>4</v>
@@ -3251,7 +3206,7 @@
         <v>281</v>
       </c>
       <c r="H33" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I33">
         <v>2</v>
@@ -3262,10 +3217,10 @@
         <v>8829</v>
       </c>
       <c r="B34" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="C34" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="D34">
         <v>4</v>
@@ -3281,7 +3236,7 @@
         <v>281</v>
       </c>
       <c r="H34" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I34">
         <v>2</v>
@@ -3292,10 +3247,10 @@
         <v>8830</v>
       </c>
       <c r="B35" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="C35" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="D35">
         <v>4</v>
@@ -3311,7 +3266,7 @@
         <v>281</v>
       </c>
       <c r="H35" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I35">
         <v>2</v>
@@ -3322,10 +3277,10 @@
         <v>8831</v>
       </c>
       <c r="B36" t="s">
-        <v>334</v>
+        <v>319</v>
       </c>
       <c r="C36" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="D36">
         <v>4</v>
@@ -3341,7 +3296,7 @@
         <v>281</v>
       </c>
       <c r="H36" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I36">
         <v>2</v>
@@ -3352,10 +3307,10 @@
         <v>8832</v>
       </c>
       <c r="B37" t="s">
-        <v>336</v>
+        <v>321</v>
       </c>
       <c r="C37" t="s">
-        <v>337</v>
+        <v>322</v>
       </c>
       <c r="D37">
         <v>4</v>
@@ -3371,7 +3326,7 @@
         <v>281</v>
       </c>
       <c r="H37" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I37">
         <v>2</v>
@@ -3382,10 +3337,10 @@
         <v>8833</v>
       </c>
       <c r="B38" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="C38" t="s">
-        <v>339</v>
+        <v>324</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -3401,7 +3356,7 @@
         <v>281</v>
       </c>
       <c r="H38" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I38">
         <v>2</v>
@@ -3412,10 +3367,10 @@
         <v>8834</v>
       </c>
       <c r="B39" t="s">
-        <v>340</v>
+        <v>325</v>
       </c>
       <c r="C39" t="s">
-        <v>341</v>
+        <v>326</v>
       </c>
       <c r="D39">
         <v>4</v>
@@ -3431,7 +3386,7 @@
         <v>281</v>
       </c>
       <c r="H39" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I39">
         <v>2</v>
@@ -3442,10 +3397,10 @@
         <v>8835</v>
       </c>
       <c r="B40" t="s">
-        <v>342</v>
+        <v>327</v>
       </c>
       <c r="C40" t="s">
-        <v>343</v>
+        <v>328</v>
       </c>
       <c r="D40">
         <v>4</v>
@@ -3461,7 +3416,7 @@
         <v>281</v>
       </c>
       <c r="H40" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I40">
         <v>2</v>
@@ -3472,10 +3427,10 @@
         <v>8836</v>
       </c>
       <c r="B41" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="C41" t="s">
-        <v>345</v>
+        <v>330</v>
       </c>
       <c r="D41">
         <v>4</v>
@@ -3491,7 +3446,7 @@
         <v>281</v>
       </c>
       <c r="H41" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I41">
         <v>2</v>
@@ -3502,10 +3457,10 @@
         <v>8837</v>
       </c>
       <c r="B42" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="C42" t="s">
-        <v>347</v>
+        <v>332</v>
       </c>
       <c r="D42">
         <v>4</v>
@@ -3521,7 +3476,7 @@
         <v>281</v>
       </c>
       <c r="H42" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I42">
         <v>2</v>
@@ -3532,10 +3487,10 @@
         <v>8838</v>
       </c>
       <c r="B43" t="s">
-        <v>348</v>
+        <v>333</v>
       </c>
       <c r="C43" t="s">
-        <v>349</v>
+        <v>334</v>
       </c>
       <c r="D43">
         <v>4</v>
@@ -3551,7 +3506,7 @@
         <v>281</v>
       </c>
       <c r="H43" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I43">
         <v>2</v>
@@ -3562,10 +3517,10 @@
         <v>8842</v>
       </c>
       <c r="B44" t="s">
-        <v>350</v>
+        <v>335</v>
       </c>
       <c r="C44" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="D44">
         <v>4</v>
@@ -3581,7 +3536,7 @@
         <v>281</v>
       </c>
       <c r="H44" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I44">
         <v>2</v>
@@ -3592,10 +3547,10 @@
         <v>8843</v>
       </c>
       <c r="B45" t="s">
-        <v>352</v>
+        <v>337</v>
       </c>
       <c r="C45" t="s">
-        <v>353</v>
+        <v>338</v>
       </c>
       <c r="D45">
         <v>4</v>
@@ -3611,7 +3566,7 @@
         <v>281</v>
       </c>
       <c r="H45" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I45">
         <v>2</v>
@@ -3622,7 +3577,7 @@
         <v>6392</v>
       </c>
       <c r="B46" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
@@ -3652,10 +3607,10 @@
         <v>6393</v>
       </c>
       <c r="B47" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="C47" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="D47">
         <v>1</v>
@@ -3682,10 +3637,10 @@
         <v>6394</v>
       </c>
       <c r="B48" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="C48" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -3712,10 +3667,10 @@
         <v>6395</v>
       </c>
       <c r="B49" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="C49" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -3772,10 +3727,10 @@
         <v>6397</v>
       </c>
       <c r="B51" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C51" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D51">
         <v>1</v>
@@ -3802,10 +3757,10 @@
         <v>6398</v>
       </c>
       <c r="B52" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="C52" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -3832,10 +3787,10 @@
         <v>6399</v>
       </c>
       <c r="B53" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="C53" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -3862,10 +3817,10 @@
         <v>6400</v>
       </c>
       <c r="B54" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C54" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -3892,10 +3847,10 @@
         <v>6401</v>
       </c>
       <c r="B55" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="C55" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -3922,10 +3877,10 @@
         <v>6402</v>
       </c>
       <c r="B56" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="C56" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="D56">
         <v>2</v>
@@ -3952,10 +3907,10 @@
         <v>6403</v>
       </c>
       <c r="B57" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="C57" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -3982,10 +3937,10 @@
         <v>6404</v>
       </c>
       <c r="B58" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="C58" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="D58">
         <v>2</v>
@@ -4012,10 +3967,10 @@
         <v>6405</v>
       </c>
       <c r="B59" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C59" t="s">
-        <v>376</v>
+        <v>361</v>
       </c>
       <c r="D59">
         <v>2</v>
@@ -4042,10 +3997,10 @@
         <v>6406</v>
       </c>
       <c r="B60" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="C60" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="D60">
         <v>2</v>
@@ -4072,10 +4027,10 @@
         <v>6407</v>
       </c>
       <c r="B61" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="C61" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="D61">
         <v>2</v>
@@ -4102,10 +4057,10 @@
         <v>6408</v>
       </c>
       <c r="B62" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="C62" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -4132,10 +4087,10 @@
         <v>6409</v>
       </c>
       <c r="B63" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="C63" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -4162,10 +4117,10 @@
         <v>6410</v>
       </c>
       <c r="B64" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="C64" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="D64">
         <v>2</v>
@@ -4192,10 +4147,10 @@
         <v>6411</v>
       </c>
       <c r="B65" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="C65" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="D65">
         <v>2</v>
@@ -4222,10 +4177,10 @@
         <v>6412</v>
       </c>
       <c r="B66" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="C66" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="D66">
         <v>3</v>
@@ -4252,10 +4207,10 @@
         <v>6413</v>
       </c>
       <c r="B67" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="C67" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
       <c r="D67">
         <v>3</v>
@@ -4282,10 +4237,10 @@
         <v>6414</v>
       </c>
       <c r="B68" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="C68" t="s">
-        <v>394</v>
+        <v>379</v>
       </c>
       <c r="D68">
         <v>3</v>
@@ -4312,10 +4267,10 @@
         <v>6415</v>
       </c>
       <c r="B69" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="C69" t="s">
-        <v>396</v>
+        <v>381</v>
       </c>
       <c r="D69">
         <v>3</v>
@@ -4342,10 +4297,10 @@
         <v>6416</v>
       </c>
       <c r="B70" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="C70" t="s">
-        <v>398</v>
+        <v>383</v>
       </c>
       <c r="D70">
         <v>3</v>
@@ -4372,10 +4327,10 @@
         <v>6417</v>
       </c>
       <c r="B71" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C71" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -4402,10 +4357,10 @@
         <v>6418</v>
       </c>
       <c r="B72" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="C72" t="s">
-        <v>402</v>
+        <v>387</v>
       </c>
       <c r="D72">
         <v>3</v>
@@ -4432,10 +4387,10 @@
         <v>6419</v>
       </c>
       <c r="B73" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="C73" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="D73">
         <v>3</v>
@@ -4462,10 +4417,10 @@
         <v>6420</v>
       </c>
       <c r="B74" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="C74" t="s">
-        <v>406</v>
+        <v>391</v>
       </c>
       <c r="D74">
         <v>3</v>
@@ -4492,10 +4447,10 @@
         <v>6421</v>
       </c>
       <c r="B75" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="C75" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="D75">
         <v>3</v>
@@ -4522,10 +4477,10 @@
         <v>6422</v>
       </c>
       <c r="B76" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="C76" t="s">
-        <v>410</v>
+        <v>395</v>
       </c>
       <c r="D76">
         <v>4</v>
@@ -4552,10 +4507,10 @@
         <v>6423</v>
       </c>
       <c r="B77" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="C77" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="D77">
         <v>4</v>
@@ -4582,10 +4537,10 @@
         <v>6424</v>
       </c>
       <c r="B78" t="s">
-        <v>413</v>
+        <v>398</v>
       </c>
       <c r="C78" t="s">
-        <v>414</v>
+        <v>399</v>
       </c>
       <c r="D78">
         <v>4</v>
@@ -4601,7 +4556,7 @@
         <v>147</v>
       </c>
       <c r="H78" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I78">
         <v>2</v>
@@ -4612,10 +4567,10 @@
         <v>6425</v>
       </c>
       <c r="B79" t="s">
-        <v>415</v>
+        <v>400</v>
       </c>
       <c r="C79" t="s">
-        <v>416</v>
+        <v>401</v>
       </c>
       <c r="D79">
         <v>4</v>
@@ -4631,7 +4586,7 @@
         <v>147</v>
       </c>
       <c r="H79" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I79">
         <v>2</v>
@@ -4642,10 +4597,10 @@
         <v>6426</v>
       </c>
       <c r="B80" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="C80" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="D80">
         <v>4</v>
@@ -4661,7 +4616,7 @@
         <v>147</v>
       </c>
       <c r="H80" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I80">
         <v>2</v>
@@ -4672,10 +4627,10 @@
         <v>6427</v>
       </c>
       <c r="B81" t="s">
-        <v>419</v>
+        <v>404</v>
       </c>
       <c r="C81" t="s">
-        <v>420</v>
+        <v>405</v>
       </c>
       <c r="D81">
         <v>4</v>
@@ -4691,7 +4646,7 @@
         <v>147</v>
       </c>
       <c r="H81" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I81">
         <v>2</v>
@@ -4702,10 +4657,10 @@
         <v>6428</v>
       </c>
       <c r="B82" t="s">
-        <v>421</v>
+        <v>406</v>
       </c>
       <c r="C82" t="s">
-        <v>422</v>
+        <v>407</v>
       </c>
       <c r="D82">
         <v>4</v>
@@ -4721,7 +4676,7 @@
         <v>147</v>
       </c>
       <c r="H82" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I82">
         <v>2</v>
@@ -4732,10 +4687,10 @@
         <v>6429</v>
       </c>
       <c r="B83" t="s">
-        <v>423</v>
+        <v>408</v>
       </c>
       <c r="C83" t="s">
-        <v>424</v>
+        <v>409</v>
       </c>
       <c r="D83">
         <v>4</v>
@@ -4751,7 +4706,7 @@
         <v>147</v>
       </c>
       <c r="H83" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I83">
         <v>2</v>
@@ -4762,10 +4717,10 @@
         <v>6430</v>
       </c>
       <c r="B84" t="s">
-        <v>425</v>
+        <v>410</v>
       </c>
       <c r="C84" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="D84">
         <v>4</v>
@@ -4781,7 +4736,7 @@
         <v>147</v>
       </c>
       <c r="H84" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I84">
         <v>2</v>
@@ -4792,10 +4747,10 @@
         <v>6431</v>
       </c>
       <c r="B85" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="C85" t="s">
-        <v>428</v>
+        <v>413</v>
       </c>
       <c r="D85">
         <v>4</v>
@@ -4822,10 +4777,10 @@
         <v>6432</v>
       </c>
       <c r="B86" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="C86" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="D86">
         <v>4</v>
@@ -4852,10 +4807,10 @@
         <v>6302</v>
       </c>
       <c r="B87" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="C87" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4882,7 +4837,7 @@
         <v>6303</v>
       </c>
       <c r="B88" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="C88" t="s">
         <v>9</v>
@@ -4912,10 +4867,10 @@
         <v>6304</v>
       </c>
       <c r="B89" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="C89" t="s">
-        <v>356</v>
+        <v>341</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -4942,10 +4897,10 @@
         <v>6305</v>
       </c>
       <c r="B90" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C90" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -4972,10 +4927,10 @@
         <v>6306</v>
       </c>
       <c r="B91" t="s">
-        <v>357</v>
+        <v>342</v>
       </c>
       <c r="C91" t="s">
-        <v>358</v>
+        <v>343</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -5002,10 +4957,10 @@
         <v>6307</v>
       </c>
       <c r="B92" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="C92" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -5062,10 +5017,10 @@
         <v>6309</v>
       </c>
       <c r="B94" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="C94" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -5092,10 +5047,10 @@
         <v>6310</v>
       </c>
       <c r="B95" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C95" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -5122,10 +5077,10 @@
         <v>6311</v>
       </c>
       <c r="B96" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="C96" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -5152,10 +5107,10 @@
         <v>6312</v>
       </c>
       <c r="B97" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="C97" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="D97">
         <v>2</v>
@@ -5182,10 +5137,10 @@
         <v>6313</v>
       </c>
       <c r="B98" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="C98" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="D98">
         <v>2</v>
@@ -5212,10 +5167,10 @@
         <v>6314</v>
       </c>
       <c r="B99" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="C99" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -5242,10 +5197,10 @@
         <v>6315</v>
       </c>
       <c r="B100" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="C100" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="D100">
         <v>2</v>
@@ -5272,10 +5227,10 @@
         <v>6316</v>
       </c>
       <c r="B101" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="C101" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="D101">
         <v>2</v>
@@ -5302,10 +5257,10 @@
         <v>6317</v>
       </c>
       <c r="B102" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="C102" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D102">
         <v>2</v>
@@ -5332,10 +5287,10 @@
         <v>6318</v>
       </c>
       <c r="B103" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="C103" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -5362,10 +5317,10 @@
         <v>6319</v>
       </c>
       <c r="B104" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="C104" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D104">
         <v>2</v>
@@ -5392,10 +5347,10 @@
         <v>6320</v>
       </c>
       <c r="B105" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="C105" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -5422,10 +5377,10 @@
         <v>6321</v>
       </c>
       <c r="B106" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C106" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="D106">
         <v>2</v>
@@ -5452,10 +5407,10 @@
         <v>6322</v>
       </c>
       <c r="B107" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="C107" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="D107">
         <v>3</v>
@@ -5482,10 +5437,10 @@
         <v>6323</v>
       </c>
       <c r="B108" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="C108" t="s">
-        <v>437</v>
+        <v>422</v>
       </c>
       <c r="D108">
         <v>3</v>
@@ -5512,10 +5467,10 @@
         <v>6324</v>
       </c>
       <c r="B109" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="C109" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="D109">
         <v>3</v>
@@ -5542,10 +5497,10 @@
         <v>6325</v>
       </c>
       <c r="B110" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="C110" t="s">
-        <v>441</v>
+        <v>426</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -5572,10 +5527,10 @@
         <v>6326</v>
       </c>
       <c r="B111" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="C111" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="D111">
         <v>3</v>
@@ -5602,10 +5557,10 @@
         <v>6327</v>
       </c>
       <c r="B112" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="C112" t="s">
-        <v>445</v>
+        <v>430</v>
       </c>
       <c r="D112">
         <v>3</v>
@@ -5632,10 +5587,10 @@
         <v>6328</v>
       </c>
       <c r="B113" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="C113" t="s">
-        <v>447</v>
+        <v>432</v>
       </c>
       <c r="D113">
         <v>3</v>
@@ -5662,10 +5617,10 @@
         <v>6329</v>
       </c>
       <c r="B114" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="C114" t="s">
-        <v>449</v>
+        <v>434</v>
       </c>
       <c r="D114">
         <v>3</v>
@@ -5692,10 +5647,10 @@
         <v>6330</v>
       </c>
       <c r="B115" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="C115" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="D115">
         <v>3</v>
@@ -5722,10 +5677,10 @@
         <v>6331</v>
       </c>
       <c r="B116" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="C116" t="s">
-        <v>453</v>
+        <v>438</v>
       </c>
       <c r="D116">
         <v>3</v>
@@ -5752,10 +5707,10 @@
         <v>6332</v>
       </c>
       <c r="B117" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="C117" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="D117">
         <v>4</v>
@@ -5782,10 +5737,10 @@
         <v>6333</v>
       </c>
       <c r="B118" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="C118" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="D118">
         <v>4</v>
@@ -5812,10 +5767,10 @@
         <v>6334</v>
       </c>
       <c r="B119" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="C119" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="D119">
         <v>4</v>
@@ -5842,10 +5797,10 @@
         <v>6335</v>
       </c>
       <c r="B120" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="C120" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="D120">
         <v>4</v>
@@ -5872,10 +5827,10 @@
         <v>6336</v>
       </c>
       <c r="B121" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="C121" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="D121">
         <v>4</v>
@@ -5902,10 +5857,10 @@
         <v>8507</v>
       </c>
       <c r="B122" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="C122" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="D122">
         <v>4</v>
@@ -5921,7 +5876,7 @@
         <v>166</v>
       </c>
       <c r="H122" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I122">
         <v>2</v>
@@ -5932,10 +5887,10 @@
         <v>6338</v>
       </c>
       <c r="B123" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="C123" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="D123">
         <v>4</v>
@@ -5951,7 +5906,7 @@
         <v>166</v>
       </c>
       <c r="H123" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I123">
         <v>2</v>
@@ -5962,10 +5917,10 @@
         <v>6339</v>
       </c>
       <c r="B124" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="C124" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="D124">
         <v>4</v>
@@ -5981,7 +5936,7 @@
         <v>166</v>
       </c>
       <c r="H124" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I124">
         <v>2</v>
@@ -5992,10 +5947,10 @@
         <v>6340</v>
       </c>
       <c r="B125" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="C125" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="D125">
         <v>4</v>
@@ -6011,7 +5966,7 @@
         <v>166</v>
       </c>
       <c r="H125" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I125">
         <v>2</v>
@@ -6022,10 +5977,10 @@
         <v>6341</v>
       </c>
       <c r="B126" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="C126" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="D126">
         <v>4</v>
@@ -6041,7 +5996,7 @@
         <v>166</v>
       </c>
       <c r="H126" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I126">
         <v>2</v>
@@ -6052,10 +6007,10 @@
         <v>9115</v>
       </c>
       <c r="B127" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="C127" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="D127">
         <v>1</v>
@@ -6082,7 +6037,7 @@
         <v>9116</v>
       </c>
       <c r="B128" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="C128" t="s">
         <v>18</v>
@@ -6112,10 +6067,10 @@
         <v>9117</v>
       </c>
       <c r="B129" t="s">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="C129" t="s">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="D129">
         <v>1</v>
@@ -6172,10 +6127,10 @@
         <v>9119</v>
       </c>
       <c r="B131" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C131" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -6202,7 +6157,7 @@
         <v>9120</v>
       </c>
       <c r="B132" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="C132" t="s">
         <v>9</v>
@@ -6232,10 +6187,10 @@
         <v>9121</v>
       </c>
       <c r="B133" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="C133" t="s">
-        <v>364</v>
+        <v>349</v>
       </c>
       <c r="D133">
         <v>1</v>
@@ -6262,10 +6217,10 @@
         <v>9122</v>
       </c>
       <c r="B134" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="C134" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="D134">
         <v>1</v>
@@ -6292,10 +6247,10 @@
         <v>9123</v>
       </c>
       <c r="B135" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="C135" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="D135">
         <v>1</v>
@@ -6322,10 +6277,10 @@
         <v>9124</v>
       </c>
       <c r="B136" t="s">
-        <v>359</v>
+        <v>344</v>
       </c>
       <c r="C136" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -6352,10 +6307,10 @@
         <v>9125</v>
       </c>
       <c r="B137" t="s">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="C137" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="D137">
         <v>2</v>
@@ -6382,10 +6337,10 @@
         <v>9126</v>
       </c>
       <c r="B138" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C138" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
       <c r="D138">
         <v>2</v>
@@ -6412,10 +6367,10 @@
         <v>9127</v>
       </c>
       <c r="B139" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="C139" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="D139">
         <v>2</v>
@@ -6442,10 +6397,10 @@
         <v>9128</v>
       </c>
       <c r="B140" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="C140" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="D140">
         <v>2</v>
@@ -6472,10 +6427,10 @@
         <v>9129</v>
       </c>
       <c r="B141" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="C141" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="D141">
         <v>2</v>
@@ -6502,10 +6457,10 @@
         <v>9130</v>
       </c>
       <c r="B142" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="C142" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D142">
         <v>2</v>
@@ -6532,10 +6487,10 @@
         <v>9131</v>
       </c>
       <c r="B143" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="C143" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="D143">
         <v>2</v>
@@ -6562,10 +6517,10 @@
         <v>9132</v>
       </c>
       <c r="B144" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="C144" t="s">
-        <v>370</v>
+        <v>355</v>
       </c>
       <c r="D144">
         <v>2</v>
@@ -6592,10 +6547,10 @@
         <v>9133</v>
       </c>
       <c r="B145" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="C145" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D145">
         <v>2</v>
@@ -6622,10 +6577,10 @@
         <v>9134</v>
       </c>
       <c r="B146" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="C146" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D146">
         <v>2</v>
@@ -6652,10 +6607,10 @@
         <v>9135</v>
       </c>
       <c r="B147" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="C147" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="D147">
         <v>3</v>
@@ -6682,10 +6637,10 @@
         <v>9136</v>
       </c>
       <c r="B148" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="C148" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="D148">
         <v>3</v>
@@ -6712,10 +6667,10 @@
         <v>9137</v>
       </c>
       <c r="B149" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="C149" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="D149">
         <v>3</v>
@@ -6742,10 +6697,10 @@
         <v>9138</v>
       </c>
       <c r="B150" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="C150" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="D150">
         <v>3</v>
@@ -6772,10 +6727,10 @@
         <v>9139</v>
       </c>
       <c r="B151" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="C151" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="D151">
         <v>3</v>
@@ -6802,10 +6757,10 @@
         <v>9140</v>
       </c>
       <c r="B152" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="C152" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="D152">
         <v>3</v>
@@ -6832,10 +6787,10 @@
         <v>9141</v>
       </c>
       <c r="B153" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="C153" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="D153">
         <v>3</v>
@@ -6862,10 +6817,10 @@
         <v>9142</v>
       </c>
       <c r="B154" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="C154" t="s">
-        <v>493</v>
+        <v>478</v>
       </c>
       <c r="D154">
         <v>3</v>
@@ -6892,10 +6847,10 @@
         <v>9143</v>
       </c>
       <c r="B155" t="s">
-        <v>494</v>
+        <v>479</v>
       </c>
       <c r="C155" t="s">
-        <v>495</v>
+        <v>480</v>
       </c>
       <c r="D155">
         <v>3</v>
@@ -6922,10 +6877,10 @@
         <v>9144</v>
       </c>
       <c r="B156" t="s">
-        <v>496</v>
+        <v>481</v>
       </c>
       <c r="C156" t="s">
-        <v>497</v>
+        <v>482</v>
       </c>
       <c r="D156">
         <v>3</v>
@@ -6952,10 +6907,10 @@
         <v>9145</v>
       </c>
       <c r="B157" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="C157" t="s">
-        <v>412</v>
+        <v>397</v>
       </c>
       <c r="D157">
         <v>4</v>
@@ -6982,10 +6937,10 @@
         <v>9146</v>
       </c>
       <c r="B158" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="C158" t="s">
-        <v>498</v>
+        <v>483</v>
       </c>
       <c r="D158">
         <v>4</v>
@@ -7012,10 +6967,10 @@
         <v>9147</v>
       </c>
       <c r="B159" t="s">
-        <v>499</v>
+        <v>484</v>
       </c>
       <c r="C159" t="s">
-        <v>500</v>
+        <v>485</v>
       </c>
       <c r="D159">
         <v>4</v>
@@ -7042,10 +6997,10 @@
         <v>9148</v>
       </c>
       <c r="B160" t="s">
-        <v>501</v>
+        <v>486</v>
       </c>
       <c r="C160" t="s">
-        <v>502</v>
+        <v>487</v>
       </c>
       <c r="D160">
         <v>4</v>
@@ -7072,10 +7027,10 @@
         <v>9149</v>
       </c>
       <c r="B161" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="C161" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="D161">
         <v>4</v>
@@ -7102,10 +7057,10 @@
         <v>9151</v>
       </c>
       <c r="B162" t="s">
-        <v>505</v>
+        <v>490</v>
       </c>
       <c r="C162" t="s">
-        <v>506</v>
+        <v>491</v>
       </c>
       <c r="D162">
         <v>4</v>
@@ -7121,7 +7076,7 @@
         <v>291</v>
       </c>
       <c r="H162" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I162">
         <v>2</v>
@@ -7132,10 +7087,10 @@
         <v>9152</v>
       </c>
       <c r="B163" t="s">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="C163" t="s">
-        <v>508</v>
+        <v>493</v>
       </c>
       <c r="D163">
         <v>4</v>
@@ -7151,7 +7106,7 @@
         <v>291</v>
       </c>
       <c r="H163" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I163">
         <v>2</v>
@@ -7162,10 +7117,10 @@
         <v>9153</v>
       </c>
       <c r="B164" t="s">
-        <v>509</v>
+        <v>494</v>
       </c>
       <c r="C164" t="s">
-        <v>510</v>
+        <v>495</v>
       </c>
       <c r="D164">
         <v>4</v>
@@ -7181,7 +7136,7 @@
         <v>291</v>
       </c>
       <c r="H164" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I164">
         <v>2</v>
@@ -7192,10 +7147,10 @@
         <v>7711</v>
       </c>
       <c r="B165" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
       <c r="C165" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="D165">
         <v>1</v>
@@ -7222,10 +7177,10 @@
         <v>7712</v>
       </c>
       <c r="B166" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="C166" t="s">
-        <v>511</v>
+        <v>496</v>
       </c>
       <c r="D166">
         <v>1</v>
@@ -7252,10 +7207,10 @@
         <v>7713</v>
       </c>
       <c r="B167" t="s">
-        <v>355</v>
+        <v>340</v>
       </c>
       <c r="C167" t="s">
-        <v>512</v>
+        <v>497</v>
       </c>
       <c r="D167">
         <v>1</v>
@@ -7282,10 +7237,10 @@
         <v>7714</v>
       </c>
       <c r="B168" t="s">
-        <v>365</v>
+        <v>350</v>
       </c>
       <c r="C168" t="s">
-        <v>366</v>
+        <v>351</v>
       </c>
       <c r="D168">
         <v>1</v>
@@ -7312,10 +7267,10 @@
         <v>7715</v>
       </c>
       <c r="B169" t="s">
-        <v>513</v>
+        <v>498</v>
       </c>
       <c r="C169" t="s">
-        <v>514</v>
+        <v>499</v>
       </c>
       <c r="D169">
         <v>1</v>
@@ -7342,10 +7297,10 @@
         <v>7716</v>
       </c>
       <c r="B170" t="s">
-        <v>361</v>
+        <v>346</v>
       </c>
       <c r="C170" t="s">
-        <v>362</v>
+        <v>347</v>
       </c>
       <c r="D170">
         <v>1</v>
@@ -7402,10 +7357,10 @@
         <v>7718</v>
       </c>
       <c r="B172" t="s">
-        <v>363</v>
+        <v>348</v>
       </c>
       <c r="C172" t="s">
-        <v>515</v>
+        <v>500</v>
       </c>
       <c r="D172">
         <v>1</v>
@@ -7432,10 +7387,10 @@
         <v>7719</v>
       </c>
       <c r="B173" t="s">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="C173" t="s">
-        <v>517</v>
+        <v>502</v>
       </c>
       <c r="D173">
         <v>1</v>
@@ -7462,10 +7417,10 @@
         <v>7720</v>
       </c>
       <c r="B174" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="C174" t="s">
-        <v>368</v>
+        <v>353</v>
       </c>
       <c r="D174">
         <v>1</v>
@@ -7492,10 +7447,10 @@
         <v>7721</v>
       </c>
       <c r="B175" t="s">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="C175" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="D175">
         <v>1</v>
@@ -7522,10 +7477,10 @@
         <v>7722</v>
       </c>
       <c r="B176" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="C176" t="s">
-        <v>518</v>
+        <v>503</v>
       </c>
       <c r="D176">
         <v>2</v>
@@ -7552,10 +7507,10 @@
         <v>7723</v>
       </c>
       <c r="B177" t="s">
-        <v>373</v>
+        <v>358</v>
       </c>
       <c r="C177" t="s">
-        <v>374</v>
+        <v>359</v>
       </c>
       <c r="D177">
         <v>2</v>
@@ -7582,10 +7537,10 @@
         <v>7724</v>
       </c>
       <c r="B178" t="s">
-        <v>377</v>
+        <v>362</v>
       </c>
       <c r="C178" t="s">
-        <v>519</v>
+        <v>504</v>
       </c>
       <c r="D178">
         <v>2</v>
@@ -7612,10 +7567,10 @@
         <v>7725</v>
       </c>
       <c r="B179" t="s">
-        <v>371</v>
+        <v>356</v>
       </c>
       <c r="C179" t="s">
-        <v>372</v>
+        <v>357</v>
       </c>
       <c r="D179">
         <v>2</v>
@@ -7642,10 +7597,10 @@
         <v>7726</v>
       </c>
       <c r="B180" t="s">
-        <v>375</v>
+        <v>360</v>
       </c>
       <c r="C180" t="s">
-        <v>520</v>
+        <v>505</v>
       </c>
       <c r="D180">
         <v>2</v>
@@ -7672,10 +7627,10 @@
         <v>7727</v>
       </c>
       <c r="B181" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="C181" t="s">
-        <v>418</v>
+        <v>403</v>
       </c>
       <c r="D181">
         <v>2</v>
@@ -7702,10 +7657,10 @@
         <v>7728</v>
       </c>
       <c r="B182" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="C182" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="D182">
         <v>2</v>
@@ -7732,10 +7687,10 @@
         <v>7729</v>
       </c>
       <c r="B183" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="C183" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="D183">
         <v>2</v>
@@ -7762,10 +7717,10 @@
         <v>7730</v>
       </c>
       <c r="B184" t="s">
-        <v>383</v>
+        <v>368</v>
       </c>
       <c r="C184" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="D184">
         <v>2</v>
@@ -7792,10 +7747,10 @@
         <v>7731</v>
       </c>
       <c r="B185" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="C185" t="s">
-        <v>380</v>
+        <v>365</v>
       </c>
       <c r="D185">
         <v>2</v>
@@ -7822,10 +7777,10 @@
         <v>7732</v>
       </c>
       <c r="B186" t="s">
-        <v>521</v>
+        <v>506</v>
       </c>
       <c r="C186" t="s">
-        <v>386</v>
+        <v>371</v>
       </c>
       <c r="D186">
         <v>2</v>
@@ -7852,10 +7807,10 @@
         <v>7733</v>
       </c>
       <c r="B187" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="C187" t="s">
-        <v>360</v>
+        <v>345</v>
       </c>
       <c r="D187">
         <v>3</v>
@@ -7882,10 +7837,10 @@
         <v>7740</v>
       </c>
       <c r="B188" t="s">
-        <v>397</v>
+        <v>382</v>
       </c>
       <c r="C188" t="s">
-        <v>522</v>
+        <v>507</v>
       </c>
       <c r="D188">
         <v>3</v>
@@ -7912,10 +7867,10 @@
         <v>7735</v>
       </c>
       <c r="B189" t="s">
-        <v>438</v>
+        <v>423</v>
       </c>
       <c r="C189" t="s">
-        <v>439</v>
+        <v>424</v>
       </c>
       <c r="D189">
         <v>3</v>
@@ -7942,10 +7897,10 @@
         <v>7736</v>
       </c>
       <c r="B190" t="s">
-        <v>442</v>
+        <v>427</v>
       </c>
       <c r="C190" t="s">
-        <v>443</v>
+        <v>428</v>
       </c>
       <c r="D190">
         <v>3</v>
@@ -7972,10 +7927,10 @@
         <v>7737</v>
       </c>
       <c r="B191" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="C191" t="s">
-        <v>523</v>
+        <v>508</v>
       </c>
       <c r="D191">
         <v>3</v>
@@ -8002,10 +7957,10 @@
         <v>7738</v>
       </c>
       <c r="B192" t="s">
-        <v>391</v>
+        <v>376</v>
       </c>
       <c r="C192" t="s">
-        <v>524</v>
+        <v>509</v>
       </c>
       <c r="D192">
         <v>3</v>
@@ -8032,10 +7987,10 @@
         <v>7739</v>
       </c>
       <c r="B193" t="s">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="C193" t="s">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="D193">
         <v>3</v>
@@ -8062,10 +8017,10 @@
         <v>7734</v>
       </c>
       <c r="B194" t="s">
-        <v>446</v>
+        <v>431</v>
       </c>
       <c r="C194" t="s">
-        <v>527</v>
+        <v>512</v>
       </c>
       <c r="D194">
         <v>3</v>
@@ -8092,10 +8047,10 @@
         <v>7741</v>
       </c>
       <c r="B195" t="s">
-        <v>393</v>
+        <v>378</v>
       </c>
       <c r="C195" t="s">
-        <v>528</v>
+        <v>513</v>
       </c>
       <c r="D195">
         <v>3</v>
@@ -8122,10 +8077,10 @@
         <v>7742</v>
       </c>
       <c r="B196" t="s">
-        <v>529</v>
+        <v>514</v>
       </c>
       <c r="C196" t="s">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="D196">
         <v>3</v>
@@ -8152,10 +8107,10 @@
         <v>7743</v>
       </c>
       <c r="B197" t="s">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="C197" t="s">
-        <v>531</v>
+        <v>516</v>
       </c>
       <c r="D197">
         <v>3</v>
@@ -8182,10 +8137,10 @@
         <v>7749</v>
       </c>
       <c r="B198" t="s">
-        <v>452</v>
+        <v>437</v>
       </c>
       <c r="C198" t="s">
-        <v>532</v>
+        <v>517</v>
       </c>
       <c r="D198">
         <v>4</v>
@@ -8212,10 +8167,10 @@
         <v>7745</v>
       </c>
       <c r="B199" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="C199" t="s">
-        <v>533</v>
+        <v>518</v>
       </c>
       <c r="D199">
         <v>4</v>
@@ -8242,10 +8197,10 @@
         <v>7746</v>
       </c>
       <c r="B200" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="C200" t="s">
-        <v>534</v>
+        <v>519</v>
       </c>
       <c r="D200">
         <v>4</v>
@@ -8272,10 +8227,10 @@
         <v>7747</v>
       </c>
       <c r="B201" t="s">
-        <v>440</v>
+        <v>425</v>
       </c>
       <c r="C201" t="s">
-        <v>535</v>
+        <v>520</v>
       </c>
       <c r="D201">
         <v>4</v>
@@ -8302,10 +8257,10 @@
         <v>7748</v>
       </c>
       <c r="B202" t="s">
-        <v>395</v>
+        <v>380</v>
       </c>
       <c r="C202" t="s">
-        <v>536</v>
+        <v>521</v>
       </c>
       <c r="D202">
         <v>4</v>
@@ -8332,10 +8287,10 @@
         <v>7744</v>
       </c>
       <c r="B203" t="s">
-        <v>399</v>
+        <v>384</v>
       </c>
       <c r="C203" t="s">
-        <v>537</v>
+        <v>522</v>
       </c>
       <c r="D203">
         <v>4</v>
@@ -8362,10 +8317,10 @@
         <v>7750</v>
       </c>
       <c r="B204" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="C204" t="s">
-        <v>538</v>
+        <v>523</v>
       </c>
       <c r="D204">
         <v>4</v>
@@ -8392,10 +8347,10 @@
         <v>7751</v>
       </c>
       <c r="B205" t="s">
-        <v>454</v>
+        <v>439</v>
       </c>
       <c r="C205" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="D205">
         <v>4</v>
@@ -8422,10 +8377,10 @@
         <v>7752</v>
       </c>
       <c r="B206" t="s">
-        <v>409</v>
+        <v>394</v>
       </c>
       <c r="C206" t="s">
-        <v>539</v>
+        <v>524</v>
       </c>
       <c r="D206">
         <v>4</v>
@@ -8452,10 +8407,10 @@
         <v>7753</v>
       </c>
       <c r="B207" t="s">
-        <v>450</v>
+        <v>435</v>
       </c>
       <c r="C207" t="s">
-        <v>451</v>
+        <v>436</v>
       </c>
       <c r="D207">
         <v>4</v>
@@ -8482,10 +8437,10 @@
         <v>7763</v>
       </c>
       <c r="B208" t="s">
-        <v>444</v>
+        <v>429</v>
       </c>
       <c r="C208" t="s">
-        <v>540</v>
+        <v>525</v>
       </c>
       <c r="D208">
         <v>4</v>
@@ -8512,10 +8467,10 @@
         <v>7754</v>
       </c>
       <c r="B209" t="s">
-        <v>411</v>
+        <v>396</v>
       </c>
       <c r="C209" t="s">
-        <v>541</v>
+        <v>526</v>
       </c>
       <c r="D209">
         <v>5</v>
@@ -8542,10 +8497,10 @@
         <v>7755</v>
       </c>
       <c r="B210" t="s">
-        <v>427</v>
+        <v>412</v>
       </c>
       <c r="C210" t="s">
-        <v>542</v>
+        <v>527</v>
       </c>
       <c r="D210">
         <v>5</v>
@@ -8572,10 +8527,10 @@
         <v>7756</v>
       </c>
       <c r="B211" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="C211" t="s">
-        <v>459</v>
+        <v>444</v>
       </c>
       <c r="D211">
         <v>5</v>
@@ -8602,10 +8557,10 @@
         <v>7757</v>
       </c>
       <c r="B212" t="s">
-        <v>460</v>
+        <v>445</v>
       </c>
       <c r="C212" t="s">
-        <v>543</v>
+        <v>528</v>
       </c>
       <c r="D212">
         <v>5</v>
@@ -8632,10 +8587,10 @@
         <v>7758</v>
       </c>
       <c r="B213" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="C213" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
       <c r="D213">
         <v>5</v>
@@ -8662,10 +8617,10 @@
         <v>7760</v>
       </c>
       <c r="B214" t="s">
-        <v>544</v>
+        <v>529</v>
       </c>
       <c r="C214" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="D214">
         <v>5</v>
@@ -8681,7 +8636,7 @@
         <v>254</v>
       </c>
       <c r="H214" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I214">
         <v>2</v>
@@ -14216,8 +14171,8 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>114</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2">
         <v>2</v>
@@ -14226,21 +14181,21 @@
         <v>46038</v>
       </c>
       <c r="D2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F2" t="s">
         <v>115</v>
       </c>
-      <c r="E2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>116</v>
       </c>
-      <c r="G2" t="s">
-        <v>117</v>
-      </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>118</v>
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3">
         <v>23</v>
@@ -14249,21 +14204,21 @@
         <v>46044</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>121</v>
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -14272,21 +14227,21 @@
         <v>46049</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F4" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>125</v>
+      <c r="A5">
+        <v>4</v>
       </c>
       <c r="B5">
         <v>12</v>
@@ -14295,21 +14250,21 @@
         <v>46045</v>
       </c>
       <c r="D5" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F5" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="G5" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>129</v>
+      <c r="A6">
+        <v>5</v>
       </c>
       <c r="B6">
         <v>47</v>
@@ -14318,21 +14273,21 @@
         <v>46051</v>
       </c>
       <c r="D6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="E6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>131</v>
+      <c r="A7">
+        <v>6</v>
       </c>
       <c r="B7">
         <v>12</v>
@@ -14341,21 +14296,21 @@
         <v>46049</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G7" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>133</v>
+      <c r="A8">
+        <v>7</v>
       </c>
       <c r="B8">
         <v>23</v>
@@ -14364,21 +14319,21 @@
         <v>46056</v>
       </c>
       <c r="D8" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F8" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G8" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>134</v>
+      <c r="A9">
+        <v>8</v>
       </c>
       <c r="B9">
         <v>23</v>
@@ -14387,21 +14342,21 @@
         <v>46063</v>
       </c>
       <c r="D9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F9" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G9" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>135</v>
+      <c r="A10">
+        <v>9</v>
       </c>
       <c r="B10">
         <v>23</v>
@@ -14410,21 +14365,21 @@
         <v>46070</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F10" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="G10" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>136</v>
+      <c r="A11">
+        <v>10</v>
       </c>
       <c r="B11">
         <v>12</v>
@@ -14433,21 +14388,21 @@
         <v>46056</v>
       </c>
       <c r="D11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F11" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="G11" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>139</v>
+      <c r="A12">
+        <v>11</v>
       </c>
       <c r="B12">
         <v>12</v>
@@ -14456,21 +14411,21 @@
         <v>46063</v>
       </c>
       <c r="D12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="G12" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>140</v>
+      <c r="A13">
+        <v>12</v>
       </c>
       <c r="B13">
         <v>12</v>
@@ -14479,21 +14434,21 @@
         <v>46070</v>
       </c>
       <c r="D13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F13" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="G13" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>141</v>
+      <c r="A14">
+        <v>13</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -14502,21 +14457,21 @@
         <v>46058</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E14" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F14" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="G14" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>144</v>
+      <c r="A15">
+        <v>14</v>
       </c>
       <c r="B15">
         <v>23</v>
@@ -14525,21 +14480,21 @@
         <v>46059</v>
       </c>
       <c r="D15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E15" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F15" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="G15" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>147</v>
+      <c r="A16">
+        <v>15</v>
       </c>
       <c r="B16">
         <v>12</v>
@@ -14548,16 +14503,16 @@
         <v>46112</v>
       </c>
       <c r="D16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E16" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F16" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G16" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
     </row>
   </sheetData>
@@ -14580,10 +14535,10 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>54</v>
@@ -14595,7 +14550,7 @@
         <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -14610,57 +14565,57 @@
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>154</v>
+        <v>139</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>114</v>
+      <c r="A2">
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C2" t="s">
         <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="E2" s="3">
         <v>46038.654861111107</v>
@@ -14688,17 +14643,17 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>118</v>
+      <c r="A3">
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="C3" t="s">
         <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="E3" s="3">
         <v>46044.75</v>
@@ -14726,17 +14681,17 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>121</v>
+      <c r="A4">
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="C4" t="s">
         <v>39</v>
       </c>
       <c r="D4" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="E4" s="3">
         <v>46049.416666666657</v>
@@ -14764,17 +14719,17 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>125</v>
+      <c r="A5">
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D5" t="s">
-        <v>170</v>
+        <v>155</v>
       </c>
       <c r="E5" s="3">
         <v>46045.375</v>
@@ -14802,17 +14757,17 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>129</v>
+      <c r="A6">
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C6" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D6" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="E6" s="3">
         <v>46051.666666666657</v>
@@ -14840,17 +14795,17 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>131</v>
+      <c r="A7">
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C7" t="s">
         <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="E7" s="3">
         <v>46049.416666666657</v>
@@ -14878,17 +14833,17 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>133</v>
+      <c r="A8">
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C8" t="s">
         <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="E8" s="3">
         <v>46056.416666666657</v>
@@ -14916,17 +14871,17 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>134</v>
+      <c r="A9">
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C9" t="s">
         <v>32</v>
       </c>
       <c r="D9" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="E9" s="3">
         <v>46063.416666666657</v>
@@ -14954,17 +14909,17 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>135</v>
+      <c r="A10">
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="C10" t="s">
         <v>32</v>
       </c>
       <c r="D10" t="s">
-        <v>175</v>
+        <v>160</v>
       </c>
       <c r="E10" s="3">
         <v>46070.416666666657</v>
@@ -14992,17 +14947,17 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>136</v>
+      <c r="A11">
+        <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C11" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D11" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="E11" s="3">
         <v>46056.6875</v>
@@ -15030,17 +14985,17 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>139</v>
+      <c r="A12">
+        <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C12" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="E12" s="3">
         <v>46063.6875</v>
@@ -15068,17 +15023,17 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>140</v>
+      <c r="A13">
+        <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C13" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D13" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="E13" s="3">
         <v>46070.6875</v>
@@ -15106,17 +15061,17 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>141</v>
+      <c r="A14">
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="C14" t="s">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="D14" t="s">
-        <v>167</v>
+        <v>152</v>
       </c>
       <c r="E14" s="3">
         <v>46058.479166666657</v>
@@ -15144,17 +15099,17 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>144</v>
+      <c r="A15">
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="C15" t="s">
-        <v>179</v>
+        <v>164</v>
       </c>
       <c r="D15" t="s">
-        <v>180</v>
+        <v>165</v>
       </c>
       <c r="E15" s="3">
         <v>46059.727777777778</v>
@@ -15182,17 +15137,17 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>147</v>
+      <c r="A16">
+        <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="C16" t="s">
-        <v>169</v>
+        <v>154</v>
       </c>
       <c r="D16" t="s">
-        <v>182</v>
+        <v>167</v>
       </c>
       <c r="E16" s="3">
         <v>46112.625</v>
@@ -15248,49 +15203,49 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="B2" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="C2" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>176</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="C3" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="B4" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="C4" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="D4" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>168</v>
+        <v>153</v>
       </c>
       <c r="B5" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -15312,49 +15267,49 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>165</v>
+        <v>150</v>
       </c>
       <c r="B7" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C7" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="D7" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>181</v>
+        <v>166</v>
       </c>
       <c r="B8" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="C8" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="C9" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="B10" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="C10" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -15369,13 +15324,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>49</v>
@@ -15595,34 +15550,34 @@
         <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -15691,7 +15646,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="C2" t="s">
         <v>31</v>
@@ -15715,7 +15670,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>545</v>
+        <v>530</v>
       </c>
       <c r="O2" t="s">
         <v>35</v>
@@ -15726,7 +15681,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>576</v>
+        <v>561</v>
       </c>
       <c r="C3" t="s">
         <v>31</v>
@@ -15753,7 +15708,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>546</v>
+        <v>531</v>
       </c>
       <c r="O3" t="s">
         <v>35</v>
@@ -15764,7 +15719,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>575</v>
+        <v>560</v>
       </c>
       <c r="C4" t="s">
         <v>31</v>
@@ -15791,7 +15746,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="O4" t="s">
         <v>35</v>
@@ -15802,7 +15757,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>577</v>
+        <v>562</v>
       </c>
       <c r="C5" t="s">
         <v>31</v>
@@ -15826,7 +15781,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>548</v>
+        <v>533</v>
       </c>
       <c r="O5" t="s">
         <v>35</v>
@@ -15837,7 +15792,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C6" t="s">
         <v>31</v>
@@ -15875,7 +15830,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="C7" t="s">
         <v>31</v>
@@ -15902,7 +15857,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>547</v>
+        <v>532</v>
       </c>
       <c r="O7" t="s">
         <v>35</v>
@@ -15913,7 +15868,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C8" t="s">
         <v>31</v>
@@ -15940,7 +15895,7 @@
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>549</v>
+        <v>534</v>
       </c>
       <c r="O8" t="s">
         <v>35</v>
@@ -15951,7 +15906,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>578</v>
+        <v>563</v>
       </c>
       <c r="C9" t="s">
         <v>31</v>
@@ -15978,7 +15933,7 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>550</v>
+        <v>535</v>
       </c>
       <c r="O9" t="s">
         <v>35</v>
@@ -15989,7 +15944,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>579</v>
+        <v>564</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
@@ -16016,7 +15971,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>551</v>
+        <v>536</v>
       </c>
       <c r="O10" t="s">
         <v>35</v>
@@ -16027,7 +15982,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>580</v>
+        <v>565</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -16054,7 +16009,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>552</v>
+        <v>537</v>
       </c>
       <c r="O11" t="s">
         <v>35</v>
@@ -16065,7 +16020,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -16092,10 +16047,10 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>553</v>
+        <v>538</v>
       </c>
       <c r="L12" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="O12" t="s">
         <v>35</v>
@@ -16133,10 +16088,10 @@
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>554</v>
+        <v>539</v>
       </c>
       <c r="L13" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="O13" t="s">
         <v>35</v>
@@ -16147,7 +16102,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -16171,10 +16126,10 @@
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>555</v>
+        <v>540</v>
       </c>
       <c r="L14" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="O14" t="s">
         <v>35</v>
@@ -16185,7 +16140,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
@@ -16209,10 +16164,10 @@
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>556</v>
+        <v>541</v>
       </c>
       <c r="L15" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="O15" t="s">
         <v>35</v>
@@ -16223,7 +16178,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="C16" t="s">
         <v>31</v>
@@ -16232,7 +16187,7 @@
         <v>4</v>
       </c>
       <c r="K16" t="s">
-        <v>557</v>
+        <v>542</v>
       </c>
       <c r="O16" t="s">
         <v>35</v>
@@ -16243,7 +16198,7 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="C17" t="s">
         <v>37</v>
@@ -16270,7 +16225,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>558</v>
+        <v>543</v>
       </c>
       <c r="O17" t="s">
         <v>35</v>
@@ -16281,7 +16236,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="C18" t="s">
         <v>37</v>
@@ -16308,7 +16263,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>559</v>
+        <v>544</v>
       </c>
       <c r="O18" t="s">
         <v>35</v>
@@ -16319,7 +16274,7 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="C19" t="s">
         <v>37</v>
@@ -16346,7 +16301,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>560</v>
+        <v>545</v>
       </c>
       <c r="O19" t="s">
         <v>35</v>
@@ -16357,7 +16312,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="C20" t="s">
         <v>37</v>
@@ -16384,7 +16339,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>561</v>
+        <v>546</v>
       </c>
       <c r="O20" t="s">
         <v>35</v>
@@ -16395,7 +16350,7 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="C21" t="s">
         <v>37</v>
@@ -16422,7 +16377,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>562</v>
+        <v>547</v>
       </c>
       <c r="O21" t="s">
         <v>35</v>
@@ -16433,7 +16388,7 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C22" t="s">
         <v>37</v>
@@ -16460,7 +16415,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>563</v>
+        <v>548</v>
       </c>
       <c r="O22" t="s">
         <v>35</v>
@@ -16471,7 +16426,7 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="C23" t="s">
         <v>37</v>
@@ -16498,7 +16453,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>564</v>
+        <v>549</v>
       </c>
       <c r="O23" t="s">
         <v>35</v>
@@ -16536,7 +16491,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>565</v>
+        <v>550</v>
       </c>
       <c r="O24" t="s">
         <v>35</v>
@@ -16547,7 +16502,7 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C25" t="s">
         <v>37</v>
@@ -16574,7 +16529,7 @@
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>566</v>
+        <v>551</v>
       </c>
       <c r="O25" t="s">
         <v>35</v>
@@ -16585,7 +16540,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="C26" t="s">
         <v>37</v>
@@ -16609,10 +16564,10 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>567</v>
+        <v>552</v>
       </c>
       <c r="L26" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="O26" t="s">
         <v>35</v>
@@ -16623,7 +16578,7 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="C27" t="s">
         <v>37</v>
@@ -16644,7 +16599,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>568</v>
+        <v>553</v>
       </c>
       <c r="O27" t="s">
         <v>35</v>
@@ -16655,7 +16610,7 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C28" t="s">
         <v>37</v>
@@ -16679,7 +16634,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>569</v>
+        <v>554</v>
       </c>
       <c r="O28" t="s">
         <v>35</v>
@@ -16690,7 +16645,7 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C29" t="s">
         <v>37</v>
@@ -16714,7 +16669,7 @@
         <v>0</v>
       </c>
       <c r="K29" t="s">
-        <v>570</v>
+        <v>555</v>
       </c>
       <c r="O29" t="s">
         <v>35</v>
@@ -16725,7 +16680,7 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C30" t="s">
         <v>37</v>
@@ -16754,7 +16709,7 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="C31" t="s">
         <v>31</v>
@@ -16766,7 +16721,7 @@
         <v>442</v>
       </c>
       <c r="L31" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="O31" t="s">
         <v>35</v>
@@ -16777,7 +16732,7 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C32" t="s">
         <v>31</v>
@@ -16794,7 +16749,7 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="C33" t="s">
         <v>42</v>
@@ -16809,7 +16764,7 @@
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>571</v>
+        <v>556</v>
       </c>
       <c r="O33" t="s">
         <v>35</v>
@@ -16820,7 +16775,7 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="C34" t="s">
         <v>42</v>
@@ -16844,7 +16799,7 @@
         <v>0</v>
       </c>
       <c r="K34" t="s">
-        <v>572</v>
+        <v>557</v>
       </c>
       <c r="O34" t="s">
         <v>35</v>
@@ -16855,7 +16810,7 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="C35" t="s">
         <v>42</v>
@@ -16867,7 +16822,7 @@
         <v>30</v>
       </c>
       <c r="K35" t="s">
-        <v>573</v>
+        <v>558</v>
       </c>
       <c r="O35" t="s">
         <v>35</v>
@@ -16878,7 +16833,7 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="C36" t="s">
         <v>42</v>
@@ -16902,7 +16857,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>574</v>
+        <v>559</v>
       </c>
       <c r="O36" t="s">
         <v>35</v>
@@ -16913,7 +16868,7 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C37" t="s">
         <v>42</v>
@@ -16937,7 +16892,7 @@
         <v>149</v>
       </c>
       <c r="L37" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="O37" t="s">
         <v>35</v>
@@ -16948,7 +16903,7 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="C38" t="s">
         <v>42</v>
@@ -16963,7 +16918,7 @@
         <v>1</v>
       </c>
       <c r="L38" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="O38" t="s">
         <v>35</v>
@@ -16974,7 +16929,7 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="C39" t="s">
         <v>42</v>
@@ -16998,7 +16953,7 @@
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="O39" t="s">
         <v>35</v>
@@ -17009,7 +16964,7 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C40" t="s">
         <v>42</v>
@@ -17029,7 +16984,7 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="O41" t="s">
         <v>35</v>
@@ -17040,7 +16995,7 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="O42" t="s">
         <v>35</v>
@@ -17051,7 +17006,7 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="O43" t="s">
         <v>35</v>
@@ -17062,7 +17017,7 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="O44" t="s">
         <v>35</v>
@@ -17073,7 +17028,7 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="O45" t="s">
         <v>35</v>
@@ -17084,7 +17039,7 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="O46" t="s">
         <v>35</v>
@@ -17095,7 +17050,7 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="O47" t="s">
         <v>35</v>
@@ -17106,7 +17061,7 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
       <c r="O48" t="s">
         <v>35</v>
@@ -17117,7 +17072,7 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
       <c r="O49" t="s">
         <v>35</v>
@@ -17128,7 +17083,7 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="O50" t="s">
         <v>35</v>
@@ -17139,7 +17094,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="O51" t="s">
         <v>35</v>
@@ -17150,7 +17105,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="O52" t="s">
         <v>35</v>
@@ -17161,7 +17116,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="O53" t="s">
         <v>35</v>
@@ -17172,7 +17127,7 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="O54" t="s">
         <v>35</v>
@@ -17183,7 +17138,7 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="O55" t="s">
         <v>35</v>
@@ -17194,7 +17149,7 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="O56" t="s">
         <v>35</v>
@@ -17205,7 +17160,7 @@
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="O57" t="s">
         <v>35</v>
@@ -17216,7 +17171,7 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="O58" t="s">
         <v>35</v>
@@ -17227,7 +17182,7 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="O59" t="s">
         <v>35</v>
@@ -17238,7 +17193,7 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="O60" t="s">
         <v>35</v>
@@ -17249,7 +17204,7 @@
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>581</v>
+        <v>566</v>
       </c>
       <c r="O61" t="s">
         <v>35</v>
